--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
   <si>
     <t>Date</t>
   </si>
@@ -58,16 +63,79 @@
     <t>Tools Keeper</t>
   </si>
   <si>
-    <t>2025-07-07</t>
-  </si>
-  <si>
-    <t>2025-07-05</t>
-  </si>
-  <si>
-    <t>5631</t>
-  </si>
-  <si>
-    <t>100</t>
+    <t>Tasker</t>
+  </si>
+  <si>
+    <t>Conductor</t>
+  </si>
+  <si>
+    <t>T/Transporter</t>
+  </si>
+  <si>
+    <t>Hectares</t>
+  </si>
+  <si>
+    <t>Variety</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>2025-05-03</t>
+  </si>
+  <si>
+    <t>2025-05-04</t>
+  </si>
+  <si>
+    <t>2025-05-06</t>
+  </si>
+  <si>
+    <t>2025-05-08</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>2025-05-11</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>2025-05-16</t>
+  </si>
+  <si>
+    <t>2025-05-17</t>
+  </si>
+  <si>
+    <t>2025-05-22</t>
+  </si>
+  <si>
+    <t>2025-05-23</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>2025-10-29</t>
+  </si>
+  <si>
+    <t>DG34001</t>
+  </si>
+  <si>
+    <t>300</t>
   </si>
   <si>
     <t>1</t>
@@ -76,29 +144,92 @@
     <t>9</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>7</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>R579</t>
+  </si>
+  <si>
+    <t>MN1</t>
+  </si>
+  <si>
+    <t>MN2</t>
+  </si>
+  <si>
+    <t>MN6</t>
+  </si>
+  <si>
+    <t>MN8</t>
+  </si>
+  <si>
+    <t>MN3</t>
+  </si>
+  <si>
+    <t>MN4</t>
+  </si>
+  <si>
+    <t>MN5</t>
+  </si>
+  <si>
+    <t>MN7</t>
+  </si>
+  <si>
+    <t>MN9</t>
+  </si>
+  <si>
+    <t>MN10</t>
+  </si>
+  <si>
+    <t>MN11</t>
+  </si>
+  <si>
+    <t>MN12</t>
+  </si>
+  <si>
+    <t>MN13</t>
+  </si>
+  <si>
+    <t>MN14</t>
+  </si>
+  <si>
+    <t>MN15</t>
+  </si>
+  <si>
+    <t>MN16</t>
+  </si>
+  <si>
+    <t>MN17</t>
+  </si>
+  <si>
+    <t>MN18</t>
+  </si>
+  <si>
+    <t>MN19</t>
+  </si>
+  <si>
+    <t>MN20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +292,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -207,7 +346,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -239,9 +378,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -273,6 +413,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -448,11 +589,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,93 +636,1259 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>5290</v>
       </c>
       <c r="C2">
+        <v>84</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>249</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1.5</v>
+      </c>
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>3109</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>293</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>20</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>2.9</v>
+      </c>
+      <c r="S3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>5217</v>
+      </c>
+      <c r="C4">
         <v>170</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>9</v>
       </c>
-      <c r="F2">
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>17</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>390</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>12</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
+      <c r="R4">
+        <v>17</v>
+      </c>
+      <c r="S4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>2405</v>
+      </c>
+      <c r="C5">
+        <v>147</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>17</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>380</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>21</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>4222</v>
+      </c>
+      <c r="C6">
+        <v>86</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="G2">
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>162</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>13</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>21.5</v>
+      </c>
+      <c r="S6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>4224</v>
+      </c>
+      <c r="C7">
+        <v>52</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>135</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>2205</v>
+      </c>
+      <c r="C8">
+        <v>184</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>17</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>390</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>23</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>5</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>2207</v>
+      </c>
+      <c r="C9">
+        <v>73</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>166</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <v>16</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <v>4</v>
+      </c>
+      <c r="S9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>2205</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>104</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>6</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="R10">
+        <v>9</v>
+      </c>
+      <c r="S10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>2207</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <v>11</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>217</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>14</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>2</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>2304</v>
+      </c>
+      <c r="C12">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <v>186</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>25</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
+      <c r="R12">
+        <v>2.4</v>
+      </c>
+      <c r="S12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>1112</v>
+      </c>
+      <c r="C13">
+        <v>102</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>11</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>247</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>20</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="S13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>4107</v>
+      </c>
+      <c r="C14">
+        <v>41</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>120</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>15</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>3</v>
+      </c>
+      <c r="R14">
+        <v>3.2</v>
+      </c>
+      <c r="S14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>5219</v>
+      </c>
+      <c r="C15">
+        <v>87</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+      <c r="H15">
+        <v>15</v>
+      </c>
+      <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>242</v>
+      </c>
+      <c r="L15">
+        <v>4</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>20</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>5</v>
+      </c>
+      <c r="R15">
+        <v>4</v>
+      </c>
+      <c r="S15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>5216</v>
+      </c>
+      <c r="C16">
+        <v>85</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>7</v>
+      </c>
+      <c r="I16">
+        <v>7</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>236</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>20</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>5</v>
+      </c>
+      <c r="R16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>4311</v>
+      </c>
+      <c r="C17">
+        <v>126</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>17</v>
+      </c>
+      <c r="G17">
+        <v>17</v>
+      </c>
+      <c r="H17">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>9</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <v>317</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>20</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>5</v>
+      </c>
+      <c r="R17">
+        <v>4.8</v>
+      </c>
+      <c r="S17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <v>5513</v>
+      </c>
+      <c r="C18">
+        <v>52</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>169</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
         <v>12</v>
       </c>
-      <c r="H2">
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>2</v>
+      </c>
+      <c r="R18">
+        <v>5.2</v>
+      </c>
+      <c r="S18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>5510</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>106</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
         <v>8</v>
       </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>2</v>
+      </c>
+      <c r="R19">
+        <v>5.6</v>
+      </c>
+      <c r="S19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>2106</v>
+      </c>
+      <c r="C20">
+        <v>57</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
         <v>6</v>
       </c>
-      <c r="K2">
-        <v>368</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G20">
+        <v>6</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>207</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>5</v>
+      </c>
+      <c r="R20">
+        <v>6</v>
+      </c>
+      <c r="S20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>1125</v>
+      </c>
+      <c r="C21">
+        <v>98</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>227</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <v>13</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>2</v>
+      </c>
+      <c r="R21">
+        <v>6.4</v>
+      </c>
+      <c r="S21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" t="s">
+        <v>42</v>
+      </c>
+      <c r="O22" t="s">
+        <v>45</v>
+      </c>
+      <c r="P22" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>42</v>
+      </c>
+      <c r="R22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S22" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -30,6 +25,12 @@
     <t>Bundles Cut</t>
   </si>
   <si>
+    <t>Hectares</t>
+  </si>
+  <si>
+    <t>Variety</t>
+  </si>
+  <si>
     <t>Foreman</t>
   </si>
   <si>
@@ -72,12 +73,6 @@
     <t>T/Transporter</t>
   </si>
   <si>
-    <t>Hectares</t>
-  </si>
-  <si>
-    <t>Variety</t>
-  </si>
-  <si>
     <t>2025-04-27</t>
   </si>
   <si>
@@ -129,107 +124,86 @@
     <t>2025-05-26</t>
   </si>
   <si>
-    <t>2025-10-29</t>
-  </si>
-  <si>
-    <t>DG34001</t>
-  </si>
-  <si>
-    <t>300</t>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>2025-06-03</t>
+  </si>
+  <si>
+    <t>4211</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>7.95</t>
+  </si>
+  <si>
+    <t>N14</t>
+  </si>
+  <si>
+    <t>R579</t>
+  </si>
+  <si>
+    <t>N41</t>
+  </si>
+  <si>
+    <t>R570</t>
+  </si>
+  <si>
+    <t>97F1692</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>MN1</t>
+  </si>
+  <si>
+    <t>N23</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>200</t>
+    <t>319</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>R579</t>
-  </si>
-  <si>
-    <t>MN1</t>
-  </si>
-  <si>
-    <t>MN2</t>
-  </si>
-  <si>
-    <t>MN6</t>
-  </si>
-  <si>
-    <t>MN8</t>
-  </si>
-  <si>
-    <t>MN3</t>
-  </si>
-  <si>
-    <t>MN4</t>
-  </si>
-  <si>
-    <t>MN5</t>
-  </si>
-  <si>
-    <t>MN7</t>
-  </si>
-  <si>
-    <t>MN9</t>
-  </si>
-  <si>
-    <t>MN10</t>
-  </si>
-  <si>
-    <t>MN11</t>
-  </si>
-  <si>
-    <t>MN12</t>
-  </si>
-  <si>
-    <t>MN13</t>
-  </si>
-  <si>
-    <t>MN14</t>
-  </si>
-  <si>
-    <t>MN15</t>
-  </si>
-  <si>
-    <t>MN16</t>
-  </si>
-  <si>
-    <t>MN17</t>
-  </si>
-  <si>
-    <t>MN18</t>
-  </si>
-  <si>
-    <t>MN19</t>
-  </si>
-  <si>
-    <t>MN20</t>
+    <t>20</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,14 +266,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -346,7 +312,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -378,10 +344,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -413,7 +378,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -589,11 +553,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -663,17 +627,17 @@
         <v>84</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+        <v>3.8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>8</v>
       </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
-      </c>
       <c r="H2">
         <v>7</v>
       </c>
@@ -681,37 +645,37 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>249</v>
       </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
       <c r="N2">
         <v>3</v>
       </c>
       <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>3</v>
+      </c>
+      <c r="Q2">
         <v>10</v>
       </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
       <c r="R2">
-        <v>1.5</v>
-      </c>
-      <c r="S2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -722,55 +686,55 @@
         <v>80</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+        <v>3.6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
       <c r="H3">
         <v>7</v>
       </c>
       <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
         <v>9</v>
       </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
         <v>293</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>4</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>4</v>
       </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-      <c r="O3">
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
         <v>20</v>
       </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="R3">
-        <v>2.9</v>
-      </c>
-      <c r="S3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -781,55 +745,55 @@
         <v>170</v>
       </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+        <v>7.72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>9</v>
-      </c>
-      <c r="F4">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>17</v>
       </c>
       <c r="H4">
         <v>17</v>
       </c>
       <c r="I4">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>17</v>
+      </c>
+      <c r="K4">
         <v>9</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>6</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>390</v>
       </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
         <v>12</v>
       </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="R4">
-        <v>17</v>
-      </c>
-      <c r="S4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -840,55 +804,55 @@
         <v>147</v>
       </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
+        <v>6.6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>9</v>
-      </c>
-      <c r="F5">
-        <v>17</v>
-      </c>
-      <c r="G5">
-        <v>17</v>
       </c>
       <c r="H5">
         <v>17</v>
       </c>
       <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5">
         <v>9</v>
       </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
         <v>380</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>4</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-      <c r="O5">
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
         <v>21</v>
       </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="R5">
-        <v>23</v>
-      </c>
-      <c r="S5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -899,55 +863,55 @@
         <v>86</v>
       </c>
       <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
+        <v>3.9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>9</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>9</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>4</v>
       </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>162</v>
       </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
       <c r="N6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>13</v>
       </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>3</v>
-      </c>
       <c r="R6">
-        <v>21.5</v>
-      </c>
-      <c r="S6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -958,55 +922,55 @@
         <v>52</v>
       </c>
       <c r="D7">
+        <v>2.36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
         <v>6</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>4</v>
       </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
         <v>135</v>
       </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
       <c r="N7">
         <v>1</v>
       </c>
       <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>10</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>0</v>
       </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7">
-        <v>5</v>
-      </c>
-      <c r="S7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1017,55 +981,55 @@
         <v>184</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
+        <v>18.6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>9</v>
-      </c>
-      <c r="F8">
-        <v>17</v>
-      </c>
-      <c r="G8">
-        <v>17</v>
       </c>
       <c r="H8">
         <v>17</v>
       </c>
       <c r="I8">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <v>17</v>
+      </c>
+      <c r="K8">
         <v>9</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8">
-        <v>390</v>
       </c>
       <c r="L8">
         <v>4</v>
       </c>
       <c r="M8">
+        <v>390</v>
+      </c>
+      <c r="N8">
         <v>4</v>
       </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
       <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
         <v>23</v>
       </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="R8">
-        <v>2</v>
-      </c>
-      <c r="S8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1076,55 +1040,55 @@
         <v>73</v>
       </c>
       <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
+        <v>13.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>5</v>
-      </c>
-      <c r="F9">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
       <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9">
         <v>6</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
         <v>166</v>
       </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
       <c r="N9">
         <v>2</v>
       </c>
       <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>2</v>
+      </c>
+      <c r="Q9">
         <v>16</v>
       </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
       <c r="R9">
-        <v>4</v>
-      </c>
-      <c r="S9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1135,55 +1099,55 @@
         <v>50</v>
       </c>
       <c r="D10">
+        <v>4.3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10">
         <v>0</v>
       </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>2</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>104</v>
       </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>2</v>
-      </c>
       <c r="N10">
         <v>1</v>
       </c>
       <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <v>6</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>0</v>
       </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10">
-        <v>9</v>
-      </c>
-      <c r="S10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1194,55 +1158,55 @@
         <v>100</v>
       </c>
       <c r="D11">
+        <v>4.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11">
         <v>0</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>5</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>10</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>11</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>11</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11">
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
         <v>217</v>
       </c>
-      <c r="L11">
-        <v>2</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
       <c r="N11">
         <v>2</v>
       </c>
       <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
         <v>14</v>
       </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
       <c r="R11">
-        <v>2</v>
-      </c>
-      <c r="S11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1253,55 +1217,55 @@
         <v>80</v>
       </c>
       <c r="D12">
+        <v>3.6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12">
         <v>0</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>9</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>9</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>8</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>5</v>
       </c>
-      <c r="J12">
-        <v>3</v>
-      </c>
-      <c r="K12">
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="M12">
         <v>186</v>
       </c>
-      <c r="L12">
-        <v>3</v>
-      </c>
-      <c r="M12">
-        <v>2</v>
-      </c>
       <c r="N12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
         <v>25</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
         <v>5</v>
       </c>
-      <c r="R12">
-        <v>2.4</v>
-      </c>
-      <c r="S12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1312,55 +1276,55 @@
         <v>102</v>
       </c>
       <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
+        <v>4.6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>5</v>
-      </c>
-      <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>11</v>
       </c>
       <c r="H13">
         <v>11</v>
       </c>
       <c r="I13">
+        <v>11</v>
+      </c>
+      <c r="J13">
+        <v>11</v>
+      </c>
+      <c r="K13">
         <v>6</v>
       </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13">
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
         <v>247</v>
       </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
       <c r="N13">
         <v>2</v>
       </c>
       <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13">
         <v>20</v>
       </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
       <c r="R13">
-        <v>4</v>
-      </c>
-      <c r="S13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1371,55 +1335,55 @@
         <v>41</v>
       </c>
       <c r="D14">
+        <v>1.8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14">
         <v>0</v>
       </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K14">
+        <v>4</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
         <v>120</v>
       </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
         <v>15</v>
       </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
       <c r="R14">
-        <v>3.2</v>
-      </c>
-      <c r="S14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1430,55 +1394,55 @@
         <v>87</v>
       </c>
       <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
+        <v>3.9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
         <v>6</v>
-      </c>
-      <c r="F15">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>15</v>
       </c>
       <c r="H15">
         <v>15</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K15">
+        <v>7</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
         <v>242</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>4</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>3</v>
-      </c>
       <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+      <c r="Q15">
         <v>20</v>
       </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15">
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
         <v>5</v>
       </c>
-      <c r="R15">
-        <v>4</v>
-      </c>
-      <c r="S15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1489,17 +1453,17 @@
         <v>85</v>
       </c>
       <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
+        <v>3.8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
         <v>6</v>
       </c>
-      <c r="F16">
-        <v>7</v>
-      </c>
-      <c r="G16">
-        <v>7</v>
-      </c>
       <c r="H16">
         <v>7</v>
       </c>
@@ -1507,37 +1471,37 @@
         <v>7</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K16">
+        <v>7</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
         <v>236</v>
       </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
       <c r="N16">
         <v>2</v>
       </c>
       <c r="O16">
+        <v>2</v>
+      </c>
+      <c r="P16">
+        <v>2</v>
+      </c>
+      <c r="Q16">
         <v>20</v>
       </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="Q16">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
         <v>5</v>
       </c>
-      <c r="R16">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="S16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1548,55 +1512,55 @@
         <v>126</v>
       </c>
       <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
+        <v>5.7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
         <v>10</v>
-      </c>
-      <c r="F17">
-        <v>17</v>
-      </c>
-      <c r="G17">
-        <v>17</v>
       </c>
       <c r="H17">
         <v>17</v>
       </c>
       <c r="I17">
+        <v>17</v>
+      </c>
+      <c r="J17">
+        <v>17</v>
+      </c>
+      <c r="K17">
         <v>9</v>
       </c>
-      <c r="J17">
-        <v>3</v>
-      </c>
-      <c r="K17">
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
         <v>317</v>
       </c>
-      <c r="L17">
-        <v>3</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
       <c r="N17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
+        <v>2</v>
+      </c>
+      <c r="Q17">
         <v>20</v>
       </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="Q17">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
         <v>5</v>
       </c>
-      <c r="R17">
-        <v>4.8</v>
-      </c>
-      <c r="S17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1607,16 +1571,16 @@
         <v>52</v>
       </c>
       <c r="D18">
+        <v>2.3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18">
         <v>0</v>
       </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
       <c r="G18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1625,37 +1589,37 @@
         <v>5</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
         <v>169</v>
       </c>
-      <c r="L18">
-        <v>2</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
       <c r="N18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
         <v>12</v>
       </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <v>2</v>
-      </c>
       <c r="R18">
-        <v>5.2</v>
-      </c>
-      <c r="S18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1666,55 +1630,55 @@
         <v>30</v>
       </c>
       <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
+        <v>1.3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
         <v>4</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>4</v>
       </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-      <c r="H19">
-        <v>3</v>
-      </c>
       <c r="I19">
         <v>3</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
         <v>106</v>
       </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
       <c r="N19">
         <v>1</v>
       </c>
       <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
         <v>8</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>0</v>
       </c>
-      <c r="Q19">
-        <v>2</v>
-      </c>
-      <c r="R19">
-        <v>5.6</v>
-      </c>
-      <c r="S19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1725,16 +1689,16 @@
         <v>57</v>
       </c>
       <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -1743,37 +1707,37 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K20">
+        <v>6</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20">
         <v>207</v>
       </c>
-      <c r="L20">
-        <v>3</v>
-      </c>
-      <c r="M20">
-        <v>2</v>
-      </c>
       <c r="N20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>2</v>
+      </c>
+      <c r="Q20">
         <v>20</v>
       </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
         <v>5</v>
       </c>
-      <c r="R20">
-        <v>6</v>
-      </c>
-      <c r="S20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1784,111 +1748,465 @@
         <v>98</v>
       </c>
       <c r="D21">
+        <v>4.4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21">
         <v>0</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>6</v>
-      </c>
-      <c r="F21">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>10</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>10</v>
+      </c>
+      <c r="K21">
         <v>5</v>
       </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
-      <c r="K21">
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
         <v>227</v>
       </c>
-      <c r="L21">
-        <v>2</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
       <c r="N21">
         <v>2</v>
       </c>
       <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
         <v>13</v>
       </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <v>2</v>
-      </c>
       <c r="R21">
-        <v>6.4</v>
-      </c>
-      <c r="S21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>3308</v>
+      </c>
+      <c r="C22">
+        <v>56</v>
+      </c>
+      <c r="D22">
+        <v>2.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>6</v>
+      </c>
+      <c r="J22">
+        <v>6</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>123</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>9</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <v>2526</v>
+      </c>
+      <c r="C23">
+        <v>205</v>
+      </c>
+      <c r="D23">
+        <v>23.7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>17</v>
+      </c>
+      <c r="I23">
+        <v>17</v>
+      </c>
+      <c r="J23">
+        <v>17</v>
+      </c>
+      <c r="K23">
+        <v>9</v>
+      </c>
+      <c r="L23">
+        <v>6</v>
+      </c>
+      <c r="M23">
+        <v>373</v>
+      </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <v>3</v>
+      </c>
+      <c r="Q23">
+        <v>20</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24">
+        <v>2526</v>
+      </c>
+      <c r="C24">
+        <v>89</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+      <c r="H24">
+        <v>9</v>
+      </c>
+      <c r="I24">
+        <v>9</v>
+      </c>
+      <c r="J24">
+        <v>9</v>
+      </c>
+      <c r="K24">
+        <v>8</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>331</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
+        <v>20</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25">
+        <v>4104</v>
+      </c>
+      <c r="C25">
         <v>67</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D25">
+        <v>3.04</v>
+      </c>
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+      <c r="H25">
+        <v>7</v>
+      </c>
+      <c r="I25">
+        <v>7</v>
+      </c>
+      <c r="J25">
+        <v>7</v>
+      </c>
+      <c r="K25">
+        <v>6</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>215</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>24</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
         <v>39</v>
       </c>
-      <c r="E22" t="s">
+      <c r="B26">
+        <v>5301</v>
+      </c>
+      <c r="C26">
+        <v>117</v>
+      </c>
+      <c r="D26">
+        <v>5.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>10</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>11</v>
+      </c>
+      <c r="K26">
+        <v>5</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <v>121</v>
+      </c>
+      <c r="N26">
+        <v>2</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>2</v>
+      </c>
+      <c r="Q26">
+        <v>12</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27">
+        <v>5434</v>
+      </c>
+      <c r="C27">
+        <v>78</v>
+      </c>
+      <c r="D27">
+        <v>4.06</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27">
+        <v>7</v>
+      </c>
+      <c r="J27">
+        <v>6</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>144</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>6</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="F22" t="s">
+      <c r="B28" t="s">
         <v>41</v>
       </c>
-      <c r="G22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="C28" t="s">
         <v>42</v>
       </c>
-      <c r="K22" t="s">
+      <c r="D28" t="s">
         <v>43</v>
       </c>
-      <c r="L22" t="s">
-        <v>44</v>
-      </c>
-      <c r="M22" t="s">
-        <v>44</v>
-      </c>
-      <c r="N22" t="s">
-        <v>42</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="E28" t="s">
         <v>45</v>
       </c>
-      <c r="P22" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>42</v>
-      </c>
-      <c r="R22" t="s">
-        <v>46</v>
-      </c>
-      <c r="S22" t="s">
-        <v>47</v>
+      <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" t="s">
+        <v>54</v>
+      </c>
+      <c r="J28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" t="s">
+        <v>55</v>
+      </c>
+      <c r="L28" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" t="s">
+        <v>58</v>
+      </c>
+      <c r="P28" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>59</v>
+      </c>
+      <c r="R28" t="s">
+        <v>52</v>
+      </c>
+      <c r="S28" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -139,13 +139,208 @@
     <t>2025-06-03</t>
   </si>
   <si>
-    <t>4211</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>7.95</t>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>2025-06-08</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>2025-06-10</t>
+  </si>
+  <si>
+    <t>2025-06-11</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>2025-06-13</t>
+  </si>
+  <si>
+    <t>2025-06-14</t>
+  </si>
+  <si>
+    <t>2025-06-15</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>2025-06-19</t>
+  </si>
+  <si>
+    <t>2025-06-20</t>
+  </si>
+  <si>
+    <t>2025-06-21</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-07-01</t>
+  </si>
+  <si>
+    <t>2025-07-02</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>2025-07-05</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>2025-07-07</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-26</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2025-08-02</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
+  </si>
+  <si>
+    <t>2025-08-16</t>
+  </si>
+  <si>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>4239</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0.24</t>
   </si>
   <si>
     <t>N14</t>
@@ -172,31 +367,34 @@
     <t>N23</t>
   </si>
   <si>
+    <t>N36</t>
+  </si>
+  <si>
+    <t>N25</t>
+  </si>
+  <si>
+    <t>MIX</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>CO62175</t>
+  </si>
+  <si>
+    <t>90F0613</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>19</t>
   </si>
 </sst>
 </file>
@@ -554,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -630,7 +828,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -689,7 +887,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -748,7 +946,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -807,7 +1005,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -866,7 +1064,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -925,7 +1123,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -984,7 +1182,7 @@
         <v>18.6</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1043,7 +1241,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1102,7 +1300,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1161,7 +1359,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1220,7 +1418,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1279,7 +1477,7 @@
         <v>4.6</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1338,7 +1536,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1397,7 +1595,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1456,7 +1654,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1515,7 +1713,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1574,7 +1772,7 @@
         <v>2.3</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1633,7 +1831,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1692,7 +1890,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1751,7 +1949,7 @@
         <v>4.4</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1810,7 +2008,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1869,7 +2067,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1928,7 +2126,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1987,7 +2185,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2046,7 +2244,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2105,7 +2303,7 @@
         <v>4.06</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2154,59 +2352,5192 @@
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>4211</v>
+      </c>
+      <c r="C28">
+        <v>175</v>
+      </c>
+      <c r="D28">
+        <v>7.95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>17</v>
+      </c>
+      <c r="I28">
+        <v>17</v>
+      </c>
+      <c r="J28">
+        <v>17</v>
+      </c>
+      <c r="K28">
+        <v>9</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
+      <c r="M28">
+        <v>319</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>20</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
         <v>41</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B29">
+        <v>4211</v>
+      </c>
+      <c r="C29">
+        <v>50</v>
+      </c>
+      <c r="D29">
+        <v>2.2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29">
+        <v>4</v>
+      </c>
+      <c r="K29">
+        <v>4</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>127</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>21</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
         <v>42</v>
       </c>
-      <c r="D28" t="s">
+      <c r="B30">
+        <v>5442</v>
+      </c>
+      <c r="C30">
+        <v>72</v>
+      </c>
+      <c r="D30">
+        <v>3.27</v>
+      </c>
+      <c r="E30" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
+      </c>
+      <c r="H30">
+        <v>7</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30">
+        <v>6</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30">
+        <v>205</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30">
+        <v>2</v>
+      </c>
+      <c r="P30">
+        <v>2</v>
+      </c>
+      <c r="Q30">
+        <v>26</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
         <v>43</v>
       </c>
-      <c r="E28" t="s">
+      <c r="B31">
+        <v>3302</v>
+      </c>
+      <c r="C31">
+        <v>183</v>
+      </c>
+      <c r="D31">
+        <v>8.31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>17</v>
+      </c>
+      <c r="I31">
+        <v>17</v>
+      </c>
+      <c r="J31">
+        <v>17</v>
+      </c>
+      <c r="K31">
+        <v>9</v>
+      </c>
+      <c r="L31">
+        <v>3</v>
+      </c>
+      <c r="M31">
+        <v>278</v>
+      </c>
+      <c r="N31">
+        <v>4</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>20</v>
+      </c>
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32">
+        <v>3302</v>
+      </c>
+      <c r="C32">
+        <v>79</v>
+      </c>
+      <c r="D32">
+        <v>3.59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>8</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+      <c r="J32">
+        <v>8</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>150</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <v>13</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>5211</v>
+      </c>
+      <c r="C33">
+        <v>47</v>
+      </c>
+      <c r="D33">
+        <v>2.13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>88</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>2</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <v>8</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" t="s">
         <v>45</v>
       </c>
-      <c r="F28" t="s">
+      <c r="B34">
+        <v>5218</v>
+      </c>
+      <c r="C34">
+        <v>106</v>
+      </c>
+      <c r="D34">
+        <v>4.8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>13</v>
+      </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
+      <c r="J34">
+        <v>13</v>
+      </c>
+      <c r="K34">
+        <v>6</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>231</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34">
+        <v>2</v>
+      </c>
+      <c r="Q34">
+        <v>22</v>
+      </c>
+      <c r="R34">
+        <v>1</v>
+      </c>
+      <c r="S34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>5454</v>
+      </c>
+      <c r="C35">
+        <v>45</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>115</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>2</v>
+      </c>
+      <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>4</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36">
+        <v>3493</v>
+      </c>
+      <c r="C36">
+        <v>145</v>
+      </c>
+      <c r="D36">
+        <v>6.45</v>
+      </c>
+      <c r="E36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>11</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+      <c r="K36">
+        <v>5</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36">
+        <v>214</v>
+      </c>
+      <c r="N36">
+        <v>2</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36">
+        <v>16</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37">
+        <v>3120</v>
+      </c>
+      <c r="C37">
+        <v>104</v>
+      </c>
+      <c r="D37">
+        <v>4.72</v>
+      </c>
+      <c r="E37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>10</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37">
+        <v>5</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>157</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>7</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38">
+        <v>5454</v>
+      </c>
+      <c r="C38">
+        <v>40</v>
+      </c>
+      <c r="D38">
+        <v>1.8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>6</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
+      </c>
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>66</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="Q38">
+        <v>5</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>3120</v>
+      </c>
+      <c r="C39">
+        <v>129</v>
+      </c>
+      <c r="D39">
+        <v>5.86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+      <c r="H39">
+        <v>15</v>
+      </c>
+      <c r="I39">
+        <v>14</v>
+      </c>
+      <c r="J39">
+        <v>15</v>
+      </c>
+      <c r="K39">
+        <v>8</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39">
+        <v>263</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+      <c r="Q39">
+        <v>26</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40">
+        <v>1211</v>
+      </c>
+      <c r="C40">
+        <v>136</v>
+      </c>
+      <c r="D40">
+        <v>6.18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+      <c r="H40">
+        <v>13</v>
+      </c>
+      <c r="I40">
+        <v>12</v>
+      </c>
+      <c r="J40">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>6</v>
+      </c>
+      <c r="L40">
+        <v>4</v>
+      </c>
+      <c r="M40">
+        <v>234</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <v>15</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41">
+        <v>1211</v>
+      </c>
+      <c r="C41">
+        <v>154</v>
+      </c>
+      <c r="D41">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>15</v>
+      </c>
+      <c r="I41">
+        <v>15</v>
+      </c>
+      <c r="J41">
+        <v>14</v>
+      </c>
+      <c r="K41">
+        <v>7</v>
+      </c>
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="M41">
+        <v>281</v>
+      </c>
+      <c r="N41">
+        <v>3</v>
+      </c>
+      <c r="O41">
+        <v>2</v>
+      </c>
+      <c r="P41">
+        <v>2</v>
+      </c>
+      <c r="Q41">
+        <v>25</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42">
+        <v>2307</v>
+      </c>
+      <c r="C42">
+        <v>157</v>
+      </c>
+      <c r="D42">
+        <v>7.13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>7</v>
+      </c>
+      <c r="H42">
+        <v>15</v>
+      </c>
+      <c r="I42">
+        <v>15</v>
+      </c>
+      <c r="J42">
+        <v>15</v>
+      </c>
+      <c r="K42">
+        <v>8</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42">
+        <v>292</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42">
+        <v>20</v>
+      </c>
+      <c r="R42">
+        <v>1</v>
+      </c>
+      <c r="S42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
+      <c r="A43" t="s">
         <v>52</v>
       </c>
-      <c r="G28" t="s">
+      <c r="B43">
+        <v>5204</v>
+      </c>
+      <c r="C43">
+        <v>182</v>
+      </c>
+      <c r="D43">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E43" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>15</v>
+      </c>
+      <c r="I43">
+        <v>15</v>
+      </c>
+      <c r="J43">
+        <v>14</v>
+      </c>
+      <c r="K43">
+        <v>9</v>
+      </c>
+      <c r="L43">
+        <v>3</v>
+      </c>
+      <c r="M43">
+        <v>304</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43">
+        <v>2</v>
+      </c>
+      <c r="P43">
+        <v>2</v>
+      </c>
+      <c r="Q43">
+        <v>25</v>
+      </c>
+      <c r="R43">
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="A44" t="s">
         <v>53</v>
       </c>
-      <c r="H28" t="s">
+      <c r="B44">
+        <v>4208</v>
+      </c>
+      <c r="C44">
+        <v>128</v>
+      </c>
+      <c r="D44">
+        <v>5.81</v>
+      </c>
+      <c r="E44" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>6</v>
+      </c>
+      <c r="H44">
+        <v>13</v>
+      </c>
+      <c r="I44">
+        <v>12</v>
+      </c>
+      <c r="J44">
+        <v>13</v>
+      </c>
+      <c r="K44">
+        <v>6</v>
+      </c>
+      <c r="L44">
+        <v>3</v>
+      </c>
+      <c r="M44">
+        <v>211</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
+      </c>
+      <c r="O44">
+        <v>2</v>
+      </c>
+      <c r="P44">
+        <v>2</v>
+      </c>
+      <c r="Q44">
+        <v>23</v>
+      </c>
+      <c r="R44">
+        <v>1</v>
+      </c>
+      <c r="S44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="A45" t="s">
         <v>54</v>
       </c>
-      <c r="I28" t="s">
+      <c r="B45">
+        <v>2302</v>
+      </c>
+      <c r="C45">
+        <v>90</v>
+      </c>
+      <c r="D45">
+        <v>4.09</v>
+      </c>
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>10</v>
+      </c>
+      <c r="I45">
+        <v>8</v>
+      </c>
+      <c r="J45">
+        <v>8</v>
+      </c>
+      <c r="K45">
+        <v>5</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
+      <c r="M45">
+        <v>154</v>
+      </c>
+      <c r="N45">
+        <v>2</v>
+      </c>
+      <c r="O45">
+        <v>2</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45">
+        <v>16</v>
+      </c>
+      <c r="R45">
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="A46" t="s">
         <v>54</v>
       </c>
-      <c r="J28" t="s">
-        <v>54</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="B46">
+        <v>5117</v>
+      </c>
+      <c r="C46">
+        <v>21</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>2</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>42</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>5</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="L28" t="s">
+      <c r="B47">
+        <v>5101</v>
+      </c>
+      <c r="C47">
+        <v>181</v>
+      </c>
+      <c r="D47">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E47" t="s">
+        <v>112</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>8</v>
+      </c>
+      <c r="H47">
+        <v>14</v>
+      </c>
+      <c r="I47">
+        <v>14</v>
+      </c>
+      <c r="J47">
+        <v>15</v>
+      </c>
+      <c r="K47">
+        <v>9</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>297</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
+      <c r="P47">
+        <v>2</v>
+      </c>
+      <c r="Q47">
+        <v>23</v>
+      </c>
+      <c r="R47">
+        <v>1</v>
+      </c>
+      <c r="S47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
         <v>56</v>
       </c>
-      <c r="M28" t="s">
+      <c r="B48">
+        <v>1221</v>
+      </c>
+      <c r="C48">
+        <v>127</v>
+      </c>
+      <c r="D48">
+        <v>5.13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>113</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="I48">
+        <v>10</v>
+      </c>
+      <c r="J48">
+        <v>8</v>
+      </c>
+      <c r="K48">
+        <v>6</v>
+      </c>
+      <c r="L48">
+        <v>4</v>
+      </c>
+      <c r="M48">
+        <v>182</v>
+      </c>
+      <c r="N48">
+        <v>2</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="Q48">
+        <v>14</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49">
+        <v>5101</v>
+      </c>
+      <c r="C49">
+        <v>40</v>
+      </c>
+      <c r="D49">
+        <v>1.81</v>
+      </c>
+      <c r="E49" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>4</v>
+      </c>
+      <c r="J49">
+        <v>4</v>
+      </c>
+      <c r="K49">
+        <v>2</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>80</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="P49">
+        <v>1</v>
+      </c>
+      <c r="Q49">
+        <v>4</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
+      <c r="A50" t="s">
         <v>57</v>
       </c>
-      <c r="N28" t="s">
+      <c r="B50">
+        <v>5113</v>
+      </c>
+      <c r="C50">
+        <v>175</v>
+      </c>
+      <c r="D50">
+        <v>7.95</v>
+      </c>
+      <c r="E50" t="s">
+        <v>118</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>7</v>
+      </c>
+      <c r="H50">
+        <v>15</v>
+      </c>
+      <c r="I50">
+        <v>14</v>
+      </c>
+      <c r="J50">
+        <v>15</v>
+      </c>
+      <c r="K50">
+        <v>8</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>290</v>
+      </c>
+      <c r="N50">
+        <v>2</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50">
+        <v>21</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
+      <c r="A51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51">
+        <v>1221</v>
+      </c>
+      <c r="C51">
+        <v>14</v>
+      </c>
+      <c r="D51">
+        <v>0.64</v>
+      </c>
+      <c r="E51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>31</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>2</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52">
+        <v>2515</v>
+      </c>
+      <c r="C52">
+        <v>135</v>
+      </c>
+      <c r="D52">
+        <v>6.13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>5</v>
+      </c>
+      <c r="H52">
+        <v>10</v>
+      </c>
+      <c r="I52">
+        <v>8</v>
+      </c>
+      <c r="J52">
+        <v>9</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+      <c r="L52">
+        <v>3</v>
+      </c>
+      <c r="M52">
+        <v>177</v>
+      </c>
+      <c r="N52">
+        <v>2</v>
+      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="Q52">
+        <v>15</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>5458</v>
+      </c>
+      <c r="C53">
+        <v>61</v>
+      </c>
+      <c r="D53">
+        <v>2.77</v>
+      </c>
+      <c r="E53" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+      <c r="K53">
+        <v>3</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>101</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53">
+        <v>1</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <v>8</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>5408</v>
+      </c>
+      <c r="C54">
+        <v>107</v>
+      </c>
+      <c r="D54">
+        <v>4.35</v>
+      </c>
+      <c r="E54" t="s">
+        <v>110</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="H54">
+        <v>13</v>
+      </c>
+      <c r="I54">
+        <v>13</v>
+      </c>
+      <c r="J54">
+        <v>13</v>
+      </c>
+      <c r="K54">
+        <v>7</v>
+      </c>
+      <c r="L54">
+        <v>3</v>
+      </c>
+      <c r="M54">
+        <v>213</v>
+      </c>
+      <c r="N54">
+        <v>2</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="Q54">
+        <v>20</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
+        <v>5209</v>
+      </c>
+      <c r="C55">
+        <v>165</v>
+      </c>
+      <c r="D55">
+        <v>5.24</v>
+      </c>
+      <c r="E55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>8</v>
+      </c>
+      <c r="H55">
+        <v>14</v>
+      </c>
+      <c r="I55">
+        <v>8</v>
+      </c>
+      <c r="J55">
+        <v>13</v>
+      </c>
+      <c r="K55">
+        <v>7</v>
+      </c>
+      <c r="L55">
+        <v>4</v>
+      </c>
+      <c r="M55">
+        <v>255</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="P55">
+        <v>2</v>
+      </c>
+      <c r="Q55">
+        <v>16</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56">
+        <v>5305</v>
+      </c>
+      <c r="C56">
+        <v>21</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>110</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>2</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>41</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="P56">
+        <v>1</v>
+      </c>
+      <c r="Q56">
+        <v>5</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57">
+        <v>5305</v>
+      </c>
+      <c r="C57">
+        <v>120</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>6</v>
+      </c>
+      <c r="H57">
+        <v>13</v>
+      </c>
+      <c r="I57">
+        <v>12</v>
+      </c>
+      <c r="J57">
+        <v>12</v>
+      </c>
+      <c r="K57">
+        <v>6</v>
+      </c>
+      <c r="L57">
+        <v>4</v>
+      </c>
+      <c r="M57">
+        <v>255</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57">
+        <v>2</v>
+      </c>
+      <c r="P57">
+        <v>2</v>
+      </c>
+      <c r="Q57">
+        <v>18</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58">
+        <v>1121</v>
+      </c>
+      <c r="C58">
+        <v>98</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>110</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>7</v>
+      </c>
+      <c r="H58">
+        <v>13</v>
+      </c>
+      <c r="I58">
+        <v>13</v>
+      </c>
+      <c r="J58">
+        <v>14</v>
+      </c>
+      <c r="K58">
+        <v>7</v>
+      </c>
+      <c r="L58">
+        <v>3</v>
+      </c>
+      <c r="M58">
+        <v>217</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58">
+        <v>2</v>
+      </c>
+      <c r="P58">
+        <v>2</v>
+      </c>
+      <c r="Q58">
+        <v>18</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59">
+        <v>5205</v>
+      </c>
+      <c r="C59">
+        <v>153</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>110</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>7</v>
+      </c>
+      <c r="H59">
+        <v>15</v>
+      </c>
+      <c r="I59">
+        <v>15</v>
+      </c>
+      <c r="J59">
+        <v>15</v>
+      </c>
+      <c r="K59">
+        <v>7</v>
+      </c>
+      <c r="L59">
+        <v>3</v>
+      </c>
+      <c r="M59">
+        <v>254</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <v>2</v>
+      </c>
+      <c r="P59">
+        <v>1</v>
+      </c>
+      <c r="Q59">
+        <v>14</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19">
+      <c r="A60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60">
+        <v>5111</v>
+      </c>
+      <c r="C60">
+        <v>41</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <v>67</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <v>1</v>
+      </c>
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="Q60">
+        <v>6</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61">
+        <v>5122</v>
+      </c>
+      <c r="C61">
+        <v>81</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>7</v>
+      </c>
+      <c r="H61">
+        <v>9</v>
+      </c>
+      <c r="I61">
+        <v>8</v>
+      </c>
+      <c r="J61">
+        <v>8</v>
+      </c>
+      <c r="K61">
+        <v>7</v>
+      </c>
+      <c r="L61">
+        <v>2</v>
+      </c>
+      <c r="M61">
+        <v>247</v>
+      </c>
+      <c r="N61">
+        <v>2</v>
+      </c>
+      <c r="O61">
+        <v>2</v>
+      </c>
+      <c r="P61">
+        <v>2</v>
+      </c>
+      <c r="Q61">
+        <v>17</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
+      <c r="A62" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62">
+        <v>5111</v>
+      </c>
+      <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
+        <v>113</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>1</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63">
+        <v>3314</v>
+      </c>
+      <c r="C63">
+        <v>107</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
+        <v>111</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>5</v>
+      </c>
+      <c r="H63">
+        <v>10</v>
+      </c>
+      <c r="I63">
+        <v>6</v>
+      </c>
+      <c r="J63">
+        <v>10</v>
+      </c>
+      <c r="K63">
+        <v>5</v>
+      </c>
+      <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
+        <v>184</v>
+      </c>
+      <c r="N63">
+        <v>2</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <v>14</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="A64" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64">
+        <v>5305</v>
+      </c>
+      <c r="C64">
+        <v>98</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>110</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>8</v>
+      </c>
+      <c r="H64">
+        <v>8</v>
+      </c>
+      <c r="I64">
+        <v>8</v>
+      </c>
+      <c r="J64">
+        <v>8</v>
+      </c>
+      <c r="K64">
+        <v>7</v>
+      </c>
+      <c r="L64">
+        <v>3</v>
+      </c>
+      <c r="M64">
+        <v>186</v>
+      </c>
+      <c r="N64">
+        <v>2</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+      <c r="P64">
+        <v>2</v>
+      </c>
+      <c r="Q64">
+        <v>20</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
+      <c r="A65" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65">
+        <v>5203</v>
+      </c>
+      <c r="C65">
+        <v>183</v>
+      </c>
+      <c r="D65">
+        <v>7.7</v>
+      </c>
+      <c r="E65" t="s">
+        <v>110</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>8</v>
+      </c>
+      <c r="H65">
+        <v>11</v>
+      </c>
+      <c r="I65">
+        <v>10</v>
+      </c>
+      <c r="J65">
+        <v>10</v>
+      </c>
+      <c r="K65">
+        <v>7</v>
+      </c>
+      <c r="L65">
+        <v>3</v>
+      </c>
+      <c r="M65">
+        <v>298</v>
+      </c>
+      <c r="N65">
+        <v>3</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>18</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66">
+        <v>5207</v>
+      </c>
+      <c r="C66">
+        <v>24</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>110</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>44</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="Q66">
+        <v>4</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67">
+        <v>5207</v>
+      </c>
+      <c r="C67">
+        <v>38</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>110</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>4</v>
+      </c>
+      <c r="I67">
+        <v>3</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+      <c r="K67">
+        <v>2</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>79</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67">
+        <v>5</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68">
+        <v>5105</v>
+      </c>
+      <c r="C68">
+        <v>87</v>
+      </c>
+      <c r="D68">
+        <v>6.54</v>
+      </c>
+      <c r="E68" t="s">
+        <v>113</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>5</v>
+      </c>
+      <c r="H68">
+        <v>10</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>9</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
+      </c>
+      <c r="L68">
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>155</v>
+      </c>
+      <c r="N68">
+        <v>2</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>1</v>
+      </c>
+      <c r="Q68">
+        <v>12</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69">
+        <v>5105</v>
+      </c>
+      <c r="C69">
+        <v>129</v>
+      </c>
+      <c r="D69">
+        <v>6.31</v>
+      </c>
+      <c r="E69" t="s">
+        <v>113</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>5</v>
+      </c>
+      <c r="H69">
+        <v>10</v>
+      </c>
+      <c r="I69">
+        <v>10</v>
+      </c>
+      <c r="J69">
+        <v>10</v>
+      </c>
+      <c r="K69">
+        <v>6</v>
+      </c>
+      <c r="L69">
+        <v>3</v>
+      </c>
+      <c r="M69">
+        <v>186</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>1</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
+      </c>
+      <c r="Q69">
+        <v>12</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70">
+        <v>5504</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+      <c r="D70">
+        <v>3.72</v>
+      </c>
+      <c r="E70" t="s">
+        <v>109</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="J70">
+        <v>6</v>
+      </c>
+      <c r="K70">
+        <v>3</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>109</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>1</v>
+      </c>
+      <c r="Q70">
+        <v>5</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71">
+        <v>2214</v>
+      </c>
+      <c r="C71">
+        <v>44</v>
+      </c>
+      <c r="D71">
+        <v>3.56</v>
+      </c>
+      <c r="E71" t="s">
+        <v>113</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71">
+        <v>6</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+      <c r="K71">
+        <v>4</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>134</v>
+      </c>
+      <c r="N71">
+        <v>2</v>
+      </c>
+      <c r="O71">
+        <v>1</v>
+      </c>
+      <c r="P71">
+        <v>2</v>
+      </c>
+      <c r="Q71">
+        <v>17</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="S71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72">
+        <v>2214</v>
+      </c>
+      <c r="C72">
+        <v>239</v>
+      </c>
+      <c r="D72">
+        <v>19.54</v>
+      </c>
+      <c r="E72" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>9</v>
+      </c>
+      <c r="H72">
+        <v>14</v>
+      </c>
+      <c r="I72">
+        <v>9</v>
+      </c>
+      <c r="J72">
+        <v>10</v>
+      </c>
+      <c r="K72">
+        <v>9</v>
+      </c>
+      <c r="L72">
+        <v>5</v>
+      </c>
+      <c r="M72">
+        <v>336</v>
+      </c>
+      <c r="N72">
+        <v>3</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>2</v>
+      </c>
+      <c r="Q72">
+        <v>24</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73">
+        <v>5409</v>
+      </c>
+      <c r="C73">
+        <v>42</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>113</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>5</v>
+      </c>
+      <c r="H73">
+        <v>5</v>
+      </c>
+      <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <v>5</v>
+      </c>
+      <c r="K73">
+        <v>4</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>153</v>
+      </c>
+      <c r="N73">
+        <v>3</v>
+      </c>
+      <c r="O73">
+        <v>1</v>
+      </c>
+      <c r="P73">
+        <v>2</v>
+      </c>
+      <c r="Q73">
+        <v>17</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="S73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74">
+        <v>3403</v>
+      </c>
+      <c r="C74">
+        <v>95</v>
+      </c>
+      <c r="D74">
+        <v>5.41</v>
+      </c>
+      <c r="E74" t="s">
+        <v>113</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>7</v>
+      </c>
+      <c r="H74">
+        <v>8</v>
+      </c>
+      <c r="I74">
+        <v>8</v>
+      </c>
+      <c r="J74">
+        <v>8</v>
+      </c>
+      <c r="K74">
+        <v>8</v>
+      </c>
+      <c r="L74">
+        <v>3</v>
+      </c>
+      <c r="M74">
+        <v>266</v>
+      </c>
+      <c r="N74">
+        <v>3</v>
+      </c>
+      <c r="O74">
+        <v>2</v>
+      </c>
+      <c r="P74">
+        <v>3</v>
+      </c>
+      <c r="Q74">
+        <v>20</v>
+      </c>
+      <c r="R74">
+        <v>1</v>
+      </c>
+      <c r="S74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75">
+        <v>4117</v>
+      </c>
+      <c r="C75">
+        <v>74</v>
+      </c>
+      <c r="D75">
+        <v>5.32</v>
+      </c>
+      <c r="E75" t="s">
+        <v>113</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>3</v>
+      </c>
+      <c r="H75">
+        <v>7</v>
+      </c>
+      <c r="I75">
+        <v>5</v>
+      </c>
+      <c r="J75">
+        <v>6</v>
+      </c>
+      <c r="K75">
+        <v>3</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>119</v>
+      </c>
+      <c r="N75">
+        <v>2</v>
+      </c>
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>7</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>5115</v>
+      </c>
+      <c r="C76">
+        <v>87</v>
+      </c>
+      <c r="D76">
+        <v>7.32</v>
+      </c>
+      <c r="E76" t="s">
+        <v>113</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+      <c r="H76">
+        <v>10</v>
+      </c>
+      <c r="I76">
+        <v>10</v>
+      </c>
+      <c r="J76">
+        <v>9</v>
+      </c>
+      <c r="K76">
+        <v>5</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>199</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76">
+        <v>2</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <v>12</v>
+      </c>
+      <c r="R76">
+        <v>1</v>
+      </c>
+      <c r="S76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>5202</v>
+      </c>
+      <c r="C77">
+        <v>211</v>
+      </c>
+      <c r="D77">
+        <v>13.1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>112</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>11</v>
+      </c>
+      <c r="H77">
+        <v>13</v>
+      </c>
+      <c r="I77">
+        <v>14</v>
+      </c>
+      <c r="J77">
+        <v>15</v>
+      </c>
+      <c r="K77">
+        <v>10</v>
+      </c>
+      <c r="L77">
+        <v>6</v>
+      </c>
+      <c r="M77">
+        <v>342</v>
+      </c>
+      <c r="N77">
+        <v>3</v>
+      </c>
+      <c r="O77">
+        <v>2</v>
+      </c>
+      <c r="P77">
+        <v>3</v>
+      </c>
+      <c r="Q77">
+        <v>24</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="S77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>3110</v>
+      </c>
+      <c r="C78">
+        <v>159</v>
+      </c>
+      <c r="D78">
+        <v>4.35</v>
+      </c>
+      <c r="E78" t="s">
+        <v>113</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>8</v>
+      </c>
+      <c r="H78">
+        <v>17</v>
+      </c>
+      <c r="I78">
+        <v>17</v>
+      </c>
+      <c r="J78">
+        <v>17</v>
+      </c>
+      <c r="K78">
+        <v>9</v>
+      </c>
+      <c r="L78">
+        <v>4</v>
+      </c>
+      <c r="M78">
+        <v>228</v>
+      </c>
+      <c r="N78">
+        <v>3</v>
+      </c>
+      <c r="O78">
+        <v>3</v>
+      </c>
+      <c r="P78">
+        <v>2</v>
+      </c>
+      <c r="Q78">
+        <v>20</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>4111</v>
+      </c>
+      <c r="C79">
+        <v>47</v>
+      </c>
+      <c r="D79">
+        <v>3.12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>113</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>5</v>
+      </c>
+      <c r="H79">
+        <v>10</v>
+      </c>
+      <c r="I79">
+        <v>7</v>
+      </c>
+      <c r="J79">
+        <v>5</v>
+      </c>
+      <c r="K79">
+        <v>5</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>104</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79">
+        <v>2</v>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>14</v>
+      </c>
+      <c r="R79">
+        <v>1</v>
+      </c>
+      <c r="S79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>4410</v>
+      </c>
+      <c r="C80">
+        <v>11</v>
+      </c>
+      <c r="D80">
+        <v>1.15</v>
+      </c>
+      <c r="E80" t="s">
+        <v>112</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>26</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>3</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>5601</v>
+      </c>
+      <c r="C81">
+        <v>132</v>
+      </c>
+      <c r="D81">
+        <v>4.68</v>
+      </c>
+      <c r="E81" t="s">
+        <v>112</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>6</v>
+      </c>
+      <c r="H81">
+        <v>11</v>
+      </c>
+      <c r="I81">
+        <v>9</v>
+      </c>
+      <c r="J81">
+        <v>10</v>
+      </c>
+      <c r="K81">
+        <v>7</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>183</v>
+      </c>
+      <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81">
+        <v>1</v>
+      </c>
+      <c r="P81">
+        <v>1</v>
+      </c>
+      <c r="Q81">
+        <v>17</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="S81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19">
+      <c r="A82" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>1135</v>
+      </c>
+      <c r="C82">
+        <v>24</v>
+      </c>
+      <c r="D82">
+        <v>0.85</v>
+      </c>
+      <c r="E82" t="s">
+        <v>119</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>4</v>
+      </c>
+      <c r="I82">
+        <v>4</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+      <c r="K82">
+        <v>2</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>46</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82">
+        <v>1</v>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>5</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19">
+      <c r="A83" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>5624</v>
+      </c>
+      <c r="C83">
+        <v>162</v>
+      </c>
+      <c r="D83">
+        <v>5.36</v>
+      </c>
+      <c r="E83" t="s">
+        <v>110</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>8</v>
+      </c>
+      <c r="H83">
+        <v>17</v>
+      </c>
+      <c r="I83">
+        <v>17</v>
+      </c>
+      <c r="J83">
+        <v>17</v>
+      </c>
+      <c r="K83">
+        <v>9</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>279</v>
+      </c>
+      <c r="N83">
+        <v>3</v>
+      </c>
+      <c r="O83">
+        <v>2</v>
+      </c>
+      <c r="P83">
+        <v>2</v>
+      </c>
+      <c r="Q83">
+        <v>20</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19">
+      <c r="A84" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>4317</v>
+      </c>
+      <c r="C84">
+        <v>95</v>
+      </c>
+      <c r="D84">
+        <v>3.64</v>
+      </c>
+      <c r="E84" t="s">
+        <v>110</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>5</v>
+      </c>
+      <c r="H84">
+        <v>9</v>
+      </c>
+      <c r="I84">
+        <v>6</v>
+      </c>
+      <c r="J84">
+        <v>8</v>
+      </c>
+      <c r="K84">
+        <v>5</v>
+      </c>
+      <c r="L84">
+        <v>3</v>
+      </c>
+      <c r="M84">
+        <v>132</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>1</v>
+      </c>
+      <c r="Q84">
+        <v>15</v>
+      </c>
+      <c r="R84">
+        <v>1</v>
+      </c>
+      <c r="S84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19">
+      <c r="A85" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85">
+        <v>1223</v>
+      </c>
+      <c r="C85">
+        <v>44</v>
+      </c>
+      <c r="D85">
+        <v>1.22</v>
+      </c>
+      <c r="E85" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
+        <v>6</v>
+      </c>
+      <c r="I85">
+        <v>5</v>
+      </c>
+      <c r="J85">
+        <v>4</v>
+      </c>
+      <c r="K85">
+        <v>3</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>88</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>5</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19">
+      <c r="A86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86">
+        <v>5621</v>
+      </c>
+      <c r="C86">
+        <v>157</v>
+      </c>
+      <c r="D86">
+        <v>7.13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>110</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>8</v>
+      </c>
+      <c r="H86">
+        <v>17</v>
+      </c>
+      <c r="I86">
+        <v>17</v>
+      </c>
+      <c r="J86">
+        <v>17</v>
+      </c>
+      <c r="K86">
+        <v>9</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>256</v>
+      </c>
+      <c r="N86">
+        <v>4</v>
+      </c>
+      <c r="O86">
+        <v>2</v>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>20</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
+      <c r="A87" t="s">
+        <v>83</v>
+      </c>
+      <c r="B87">
+        <v>3493</v>
+      </c>
+      <c r="C87">
+        <v>84</v>
+      </c>
+      <c r="D87">
+        <v>3.81</v>
+      </c>
+      <c r="E87" t="s">
+        <v>113</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>5</v>
+      </c>
+      <c r="H87">
+        <v>10</v>
+      </c>
+      <c r="I87">
+        <v>7</v>
+      </c>
+      <c r="J87">
+        <v>9</v>
+      </c>
+      <c r="K87">
+        <v>5</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>178</v>
+      </c>
+      <c r="N87">
+        <v>2</v>
+      </c>
+      <c r="O87">
+        <v>1</v>
+      </c>
+      <c r="P87">
+        <v>1</v>
+      </c>
+      <c r="Q87">
+        <v>15</v>
+      </c>
+      <c r="R87">
+        <v>1</v>
+      </c>
+      <c r="S87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" t="s">
+        <v>84</v>
+      </c>
+      <c r="B88">
+        <v>5458</v>
+      </c>
+      <c r="C88">
+        <v>214</v>
+      </c>
+      <c r="D88">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="E88" t="s">
+        <v>110</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>9</v>
+      </c>
+      <c r="H88">
+        <v>16</v>
+      </c>
+      <c r="I88">
+        <v>14</v>
+      </c>
+      <c r="J88">
+        <v>13</v>
+      </c>
+      <c r="K88">
+        <v>9</v>
+      </c>
+      <c r="L88">
+        <v>4</v>
+      </c>
+      <c r="M88">
+        <v>314</v>
+      </c>
+      <c r="N88">
+        <v>3</v>
+      </c>
+      <c r="O88">
+        <v>2</v>
+      </c>
+      <c r="P88">
+        <v>2</v>
+      </c>
+      <c r="Q88">
+        <v>21</v>
+      </c>
+      <c r="R88">
+        <v>1</v>
+      </c>
+      <c r="S88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="A89" t="s">
+        <v>85</v>
+      </c>
+      <c r="B89">
+        <v>5458</v>
+      </c>
+      <c r="C89">
+        <v>57</v>
+      </c>
+      <c r="D89">
+        <v>2.35</v>
+      </c>
+      <c r="E89" t="s">
+        <v>110</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>5</v>
+      </c>
+      <c r="H89">
+        <v>10</v>
+      </c>
+      <c r="I89">
+        <v>6</v>
+      </c>
+      <c r="J89">
+        <v>9</v>
+      </c>
+      <c r="K89">
+        <v>5</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <v>147</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89">
+        <v>2</v>
+      </c>
+      <c r="P89">
+        <v>3</v>
+      </c>
+      <c r="Q89">
+        <v>20</v>
+      </c>
+      <c r="R89">
+        <v>1</v>
+      </c>
+      <c r="S89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
+      <c r="A90" t="s">
+        <v>86</v>
+      </c>
+      <c r="B90">
+        <v>2220</v>
+      </c>
+      <c r="C90">
+        <v>140</v>
+      </c>
+      <c r="D90">
+        <v>6.36</v>
+      </c>
+      <c r="E90" t="s">
+        <v>110</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90">
+        <v>17</v>
+      </c>
+      <c r="I90">
+        <v>17</v>
+      </c>
+      <c r="J90">
+        <v>17</v>
+      </c>
+      <c r="K90">
+        <v>9</v>
+      </c>
+      <c r="L90">
+        <v>2</v>
+      </c>
+      <c r="M90">
+        <v>317</v>
+      </c>
+      <c r="N90">
+        <v>3</v>
+      </c>
+      <c r="O90">
+        <v>2</v>
+      </c>
+      <c r="P90">
+        <v>2</v>
+      </c>
+      <c r="Q90">
+        <v>20</v>
+      </c>
+      <c r="R90">
+        <v>1</v>
+      </c>
+      <c r="S90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="A91" t="s">
+        <v>87</v>
+      </c>
+      <c r="B91">
+        <v>2220</v>
+      </c>
+      <c r="C91">
+        <v>152</v>
+      </c>
+      <c r="D91">
+        <v>7.26</v>
+      </c>
+      <c r="E91" t="s">
+        <v>110</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>6</v>
+      </c>
+      <c r="H91">
+        <v>12</v>
+      </c>
+      <c r="I91">
+        <v>12</v>
+      </c>
+      <c r="J91">
+        <v>12</v>
+      </c>
+      <c r="K91">
+        <v>6</v>
+      </c>
+      <c r="L91">
+        <v>4</v>
+      </c>
+      <c r="M91">
+        <v>222</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
+      </c>
+      <c r="P91">
+        <v>2</v>
+      </c>
+      <c r="Q91">
+        <v>19</v>
+      </c>
+      <c r="R91">
+        <v>1</v>
+      </c>
+      <c r="S91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19">
+      <c r="A92" t="s">
+        <v>87</v>
+      </c>
+      <c r="B92">
+        <v>2403</v>
+      </c>
+      <c r="C92">
+        <v>40</v>
+      </c>
+      <c r="D92">
+        <v>1.02</v>
+      </c>
+      <c r="E92" t="s">
+        <v>112</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92">
+        <v>4</v>
+      </c>
+      <c r="I92">
+        <v>4</v>
+      </c>
+      <c r="J92">
+        <v>4</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>88</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92">
+        <v>1</v>
+      </c>
+      <c r="Q92">
+        <v>4</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19">
+      <c r="A93" t="s">
+        <v>88</v>
+      </c>
+      <c r="B93">
+        <v>2220</v>
+      </c>
+      <c r="C93">
+        <v>98</v>
+      </c>
+      <c r="D93">
+        <v>4.02</v>
+      </c>
+      <c r="E93" t="s">
+        <v>110</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93">
+        <v>9</v>
+      </c>
+      <c r="I93">
+        <v>8</v>
+      </c>
+      <c r="J93">
+        <v>8</v>
+      </c>
+      <c r="K93">
+        <v>4</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>164</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93">
+        <v>1</v>
+      </c>
+      <c r="P93">
+        <v>1</v>
+      </c>
+      <c r="Q93">
+        <v>12</v>
+      </c>
+      <c r="R93">
+        <v>1</v>
+      </c>
+      <c r="S93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19">
+      <c r="A94" t="s">
+        <v>88</v>
+      </c>
+      <c r="B94">
+        <v>5662</v>
+      </c>
+      <c r="C94">
+        <v>87</v>
+      </c>
+      <c r="D94">
+        <v>3.71</v>
+      </c>
+      <c r="E94" t="s">
+        <v>110</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>4</v>
+      </c>
+      <c r="H94">
+        <v>8</v>
+      </c>
+      <c r="I94">
+        <v>8</v>
+      </c>
+      <c r="J94">
+        <v>8</v>
+      </c>
+      <c r="K94">
+        <v>4</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>146</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94">
+        <v>2</v>
+      </c>
+      <c r="Q94">
+        <v>11</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19">
+      <c r="A95" t="s">
+        <v>89</v>
+      </c>
+      <c r="B95">
+        <v>2512</v>
+      </c>
+      <c r="C95">
+        <v>75</v>
+      </c>
+      <c r="D95">
+        <v>4.6</v>
+      </c>
+      <c r="E95" t="s">
+        <v>112</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>3</v>
+      </c>
+      <c r="H95">
+        <v>6</v>
+      </c>
+      <c r="I95">
+        <v>6</v>
+      </c>
+      <c r="J95">
+        <v>5</v>
+      </c>
+      <c r="K95">
+        <v>3</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>127</v>
+      </c>
+      <c r="N95">
+        <v>2</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="P95">
+        <v>1</v>
+      </c>
+      <c r="Q95">
+        <v>7</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19">
+      <c r="A96" t="s">
+        <v>90</v>
+      </c>
+      <c r="B96">
+        <v>2514</v>
+      </c>
+      <c r="C96">
+        <v>170</v>
+      </c>
+      <c r="D96">
+        <v>16.21</v>
+      </c>
+      <c r="E96" t="s">
+        <v>112</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>9</v>
+      </c>
+      <c r="H96">
+        <v>16</v>
+      </c>
+      <c r="I96">
+        <v>14</v>
+      </c>
+      <c r="J96">
+        <v>14</v>
+      </c>
+      <c r="K96">
+        <v>8</v>
+      </c>
+      <c r="L96">
+        <v>5</v>
+      </c>
+      <c r="M96">
+        <v>300</v>
+      </c>
+      <c r="N96">
+        <v>3</v>
+      </c>
+      <c r="O96">
+        <v>2</v>
+      </c>
+      <c r="P96">
+        <v>3</v>
+      </c>
+      <c r="Q96">
+        <v>22</v>
+      </c>
+      <c r="R96">
+        <v>1</v>
+      </c>
+      <c r="S96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
+      <c r="A97" t="s">
+        <v>91</v>
+      </c>
+      <c r="B97">
+        <v>3106</v>
+      </c>
+      <c r="C97">
+        <v>40</v>
+      </c>
+      <c r="D97">
+        <v>3.12</v>
+      </c>
+      <c r="E97" t="s">
+        <v>113</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>4</v>
+      </c>
+      <c r="H97">
+        <v>5</v>
+      </c>
+      <c r="I97">
+        <v>5</v>
+      </c>
+      <c r="J97">
+        <v>5</v>
+      </c>
+      <c r="K97">
+        <v>5</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>114</v>
+      </c>
+      <c r="N97">
+        <v>3</v>
+      </c>
+      <c r="O97">
+        <v>2</v>
+      </c>
+      <c r="P97">
+        <v>1</v>
+      </c>
+      <c r="Q97">
+        <v>18</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="S97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" t="s">
+        <v>91</v>
+      </c>
+      <c r="B98">
+        <v>5663</v>
+      </c>
+      <c r="C98">
+        <v>5</v>
+      </c>
+      <c r="D98">
+        <v>0.03</v>
+      </c>
+      <c r="E98" t="s">
+        <v>110</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>25</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>1</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99">
+        <v>5661</v>
+      </c>
+      <c r="C99">
+        <v>87</v>
+      </c>
+      <c r="D99">
+        <v>4.23</v>
+      </c>
+      <c r="E99" t="s">
+        <v>110</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>6</v>
+      </c>
+      <c r="H99">
+        <v>13</v>
+      </c>
+      <c r="I99">
+        <v>10</v>
+      </c>
+      <c r="J99">
+        <v>10</v>
+      </c>
+      <c r="K99">
+        <v>6</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>196</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99">
+        <v>2</v>
+      </c>
+      <c r="P99">
+        <v>3</v>
+      </c>
+      <c r="Q99">
+        <v>17</v>
+      </c>
+      <c r="R99">
+        <v>1</v>
+      </c>
+      <c r="S99">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="A100" t="s">
+        <v>92</v>
+      </c>
+      <c r="B100">
+        <v>4240</v>
+      </c>
+      <c r="C100">
+        <v>38</v>
+      </c>
+      <c r="D100">
+        <v>2.72</v>
+      </c>
+      <c r="E100" t="s">
+        <v>112</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100">
+        <v>4</v>
+      </c>
+      <c r="I100">
+        <v>4</v>
+      </c>
+      <c r="J100">
+        <v>4</v>
+      </c>
+      <c r="K100">
+        <v>2</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>71</v>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>1</v>
+      </c>
+      <c r="Q100">
+        <v>6</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101">
+        <v>5664</v>
+      </c>
+      <c r="C101">
+        <v>116</v>
+      </c>
+      <c r="D101">
+        <v>9.32</v>
+      </c>
+      <c r="E101" t="s">
+        <v>110</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>7</v>
+      </c>
+      <c r="H101">
+        <v>13</v>
+      </c>
+      <c r="I101">
+        <v>9</v>
+      </c>
+      <c r="J101">
+        <v>10</v>
+      </c>
+      <c r="K101">
+        <v>7</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>226</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101">
+        <v>2</v>
+      </c>
+      <c r="P101">
+        <v>2</v>
+      </c>
+      <c r="Q101">
+        <v>17</v>
+      </c>
+      <c r="R101">
+        <v>1</v>
+      </c>
+      <c r="S101">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" t="s">
+        <v>94</v>
+      </c>
+      <c r="B102">
+        <v>5663</v>
+      </c>
+      <c r="C102">
+        <v>146</v>
+      </c>
+      <c r="D102">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="E102" t="s">
+        <v>110</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>9</v>
+      </c>
+      <c r="H102">
+        <v>13</v>
+      </c>
+      <c r="I102">
+        <v>9</v>
+      </c>
+      <c r="J102">
+        <v>10</v>
+      </c>
+      <c r="K102">
+        <v>8</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>294</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102">
+        <v>2</v>
+      </c>
+      <c r="P102">
+        <v>2</v>
+      </c>
+      <c r="Q102">
+        <v>21</v>
+      </c>
+      <c r="R102">
+        <v>1</v>
+      </c>
+      <c r="S102">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" t="s">
+        <v>95</v>
+      </c>
+      <c r="B103">
+        <v>5208</v>
+      </c>
+      <c r="C103">
+        <v>89</v>
+      </c>
+      <c r="D103">
+        <v>5.07</v>
+      </c>
+      <c r="E103" t="s">
+        <v>121</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>6</v>
+      </c>
+      <c r="H103">
+        <v>7</v>
+      </c>
+      <c r="I103">
+        <v>7</v>
+      </c>
+      <c r="J103">
+        <v>7</v>
+      </c>
+      <c r="K103">
+        <v>6</v>
+      </c>
+      <c r="L103">
+        <v>2</v>
+      </c>
+      <c r="M103">
+        <v>214</v>
+      </c>
+      <c r="N103">
+        <v>2</v>
+      </c>
+      <c r="O103">
+        <v>1</v>
+      </c>
+      <c r="P103">
+        <v>1</v>
+      </c>
+      <c r="Q103">
+        <v>20</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" t="s">
+        <v>95</v>
+      </c>
+      <c r="B104">
+        <v>4241</v>
+      </c>
+      <c r="C104">
+        <v>24</v>
+      </c>
+      <c r="D104">
+        <v>1.27</v>
+      </c>
+      <c r="E104" t="s">
+        <v>112</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>2</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>25</v>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104">
+        <v>1</v>
+      </c>
+      <c r="P104">
+        <v>1</v>
+      </c>
+      <c r="Q104">
+        <v>3</v>
+      </c>
+      <c r="R104">
+        <v>1</v>
+      </c>
+      <c r="S104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" t="s">
+        <v>96</v>
+      </c>
+      <c r="B105">
+        <v>4241</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105">
+        <v>0.05</v>
+      </c>
+      <c r="E105" t="s">
+        <v>112</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>3</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+      <c r="S105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" t="s">
+        <v>97</v>
+      </c>
+      <c r="B106">
+        <v>1107</v>
+      </c>
+      <c r="C106">
+        <v>162</v>
+      </c>
+      <c r="D106">
+        <v>6.75</v>
+      </c>
+      <c r="E106" t="s">
+        <v>113</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106">
+        <v>8</v>
+      </c>
+      <c r="H106">
+        <v>15</v>
+      </c>
+      <c r="I106">
+        <v>10</v>
+      </c>
+      <c r="J106">
+        <v>12</v>
+      </c>
+      <c r="K106">
+        <v>8</v>
+      </c>
+      <c r="L106">
+        <v>3</v>
+      </c>
+      <c r="M106">
+        <v>324</v>
+      </c>
+      <c r="N106">
+        <v>4</v>
+      </c>
+      <c r="O106">
+        <v>2</v>
+      </c>
+      <c r="P106">
+        <v>2</v>
+      </c>
+      <c r="Q106">
+        <v>22</v>
+      </c>
+      <c r="R106">
+        <v>1</v>
+      </c>
+      <c r="S106">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" t="s">
+        <v>98</v>
+      </c>
+      <c r="B107">
+        <v>4412</v>
+      </c>
+      <c r="C107">
+        <v>123</v>
+      </c>
+      <c r="D107">
+        <v>5.39</v>
+      </c>
+      <c r="E107" t="s">
+        <v>113</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>9</v>
+      </c>
+      <c r="H107">
+        <v>9</v>
+      </c>
+      <c r="I107">
+        <v>9</v>
+      </c>
+      <c r="J107">
+        <v>9</v>
+      </c>
+      <c r="K107">
+        <v>8</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>293</v>
+      </c>
+      <c r="N107">
+        <v>4</v>
+      </c>
+      <c r="O107">
+        <v>2</v>
+      </c>
+      <c r="P107">
+        <v>2</v>
+      </c>
+      <c r="Q107">
+        <v>21</v>
+      </c>
+      <c r="R107">
+        <v>1</v>
+      </c>
+      <c r="S107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" t="s">
+        <v>99</v>
+      </c>
+      <c r="B108">
+        <v>5441</v>
+      </c>
+      <c r="C108">
         <v>56</v>
       </c>
-      <c r="O28" t="s">
-        <v>58</v>
-      </c>
-      <c r="P28" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>59</v>
-      </c>
-      <c r="R28" t="s">
-        <v>52</v>
-      </c>
-      <c r="S28" t="s">
-        <v>60</v>
+      <c r="D108">
+        <v>2.66</v>
+      </c>
+      <c r="E108" t="s">
+        <v>113</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>6</v>
+      </c>
+      <c r="H108">
+        <v>5</v>
+      </c>
+      <c r="I108">
+        <v>6</v>
+      </c>
+      <c r="J108">
+        <v>5</v>
+      </c>
+      <c r="K108">
+        <v>6</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>163</v>
+      </c>
+      <c r="N108">
+        <v>3</v>
+      </c>
+      <c r="O108">
+        <v>2</v>
+      </c>
+      <c r="P108">
+        <v>2</v>
+      </c>
+      <c r="Q108">
+        <v>20</v>
+      </c>
+      <c r="R108">
+        <v>1</v>
+      </c>
+      <c r="S108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" t="s">
+        <v>100</v>
+      </c>
+      <c r="B109">
+        <v>5440</v>
+      </c>
+      <c r="C109">
+        <v>226</v>
+      </c>
+      <c r="D109">
+        <v>22.78</v>
+      </c>
+      <c r="E109" t="s">
+        <v>119</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109">
+        <v>9</v>
+      </c>
+      <c r="H109">
+        <v>17</v>
+      </c>
+      <c r="I109">
+        <v>17</v>
+      </c>
+      <c r="J109">
+        <v>17</v>
+      </c>
+      <c r="K109">
+        <v>8</v>
+      </c>
+      <c r="L109">
+        <v>5</v>
+      </c>
+      <c r="M109">
+        <v>343</v>
+      </c>
+      <c r="N109">
+        <v>4</v>
+      </c>
+      <c r="O109">
+        <v>2</v>
+      </c>
+      <c r="P109">
+        <v>2</v>
+      </c>
+      <c r="Q109">
+        <v>21</v>
+      </c>
+      <c r="R109">
+        <v>1</v>
+      </c>
+      <c r="S109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="A110" t="s">
+        <v>101</v>
+      </c>
+      <c r="B110">
+        <v>3115</v>
+      </c>
+      <c r="C110">
+        <v>199</v>
+      </c>
+      <c r="D110">
+        <v>12.71</v>
+      </c>
+      <c r="E110" t="s">
+        <v>110</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>8</v>
+      </c>
+      <c r="H110">
+        <v>17</v>
+      </c>
+      <c r="I110">
+        <v>17</v>
+      </c>
+      <c r="J110">
+        <v>17</v>
+      </c>
+      <c r="K110">
+        <v>9</v>
+      </c>
+      <c r="L110">
+        <v>5</v>
+      </c>
+      <c r="M110">
+        <v>313</v>
+      </c>
+      <c r="N110">
+        <v>3</v>
+      </c>
+      <c r="O110">
+        <v>2</v>
+      </c>
+      <c r="P110">
+        <v>2</v>
+      </c>
+      <c r="Q110">
+        <v>20</v>
+      </c>
+      <c r="R110">
+        <v>1</v>
+      </c>
+      <c r="S110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" t="s">
+        <v>102</v>
+      </c>
+      <c r="B111">
+        <v>4129</v>
+      </c>
+      <c r="C111">
+        <v>169</v>
+      </c>
+      <c r="D111">
+        <v>5.35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>110</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>8</v>
+      </c>
+      <c r="H111">
+        <v>17</v>
+      </c>
+      <c r="I111">
+        <v>17</v>
+      </c>
+      <c r="J111">
+        <v>17</v>
+      </c>
+      <c r="K111">
+        <v>9</v>
+      </c>
+      <c r="L111">
+        <v>3</v>
+      </c>
+      <c r="M111">
+        <v>308</v>
+      </c>
+      <c r="N111">
+        <v>5</v>
+      </c>
+      <c r="O111">
+        <v>3</v>
+      </c>
+      <c r="P111">
+        <v>3</v>
+      </c>
+      <c r="Q111">
+        <v>20</v>
+      </c>
+      <c r="R111">
+        <v>1</v>
+      </c>
+      <c r="S111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="A112" t="s">
+        <v>103</v>
+      </c>
+      <c r="B112">
+        <v>3317</v>
+      </c>
+      <c r="C112">
+        <v>208</v>
+      </c>
+      <c r="D112">
+        <v>16.98</v>
+      </c>
+      <c r="E112" t="s">
+        <v>119</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>8</v>
+      </c>
+      <c r="H112">
+        <v>17</v>
+      </c>
+      <c r="I112">
+        <v>17</v>
+      </c>
+      <c r="J112">
+        <v>17</v>
+      </c>
+      <c r="K112">
+        <v>9</v>
+      </c>
+      <c r="L112">
+        <v>4</v>
+      </c>
+      <c r="M112">
+        <v>324</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112">
+        <v>2</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+      <c r="Q112">
+        <v>20</v>
+      </c>
+      <c r="R112">
+        <v>1</v>
+      </c>
+      <c r="S112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
+      <c r="A113" t="s">
+        <v>104</v>
+      </c>
+      <c r="B113">
+        <v>1215</v>
+      </c>
+      <c r="C113">
+        <v>153</v>
+      </c>
+      <c r="D113">
+        <v>6.32</v>
+      </c>
+      <c r="E113" t="s">
+        <v>119</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113">
+        <v>6</v>
+      </c>
+      <c r="H113">
+        <v>12</v>
+      </c>
+      <c r="I113">
+        <v>13</v>
+      </c>
+      <c r="J113">
+        <v>12</v>
+      </c>
+      <c r="K113">
+        <v>6</v>
+      </c>
+      <c r="L113">
+        <v>3</v>
+      </c>
+      <c r="M113">
+        <v>238</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113">
+        <v>1</v>
+      </c>
+      <c r="P113">
+        <v>1</v>
+      </c>
+      <c r="Q113">
+        <v>7</v>
+      </c>
+      <c r="R113">
+        <v>1</v>
+      </c>
+      <c r="S113">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
+      <c r="A114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B114">
+        <v>4239</v>
+      </c>
+      <c r="C114">
+        <v>40</v>
+      </c>
+      <c r="D114">
+        <v>3.35</v>
+      </c>
+      <c r="E114" t="s">
+        <v>122</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>2</v>
+      </c>
+      <c r="H114">
+        <v>5</v>
+      </c>
+      <c r="I114">
+        <v>4</v>
+      </c>
+      <c r="J114">
+        <v>4</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>65</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114">
+        <v>1</v>
+      </c>
+      <c r="P114">
+        <v>1</v>
+      </c>
+      <c r="Q114">
+        <v>3</v>
+      </c>
+      <c r="R114">
+        <v>0</v>
+      </c>
+      <c r="S114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
+      <c r="A115" t="s">
+        <v>105</v>
+      </c>
+      <c r="B115" t="s">
+        <v>106</v>
+      </c>
+      <c r="C115" t="s">
+        <v>107</v>
+      </c>
+      <c r="D115" t="s">
+        <v>108</v>
+      </c>
+      <c r="E115" t="s">
+        <v>122</v>
+      </c>
+      <c r="F115" t="s">
+        <v>123</v>
+      </c>
+      <c r="G115" t="s">
+        <v>124</v>
+      </c>
+      <c r="H115" t="s">
+        <v>124</v>
+      </c>
+      <c r="I115" t="s">
+        <v>125</v>
+      </c>
+      <c r="J115" t="s">
+        <v>125</v>
+      </c>
+      <c r="K115" t="s">
+        <v>124</v>
+      </c>
+      <c r="L115" t="s">
+        <v>124</v>
+      </c>
+      <c r="M115" t="s">
+        <v>126</v>
+      </c>
+      <c r="N115" t="s">
+        <v>124</v>
+      </c>
+      <c r="O115" t="s">
+        <v>123</v>
+      </c>
+      <c r="P115" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>125</v>
+      </c>
+      <c r="R115" t="s">
+        <v>123</v>
+      </c>
+      <c r="S115" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="170">
   <si>
     <t>Date</t>
   </si>
@@ -334,67 +334,196 @@
     <t>2025-08-20</t>
   </si>
   <si>
-    <t>4239</t>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-08-29</t>
+  </si>
+  <si>
+    <t>2025-08-30</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>2025-09-06</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>5701C</t>
+  </si>
+  <si>
+    <t>5292</t>
+  </si>
+  <si>
+    <t>3122</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>5702</t>
+  </si>
+  <si>
+    <t>4212</t>
+  </si>
+  <si>
+    <t>2319</t>
+  </si>
+  <si>
+    <t>4291</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
+    <t>5406</t>
+  </si>
+  <si>
+    <t>5130</t>
+  </si>
+  <si>
+    <t>2516</t>
+  </si>
+  <si>
+    <t>5501</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>5507</t>
+  </si>
+  <si>
+    <t>4230</t>
+  </si>
+  <si>
+    <t>4228</t>
+  </si>
+  <si>
+    <t>5106</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>13.64</t>
+  </si>
+  <si>
+    <t>N14</t>
+  </si>
+  <si>
+    <t>R579</t>
+  </si>
+  <si>
+    <t>N41</t>
+  </si>
+  <si>
+    <t>R570</t>
+  </si>
+  <si>
+    <t>97F1692</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>MN1</t>
+  </si>
+  <si>
+    <t>N23</t>
+  </si>
+  <si>
+    <t>N36</t>
+  </si>
+  <si>
+    <t>N25</t>
+  </si>
+  <si>
+    <t>MIX</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>CO62175</t>
+  </si>
+  <si>
+    <t>90F0613</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>N14</t>
-  </si>
-  <si>
-    <t>R579</t>
-  </si>
-  <si>
-    <t>N41</t>
-  </si>
-  <si>
-    <t>R570</t>
-  </si>
-  <si>
-    <t>97F1692</t>
-  </si>
-  <si>
-    <t>XX</t>
-  </si>
-  <si>
-    <t>MN1</t>
-  </si>
-  <si>
-    <t>N23</t>
-  </si>
-  <si>
-    <t>N36</t>
-  </si>
-  <si>
-    <t>N25</t>
-  </si>
-  <si>
-    <t>MIX</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>CO62175</t>
-  </si>
-  <si>
-    <t>90F0613</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
 </sst>
 </file>
@@ -752,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -828,7 +957,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -887,7 +1016,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -946,7 +1075,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1005,7 +1134,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1064,7 +1193,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1123,7 +1252,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1182,7 +1311,7 @@
         <v>18.6</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1241,7 +1370,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1300,7 +1429,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1359,7 +1488,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1418,7 +1547,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1477,7 +1606,7 @@
         <v>4.6</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1536,7 +1665,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1595,7 +1724,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1654,7 +1783,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1713,7 +1842,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1772,7 +1901,7 @@
         <v>2.3</v>
       </c>
       <c r="E18" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1831,7 +1960,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1890,7 +2019,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1949,7 +2078,7 @@
         <v>4.4</v>
       </c>
       <c r="E21" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2008,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2067,7 +2196,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2126,7 +2255,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2185,7 +2314,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2244,7 +2373,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2303,7 +2432,7 @@
         <v>4.06</v>
       </c>
       <c r="E27" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2362,7 +2491,7 @@
         <v>7.95</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2421,7 +2550,7 @@
         <v>2.2</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2480,7 +2609,7 @@
         <v>3.27</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2539,7 +2668,7 @@
         <v>8.31</v>
       </c>
       <c r="E31" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2598,7 +2727,7 @@
         <v>3.59</v>
       </c>
       <c r="E32" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2657,7 +2786,7 @@
         <v>2.13</v>
       </c>
       <c r="E33" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2716,7 +2845,7 @@
         <v>4.8</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -2775,7 +2904,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2834,7 +2963,7 @@
         <v>6.45</v>
       </c>
       <c r="E36" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -2893,7 +3022,7 @@
         <v>4.72</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -2952,7 +3081,7 @@
         <v>1.8</v>
       </c>
       <c r="E38" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3011,7 +3140,7 @@
         <v>5.86</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3070,7 +3199,7 @@
         <v>6.18</v>
       </c>
       <c r="E40" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3129,7 +3258,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3188,7 +3317,7 @@
         <v>7.13</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3247,7 +3376,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3306,7 +3435,7 @@
         <v>5.81</v>
       </c>
       <c r="E44" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3365,7 +3494,7 @@
         <v>4.09</v>
       </c>
       <c r="E45" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3424,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3483,7 +3612,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3542,7 +3671,7 @@
         <v>5.13</v>
       </c>
       <c r="E48" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3601,7 +3730,7 @@
         <v>1.81</v>
       </c>
       <c r="E49" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -3660,7 +3789,7 @@
         <v>7.95</v>
       </c>
       <c r="E50" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -3719,7 +3848,7 @@
         <v>0.64</v>
       </c>
       <c r="E51" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -3778,7 +3907,7 @@
         <v>6.13</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3837,7 +3966,7 @@
         <v>2.77</v>
       </c>
       <c r="E53" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3896,7 +4025,7 @@
         <v>4.35</v>
       </c>
       <c r="E54" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -3955,7 +4084,7 @@
         <v>5.24</v>
       </c>
       <c r="E55" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4014,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4073,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4132,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4191,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4250,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4309,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4368,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4427,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4486,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4545,7 +4674,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4604,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4663,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4722,7 +4851,7 @@
         <v>6.54</v>
       </c>
       <c r="E68" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4781,7 +4910,7 @@
         <v>6.31</v>
       </c>
       <c r="E69" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4840,7 +4969,7 @@
         <v>3.72</v>
       </c>
       <c r="E70" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4899,7 +5028,7 @@
         <v>3.56</v>
       </c>
       <c r="E71" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -4958,7 +5087,7 @@
         <v>19.54</v>
       </c>
       <c r="E72" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5017,7 +5146,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5076,7 +5205,7 @@
         <v>5.41</v>
       </c>
       <c r="E74" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5135,7 +5264,7 @@
         <v>5.32</v>
       </c>
       <c r="E75" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5194,7 +5323,7 @@
         <v>7.32</v>
       </c>
       <c r="E76" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5253,7 +5382,7 @@
         <v>13.1</v>
       </c>
       <c r="E77" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5312,7 +5441,7 @@
         <v>4.35</v>
       </c>
       <c r="E78" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5371,7 +5500,7 @@
         <v>3.12</v>
       </c>
       <c r="E79" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5430,7 +5559,7 @@
         <v>1.15</v>
       </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5489,7 +5618,7 @@
         <v>4.68</v>
       </c>
       <c r="E81" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5548,7 +5677,7 @@
         <v>0.85</v>
       </c>
       <c r="E82" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -5607,7 +5736,7 @@
         <v>5.36</v>
       </c>
       <c r="E83" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -5666,7 +5795,7 @@
         <v>3.64</v>
       </c>
       <c r="E84" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -5725,7 +5854,7 @@
         <v>1.22</v>
       </c>
       <c r="E85" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5784,7 +5913,7 @@
         <v>7.13</v>
       </c>
       <c r="E86" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -5843,7 +5972,7 @@
         <v>3.81</v>
       </c>
       <c r="E87" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -5902,7 +6031,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E88" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -5961,7 +6090,7 @@
         <v>2.35</v>
       </c>
       <c r="E89" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -6020,7 +6149,7 @@
         <v>6.36</v>
       </c>
       <c r="E90" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6079,7 +6208,7 @@
         <v>7.26</v>
       </c>
       <c r="E91" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -6138,7 +6267,7 @@
         <v>1.02</v>
       </c>
       <c r="E92" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6197,7 +6326,7 @@
         <v>4.02</v>
       </c>
       <c r="E93" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -6256,7 +6385,7 @@
         <v>3.71</v>
       </c>
       <c r="E94" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6315,7 +6444,7 @@
         <v>4.6</v>
       </c>
       <c r="E95" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6374,7 +6503,7 @@
         <v>16.21</v>
       </c>
       <c r="E96" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -6433,7 +6562,7 @@
         <v>3.12</v>
       </c>
       <c r="E97" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6492,7 +6621,7 @@
         <v>0.03</v>
       </c>
       <c r="E98" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -6551,7 +6680,7 @@
         <v>4.23</v>
       </c>
       <c r="E99" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -6610,7 +6739,7 @@
         <v>2.72</v>
       </c>
       <c r="E100" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -6669,7 +6798,7 @@
         <v>9.32</v>
       </c>
       <c r="E101" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -6728,7 +6857,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="E102" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -6787,7 +6916,7 @@
         <v>5.07</v>
       </c>
       <c r="E103" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -6846,7 +6975,7 @@
         <v>1.27</v>
       </c>
       <c r="E104" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -6905,7 +7034,7 @@
         <v>0.05</v>
       </c>
       <c r="E105" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -6964,7 +7093,7 @@
         <v>6.75</v>
       </c>
       <c r="E106" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -7023,7 +7152,7 @@
         <v>5.39</v>
       </c>
       <c r="E107" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -7082,7 +7211,7 @@
         <v>2.66</v>
       </c>
       <c r="E108" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -7141,7 +7270,7 @@
         <v>22.78</v>
       </c>
       <c r="E109" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7200,7 +7329,7 @@
         <v>12.71</v>
       </c>
       <c r="E110" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -7259,7 +7388,7 @@
         <v>5.35</v>
       </c>
       <c r="E111" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -7318,7 +7447,7 @@
         <v>16.98</v>
       </c>
       <c r="E112" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -7377,7 +7506,7 @@
         <v>6.32</v>
       </c>
       <c r="E113" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -7436,7 +7565,7 @@
         <v>3.35</v>
       </c>
       <c r="E114" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7485,59 +7614,1534 @@
       <c r="A115" t="s">
         <v>105</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115">
+        <v>4239</v>
+      </c>
+      <c r="C115">
+        <v>8</v>
+      </c>
+      <c r="D115">
+        <v>0.24</v>
+      </c>
+      <c r="E115" t="s">
+        <v>159</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>19</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>2</v>
+      </c>
+      <c r="R115">
+        <v>0</v>
+      </c>
+      <c r="S115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
+      <c r="A116" t="s">
         <v>106</v>
       </c>
-      <c r="C115" t="s">
+      <c r="B116">
+        <v>4209</v>
+      </c>
+      <c r="C116">
+        <v>68</v>
+      </c>
+      <c r="D116">
+        <v>4.32</v>
+      </c>
+      <c r="E116" t="s">
+        <v>147</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>6</v>
+      </c>
+      <c r="H116">
+        <v>6</v>
+      </c>
+      <c r="I116">
+        <v>7</v>
+      </c>
+      <c r="J116">
+        <v>7</v>
+      </c>
+      <c r="K116">
+        <v>6</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>186</v>
+      </c>
+      <c r="N116">
+        <v>2</v>
+      </c>
+      <c r="O116">
+        <v>2</v>
+      </c>
+      <c r="P116">
+        <v>1</v>
+      </c>
+      <c r="Q116">
+        <v>6</v>
+      </c>
+      <c r="R116">
+        <v>1</v>
+      </c>
+      <c r="S116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" t="s">
         <v>107</v>
       </c>
-      <c r="D115" t="s">
+      <c r="B117" t="s">
+        <v>125</v>
+      </c>
+      <c r="C117">
+        <v>132</v>
+      </c>
+      <c r="D117">
+        <v>9.23</v>
+      </c>
+      <c r="E117" t="s">
+        <v>147</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>7</v>
+      </c>
+      <c r="H117">
+        <v>15</v>
+      </c>
+      <c r="I117">
+        <v>15</v>
+      </c>
+      <c r="J117">
+        <v>15</v>
+      </c>
+      <c r="K117">
+        <v>7</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>224</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117">
+        <v>3</v>
+      </c>
+      <c r="P117">
+        <v>1</v>
+      </c>
+      <c r="Q117">
+        <v>15</v>
+      </c>
+      <c r="R117">
+        <v>1</v>
+      </c>
+      <c r="S117">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19">
+      <c r="A118" t="s">
+        <v>107</v>
+      </c>
+      <c r="B118" t="s">
+        <v>126</v>
+      </c>
+      <c r="C118">
+        <v>22</v>
+      </c>
+      <c r="D118">
+        <v>2.65</v>
+      </c>
+      <c r="E118" t="s">
+        <v>149</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>2</v>
+      </c>
+      <c r="I118">
+        <v>2</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>35</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118">
+        <v>1</v>
+      </c>
+      <c r="P118">
+        <v>1</v>
+      </c>
+      <c r="Q118">
+        <v>3</v>
+      </c>
+      <c r="R118">
+        <v>0</v>
+      </c>
+      <c r="S118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
+      <c r="A119" t="s">
         <v>108</v>
       </c>
-      <c r="E115" t="s">
+      <c r="B119" t="s">
+        <v>127</v>
+      </c>
+      <c r="C119">
+        <v>178</v>
+      </c>
+      <c r="D119">
+        <v>13.54</v>
+      </c>
+      <c r="E119" t="s">
+        <v>147</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>8</v>
+      </c>
+      <c r="H119">
+        <v>17</v>
+      </c>
+      <c r="I119">
+        <v>17</v>
+      </c>
+      <c r="J119">
+        <v>17</v>
+      </c>
+      <c r="K119">
+        <v>9</v>
+      </c>
+      <c r="L119">
+        <v>4</v>
+      </c>
+      <c r="M119">
+        <v>245</v>
+      </c>
+      <c r="N119">
+        <v>4</v>
+      </c>
+      <c r="O119">
+        <v>2</v>
+      </c>
+      <c r="P119">
+        <v>2</v>
+      </c>
+      <c r="Q119">
+        <v>20</v>
+      </c>
+      <c r="R119">
+        <v>1</v>
+      </c>
+      <c r="S119">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19">
+      <c r="A120" t="s">
+        <v>108</v>
+      </c>
+      <c r="B120" t="s">
+        <v>126</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>0.04</v>
+      </c>
+      <c r="E120" t="s">
+        <v>147</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+      <c r="S120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
+      <c r="A121" t="s">
+        <v>109</v>
+      </c>
+      <c r="B121" t="s">
+        <v>128</v>
+      </c>
+      <c r="C121">
+        <v>31</v>
+      </c>
+      <c r="D121">
+        <v>2.5</v>
+      </c>
+      <c r="E121" t="s">
+        <v>147</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>4</v>
+      </c>
+      <c r="H121">
+        <v>4</v>
+      </c>
+      <c r="I121">
+        <v>4</v>
+      </c>
+      <c r="J121">
+        <v>4</v>
+      </c>
+      <c r="K121">
+        <v>3</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>91</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121">
+        <v>3</v>
+      </c>
+      <c r="P121">
+        <v>2</v>
+      </c>
+      <c r="Q121">
+        <v>20</v>
+      </c>
+      <c r="R121">
+        <v>1</v>
+      </c>
+      <c r="S121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
+      <c r="A122" t="s">
+        <v>110</v>
+      </c>
+      <c r="B122" t="s">
+        <v>129</v>
+      </c>
+      <c r="C122">
+        <v>29</v>
+      </c>
+      <c r="D122">
+        <v>1.65</v>
+      </c>
+      <c r="E122" t="s">
+        <v>147</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>3</v>
+      </c>
+      <c r="H122">
+        <v>3</v>
+      </c>
+      <c r="I122">
+        <v>3</v>
+      </c>
+      <c r="J122">
+        <v>3</v>
+      </c>
+      <c r="K122">
+        <v>3</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>93</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122">
+        <v>1</v>
+      </c>
+      <c r="P122">
+        <v>2</v>
+      </c>
+      <c r="Q122">
+        <v>21</v>
+      </c>
+      <c r="R122">
+        <v>1</v>
+      </c>
+      <c r="S122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19">
+      <c r="A123" t="s">
+        <v>111</v>
+      </c>
+      <c r="B123" t="s">
+        <v>126</v>
+      </c>
+      <c r="C123">
+        <v>219</v>
+      </c>
+      <c r="D123">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="s">
+        <v>147</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>8</v>
+      </c>
+      <c r="H123">
+        <v>17</v>
+      </c>
+      <c r="I123">
+        <v>17</v>
+      </c>
+      <c r="J123">
+        <v>17</v>
+      </c>
+      <c r="K123">
+        <v>9</v>
+      </c>
+      <c r="L123">
+        <v>5</v>
+      </c>
+      <c r="M123">
+        <v>342</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123">
+        <v>2</v>
+      </c>
+      <c r="P123">
+        <v>2</v>
+      </c>
+      <c r="Q123">
+        <v>20</v>
+      </c>
+      <c r="R123">
+        <v>1</v>
+      </c>
+      <c r="S123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
+      <c r="A124" t="s">
+        <v>112</v>
+      </c>
+      <c r="B124" t="s">
+        <v>130</v>
+      </c>
+      <c r="C124">
+        <v>254</v>
+      </c>
+      <c r="D124">
+        <v>17.37</v>
+      </c>
+      <c r="E124" t="s">
+        <v>147</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>8</v>
+      </c>
+      <c r="H124">
+        <v>17</v>
+      </c>
+      <c r="I124">
+        <v>17</v>
+      </c>
+      <c r="J124">
+        <v>17</v>
+      </c>
+      <c r="K124">
+        <v>8</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>335</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124">
+        <v>3</v>
+      </c>
+      <c r="P124">
+        <v>2</v>
+      </c>
+      <c r="Q124">
+        <v>22</v>
+      </c>
+      <c r="R124">
+        <v>1</v>
+      </c>
+      <c r="S124">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19">
+      <c r="A125" t="s">
+        <v>113</v>
+      </c>
+      <c r="B125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125">
+        <v>10</v>
+      </c>
+      <c r="D125">
+        <v>0.49</v>
+      </c>
+      <c r="E125" t="s">
+        <v>147</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+      <c r="J125">
+        <v>2</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>70</v>
+      </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
+      <c r="O125">
+        <v>1</v>
+      </c>
+      <c r="P125">
+        <v>1</v>
+      </c>
+      <c r="Q125">
+        <v>1</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19">
+      <c r="A126" t="s">
+        <v>113</v>
+      </c>
+      <c r="B126" t="s">
+        <v>131</v>
+      </c>
+      <c r="C126">
+        <v>153</v>
+      </c>
+      <c r="D126">
+        <v>13.54</v>
+      </c>
+      <c r="E126" t="s">
+        <v>150</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>7</v>
+      </c>
+      <c r="H126">
+        <v>14</v>
+      </c>
+      <c r="I126">
+        <v>14</v>
+      </c>
+      <c r="J126">
+        <v>14</v>
+      </c>
+      <c r="K126">
+        <v>7</v>
+      </c>
+      <c r="L126">
+        <v>3</v>
+      </c>
+      <c r="M126">
+        <v>254</v>
+      </c>
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126">
+        <v>1</v>
+      </c>
+      <c r="P126">
+        <v>1</v>
+      </c>
+      <c r="Q126">
+        <v>20</v>
+      </c>
+      <c r="R126">
+        <v>1</v>
+      </c>
+      <c r="S126">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19">
+      <c r="A127" t="s">
+        <v>114</v>
+      </c>
+      <c r="B127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C127">
+        <v>179</v>
+      </c>
+      <c r="D127">
+        <v>16.21</v>
+      </c>
+      <c r="E127" t="s">
+        <v>150</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>9</v>
+      </c>
+      <c r="H127">
+        <v>17</v>
+      </c>
+      <c r="I127">
+        <v>17</v>
+      </c>
+      <c r="J127">
+        <v>17</v>
+      </c>
+      <c r="K127">
+        <v>8</v>
+      </c>
+      <c r="L127">
+        <v>5</v>
+      </c>
+      <c r="M127">
+        <v>286</v>
+      </c>
+      <c r="N127">
+        <v>4</v>
+      </c>
+      <c r="O127">
+        <v>4</v>
+      </c>
+      <c r="P127">
+        <v>2</v>
+      </c>
+      <c r="Q127">
+        <v>21</v>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+      <c r="S127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19">
+      <c r="A128" t="s">
+        <v>115</v>
+      </c>
+      <c r="B128" t="s">
+        <v>132</v>
+      </c>
+      <c r="C128">
+        <v>43</v>
+      </c>
+      <c r="D128">
+        <v>3.67</v>
+      </c>
+      <c r="E128" t="s">
+        <v>150</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>4</v>
+      </c>
+      <c r="H128">
+        <v>5</v>
+      </c>
+      <c r="I128">
+        <v>5</v>
+      </c>
+      <c r="J128">
+        <v>4</v>
+      </c>
+      <c r="K128">
+        <v>5</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>175</v>
+      </c>
+      <c r="N128">
+        <v>4</v>
+      </c>
+      <c r="O128">
+        <v>2</v>
+      </c>
+      <c r="P128">
+        <v>3</v>
+      </c>
+      <c r="Q128">
+        <v>20</v>
+      </c>
+      <c r="R128">
+        <v>1</v>
+      </c>
+      <c r="S128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19">
+      <c r="A129" t="s">
+        <v>116</v>
+      </c>
+      <c r="B129" t="s">
+        <v>133</v>
+      </c>
+      <c r="C129">
+        <v>19</v>
+      </c>
+      <c r="D129">
+        <v>0.83</v>
+      </c>
+      <c r="E129" t="s">
+        <v>160</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+      <c r="H129">
+        <v>4</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>4</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>2</v>
+      </c>
+      <c r="M129">
+        <v>64</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>1</v>
+      </c>
+      <c r="Q129">
+        <v>3</v>
+      </c>
+      <c r="R129">
+        <v>1</v>
+      </c>
+      <c r="S129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19">
+      <c r="A130" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C130">
+        <v>80</v>
+      </c>
+      <c r="D130">
+        <v>5.37</v>
+      </c>
+      <c r="E130" t="s">
+        <v>147</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>5</v>
+      </c>
+      <c r="H130">
+        <v>10</v>
+      </c>
+      <c r="I130">
+        <v>10</v>
+      </c>
+      <c r="J130">
+        <v>10</v>
+      </c>
+      <c r="K130">
+        <v>5</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>200</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+      <c r="O130">
+        <v>1</v>
+      </c>
+      <c r="P130">
+        <v>1</v>
+      </c>
+      <c r="Q130">
+        <v>12</v>
+      </c>
+      <c r="R130">
+        <v>1</v>
+      </c>
+      <c r="S130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19">
+      <c r="A131" t="s">
+        <v>117</v>
+      </c>
+      <c r="B131" t="s">
+        <v>135</v>
+      </c>
+      <c r="C131">
+        <v>57</v>
+      </c>
+      <c r="D131">
+        <v>3.47</v>
+      </c>
+      <c r="E131" t="s">
+        <v>156</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>6</v>
+      </c>
+      <c r="H131">
+        <v>7</v>
+      </c>
+      <c r="I131">
+        <v>7</v>
+      </c>
+      <c r="J131">
+        <v>7</v>
+      </c>
+      <c r="K131">
+        <v>7</v>
+      </c>
+      <c r="L131">
+        <v>2</v>
+      </c>
+      <c r="M131">
+        <v>260</v>
+      </c>
+      <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131">
+        <v>2</v>
+      </c>
+      <c r="P131">
+        <v>2</v>
+      </c>
+      <c r="Q131">
+        <v>20</v>
+      </c>
+      <c r="R131">
+        <v>1</v>
+      </c>
+      <c r="S131">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19">
+      <c r="A132" t="s">
+        <v>118</v>
+      </c>
+      <c r="B132" t="s">
+        <v>136</v>
+      </c>
+      <c r="C132">
+        <v>133</v>
+      </c>
+      <c r="D132">
+        <v>8.34</v>
+      </c>
+      <c r="E132" t="s">
+        <v>149</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>8</v>
+      </c>
+      <c r="H132">
+        <v>17</v>
+      </c>
+      <c r="I132">
+        <v>17</v>
+      </c>
+      <c r="J132">
+        <v>17</v>
+      </c>
+      <c r="K132">
+        <v>9</v>
+      </c>
+      <c r="L132">
+        <v>4</v>
+      </c>
+      <c r="M132">
+        <v>357</v>
+      </c>
+      <c r="N132">
+        <v>4</v>
+      </c>
+      <c r="O132">
+        <v>4</v>
+      </c>
+      <c r="P132">
+        <v>3</v>
+      </c>
+      <c r="Q132">
+        <v>20</v>
+      </c>
+      <c r="R132">
+        <v>1</v>
+      </c>
+      <c r="S132">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19">
+      <c r="A133" t="s">
+        <v>119</v>
+      </c>
+      <c r="B133" t="s">
+        <v>137</v>
+      </c>
+      <c r="C133">
+        <v>213</v>
+      </c>
+      <c r="D133">
+        <v>19.24</v>
+      </c>
+      <c r="E133" t="s">
+        <v>149</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>8</v>
+      </c>
+      <c r="H133">
+        <v>17</v>
+      </c>
+      <c r="I133">
+        <v>17</v>
+      </c>
+      <c r="J133">
+        <v>17</v>
+      </c>
+      <c r="K133">
+        <v>9</v>
+      </c>
+      <c r="L133">
+        <v>5</v>
+      </c>
+      <c r="M133">
+        <v>354</v>
+      </c>
+      <c r="N133">
+        <v>3</v>
+      </c>
+      <c r="O133">
+        <v>2</v>
+      </c>
+      <c r="P133">
+        <v>2</v>
+      </c>
+      <c r="Q133">
+        <v>22</v>
+      </c>
+      <c r="R133">
+        <v>1</v>
+      </c>
+      <c r="S133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19">
+      <c r="A134" t="s">
+        <v>120</v>
+      </c>
+      <c r="B134" t="s">
+        <v>137</v>
+      </c>
+      <c r="C134">
+        <v>34</v>
+      </c>
+      <c r="D134">
+        <v>2.76</v>
+      </c>
+      <c r="E134" t="s">
+        <v>149</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>3</v>
+      </c>
+      <c r="I134">
+        <v>3</v>
+      </c>
+      <c r="J134">
+        <v>3</v>
+      </c>
+      <c r="K134">
+        <v>2</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>65</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134">
+        <v>2</v>
+      </c>
+      <c r="P134">
+        <v>1</v>
+      </c>
+      <c r="Q134">
+        <v>4</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19">
+      <c r="A135" t="s">
+        <v>120</v>
+      </c>
+      <c r="B135" t="s">
+        <v>138</v>
+      </c>
+      <c r="C135">
+        <v>196</v>
+      </c>
+      <c r="D135">
+        <v>13.27</v>
+      </c>
+      <c r="E135" t="s">
+        <v>147</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>7</v>
+      </c>
+      <c r="H135">
+        <v>15</v>
+      </c>
+      <c r="I135">
+        <v>15</v>
+      </c>
+      <c r="J135">
+        <v>15</v>
+      </c>
+      <c r="K135">
+        <v>7</v>
+      </c>
+      <c r="L135">
+        <v>5</v>
+      </c>
+      <c r="M135">
+        <v>295</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135">
+        <v>2</v>
+      </c>
+      <c r="P135">
+        <v>2</v>
+      </c>
+      <c r="Q135">
+        <v>20</v>
+      </c>
+      <c r="R135">
+        <v>1</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19">
+      <c r="A136" t="s">
+        <v>121</v>
+      </c>
+      <c r="B136" t="s">
+        <v>139</v>
+      </c>
+      <c r="C136">
+        <v>170</v>
+      </c>
+      <c r="D136">
+        <v>13.93</v>
+      </c>
+      <c r="E136" t="s">
+        <v>149</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136">
+        <v>9</v>
+      </c>
+      <c r="H136">
+        <v>18</v>
+      </c>
+      <c r="I136">
+        <v>18</v>
+      </c>
+      <c r="J136">
+        <v>18</v>
+      </c>
+      <c r="K136">
+        <v>9</v>
+      </c>
+      <c r="L136">
+        <v>5</v>
+      </c>
+      <c r="M136">
+        <v>366</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136">
+        <v>2</v>
+      </c>
+      <c r="P136">
+        <v>3</v>
+      </c>
+      <c r="Q136">
+        <v>23</v>
+      </c>
+      <c r="R136">
+        <v>1</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19">
+      <c r="A137" t="s">
         <v>122</v>
       </c>
-      <c r="F115" t="s">
+      <c r="B137" t="s">
+        <v>140</v>
+      </c>
+      <c r="C137">
+        <v>153</v>
+      </c>
+      <c r="D137">
+        <v>9.32</v>
+      </c>
+      <c r="E137" t="s">
+        <v>149</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>9</v>
+      </c>
+      <c r="H137">
+        <v>19</v>
+      </c>
+      <c r="I137">
+        <v>19</v>
+      </c>
+      <c r="J137">
+        <v>19</v>
+      </c>
+      <c r="K137">
+        <v>9</v>
+      </c>
+      <c r="L137">
+        <v>5</v>
+      </c>
+      <c r="M137">
+        <v>329</v>
+      </c>
+      <c r="N137">
+        <v>3</v>
+      </c>
+      <c r="O137">
+        <v>3</v>
+      </c>
+      <c r="P137">
+        <v>3</v>
+      </c>
+      <c r="Q137">
+        <v>20</v>
+      </c>
+      <c r="R137">
+        <v>1</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19">
+      <c r="A138" t="s">
         <v>123</v>
       </c>
-      <c r="G115" t="s">
+      <c r="B138" t="s">
+        <v>141</v>
+      </c>
+      <c r="C138">
+        <v>138</v>
+      </c>
+      <c r="D138">
+        <v>11.68</v>
+      </c>
+      <c r="E138" t="s">
+        <v>150</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>8</v>
+      </c>
+      <c r="H138">
+        <v>17</v>
+      </c>
+      <c r="I138">
+        <v>17</v>
+      </c>
+      <c r="J138">
+        <v>17</v>
+      </c>
+      <c r="K138">
+        <v>8</v>
+      </c>
+      <c r="L138">
+        <v>4</v>
+      </c>
+      <c r="M138">
+        <v>313</v>
+      </c>
+      <c r="N138">
+        <v>2</v>
+      </c>
+      <c r="O138">
+        <v>2</v>
+      </c>
+      <c r="P138">
+        <v>1</v>
+      </c>
+      <c r="Q138">
+        <v>18</v>
+      </c>
+      <c r="R138">
+        <v>1</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19">
+      <c r="A139" t="s">
+        <v>123</v>
+      </c>
+      <c r="B139" t="s">
+        <v>142</v>
+      </c>
+      <c r="C139">
+        <v>26</v>
+      </c>
+      <c r="D139">
+        <v>1.12</v>
+      </c>
+      <c r="E139" t="s">
+        <v>147</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>2</v>
+      </c>
+      <c r="I139">
+        <v>2</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>42</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>1</v>
+      </c>
+      <c r="Q139">
+        <v>4</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19">
+      <c r="A140" t="s">
         <v>124</v>
       </c>
-      <c r="H115" t="s">
-        <v>124</v>
-      </c>
-      <c r="I115" t="s">
-        <v>125</v>
-      </c>
-      <c r="J115" t="s">
-        <v>125</v>
-      </c>
-      <c r="K115" t="s">
-        <v>124</v>
-      </c>
-      <c r="L115" t="s">
-        <v>124</v>
-      </c>
-      <c r="M115" t="s">
-        <v>126</v>
-      </c>
-      <c r="N115" t="s">
-        <v>124</v>
-      </c>
-      <c r="O115" t="s">
-        <v>123</v>
-      </c>
-      <c r="P115" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>125</v>
-      </c>
-      <c r="R115" t="s">
-        <v>123</v>
-      </c>
-      <c r="S115" t="s">
-        <v>124</v>
+      <c r="B140" t="s">
+        <v>143</v>
+      </c>
+      <c r="C140" t="s">
+        <v>144</v>
+      </c>
+      <c r="D140" t="s">
+        <v>145</v>
+      </c>
+      <c r="E140" t="s">
+        <v>147</v>
+      </c>
+      <c r="F140" t="s">
+        <v>161</v>
+      </c>
+      <c r="G140" t="s">
+        <v>162</v>
+      </c>
+      <c r="H140" t="s">
+        <v>163</v>
+      </c>
+      <c r="I140" t="s">
+        <v>163</v>
+      </c>
+      <c r="J140" t="s">
+        <v>163</v>
+      </c>
+      <c r="K140" t="s">
+        <v>164</v>
+      </c>
+      <c r="L140" t="s">
+        <v>165</v>
+      </c>
+      <c r="M140" t="s">
+        <v>166</v>
+      </c>
+      <c r="N140" t="s">
+        <v>167</v>
+      </c>
+      <c r="O140" t="s">
+        <v>165</v>
+      </c>
+      <c r="P140" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>169</v>
+      </c>
+      <c r="R140" t="s">
+        <v>161</v>
+      </c>
+      <c r="S140" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="176">
   <si>
     <t>Date</t>
   </si>
@@ -391,6 +391,18 @@
     <t>2025-09-16</t>
   </si>
   <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -448,10 +460,16 @@
     <t>5106</t>
   </si>
   <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>13.64</t>
+    <t>4231</t>
+  </si>
+  <si>
+    <t>5118</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2.64</t>
   </si>
   <si>
     <t>N14</t>
@@ -502,28 +520,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>273</t>
+    <t>208</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
 </sst>
 </file>
@@ -881,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S140"/>
+  <dimension ref="A1:S144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -957,7 +975,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1016,7 +1034,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1075,7 +1093,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1134,7 +1152,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1193,7 +1211,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1252,7 +1270,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1311,7 +1329,7 @@
         <v>18.6</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1370,7 +1388,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1429,7 +1447,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1488,7 +1506,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1547,7 +1565,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1606,7 +1624,7 @@
         <v>4.6</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1665,7 +1683,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1724,7 +1742,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1783,7 +1801,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1842,7 +1860,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1901,7 +1919,7 @@
         <v>2.3</v>
       </c>
       <c r="E18" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1960,7 +1978,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2019,7 +2037,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2078,7 +2096,7 @@
         <v>4.4</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2137,7 +2155,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2196,7 +2214,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2255,7 +2273,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2314,7 +2332,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2373,7 +2391,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2432,7 +2450,7 @@
         <v>4.06</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2491,7 +2509,7 @@
         <v>7.95</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2550,7 +2568,7 @@
         <v>2.2</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2609,7 +2627,7 @@
         <v>3.27</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2668,7 +2686,7 @@
         <v>8.31</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2727,7 +2745,7 @@
         <v>3.59</v>
       </c>
       <c r="E32" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2786,7 +2804,7 @@
         <v>2.13</v>
       </c>
       <c r="E33" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2845,7 +2863,7 @@
         <v>4.8</v>
       </c>
       <c r="E34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -2904,7 +2922,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2963,7 +2981,7 @@
         <v>6.45</v>
       </c>
       <c r="E36" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3022,7 +3040,7 @@
         <v>4.72</v>
       </c>
       <c r="E37" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3081,7 +3099,7 @@
         <v>1.8</v>
       </c>
       <c r="E38" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3140,7 +3158,7 @@
         <v>5.86</v>
       </c>
       <c r="E39" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3199,7 +3217,7 @@
         <v>6.18</v>
       </c>
       <c r="E40" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3258,7 +3276,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3317,7 +3335,7 @@
         <v>7.13</v>
       </c>
       <c r="E42" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3376,7 +3394,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3435,7 +3453,7 @@
         <v>5.81</v>
       </c>
       <c r="E44" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3494,7 +3512,7 @@
         <v>4.09</v>
       </c>
       <c r="E45" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3553,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3612,7 +3630,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3671,7 +3689,7 @@
         <v>5.13</v>
       </c>
       <c r="E48" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3730,7 +3748,7 @@
         <v>1.81</v>
       </c>
       <c r="E49" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -3789,7 +3807,7 @@
         <v>7.95</v>
       </c>
       <c r="E50" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -3848,7 +3866,7 @@
         <v>0.64</v>
       </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -3907,7 +3925,7 @@
         <v>6.13</v>
       </c>
       <c r="E52" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3966,7 +3984,7 @@
         <v>2.77</v>
       </c>
       <c r="E53" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4025,7 +4043,7 @@
         <v>4.35</v>
       </c>
       <c r="E54" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4084,7 +4102,7 @@
         <v>5.24</v>
       </c>
       <c r="E55" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4143,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4202,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4261,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4320,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4379,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4438,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4497,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4556,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4615,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4674,7 +4692,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4733,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4792,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4851,7 +4869,7 @@
         <v>6.54</v>
       </c>
       <c r="E68" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4910,7 +4928,7 @@
         <v>6.31</v>
       </c>
       <c r="E69" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4969,7 +4987,7 @@
         <v>3.72</v>
       </c>
       <c r="E70" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -5028,7 +5046,7 @@
         <v>3.56</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5087,7 +5105,7 @@
         <v>19.54</v>
       </c>
       <c r="E72" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5146,7 +5164,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5205,7 +5223,7 @@
         <v>5.41</v>
       </c>
       <c r="E74" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5264,7 +5282,7 @@
         <v>5.32</v>
       </c>
       <c r="E75" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5323,7 +5341,7 @@
         <v>7.32</v>
       </c>
       <c r="E76" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5382,7 +5400,7 @@
         <v>13.1</v>
       </c>
       <c r="E77" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5441,7 +5459,7 @@
         <v>4.35</v>
       </c>
       <c r="E78" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5500,7 +5518,7 @@
         <v>3.12</v>
       </c>
       <c r="E79" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5559,7 +5577,7 @@
         <v>1.15</v>
       </c>
       <c r="E80" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5618,7 +5636,7 @@
         <v>4.68</v>
       </c>
       <c r="E81" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5677,7 +5695,7 @@
         <v>0.85</v>
       </c>
       <c r="E82" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -5736,7 +5754,7 @@
         <v>5.36</v>
       </c>
       <c r="E83" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -5795,7 +5813,7 @@
         <v>3.64</v>
       </c>
       <c r="E84" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -5854,7 +5872,7 @@
         <v>1.22</v>
       </c>
       <c r="E85" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5913,7 +5931,7 @@
         <v>7.13</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -5972,7 +5990,7 @@
         <v>3.81</v>
       </c>
       <c r="E87" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -6031,7 +6049,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E88" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -6090,7 +6108,7 @@
         <v>2.35</v>
       </c>
       <c r="E89" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -6149,7 +6167,7 @@
         <v>6.36</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6208,7 +6226,7 @@
         <v>7.26</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -6267,7 +6285,7 @@
         <v>1.02</v>
       </c>
       <c r="E92" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6326,7 +6344,7 @@
         <v>4.02</v>
       </c>
       <c r="E93" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -6385,7 +6403,7 @@
         <v>3.71</v>
       </c>
       <c r="E94" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6444,7 +6462,7 @@
         <v>4.6</v>
       </c>
       <c r="E95" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6503,7 +6521,7 @@
         <v>16.21</v>
       </c>
       <c r="E96" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -6562,7 +6580,7 @@
         <v>3.12</v>
       </c>
       <c r="E97" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6621,7 +6639,7 @@
         <v>0.03</v>
       </c>
       <c r="E98" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -6680,7 +6698,7 @@
         <v>4.23</v>
       </c>
       <c r="E99" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -6739,7 +6757,7 @@
         <v>2.72</v>
       </c>
       <c r="E100" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -6798,7 +6816,7 @@
         <v>9.32</v>
       </c>
       <c r="E101" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -6857,7 +6875,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="E102" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -6916,7 +6934,7 @@
         <v>5.07</v>
       </c>
       <c r="E103" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -6975,7 +6993,7 @@
         <v>1.27</v>
       </c>
       <c r="E104" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -7034,7 +7052,7 @@
         <v>0.05</v>
       </c>
       <c r="E105" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -7093,7 +7111,7 @@
         <v>6.75</v>
       </c>
       <c r="E106" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -7152,7 +7170,7 @@
         <v>5.39</v>
       </c>
       <c r="E107" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -7211,7 +7229,7 @@
         <v>2.66</v>
       </c>
       <c r="E108" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -7270,7 +7288,7 @@
         <v>22.78</v>
       </c>
       <c r="E109" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7329,7 +7347,7 @@
         <v>12.71</v>
       </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -7388,7 +7406,7 @@
         <v>5.35</v>
       </c>
       <c r="E111" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -7447,7 +7465,7 @@
         <v>16.98</v>
       </c>
       <c r="E112" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -7506,7 +7524,7 @@
         <v>6.32</v>
       </c>
       <c r="E113" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -7565,7 +7583,7 @@
         <v>3.35</v>
       </c>
       <c r="E114" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7624,7 +7642,7 @@
         <v>0.24</v>
       </c>
       <c r="E115" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -7683,7 +7701,7 @@
         <v>4.32</v>
       </c>
       <c r="E116" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -7733,7 +7751,7 @@
         <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C117">
         <v>132</v>
@@ -7742,7 +7760,7 @@
         <v>9.23</v>
       </c>
       <c r="E117" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -7792,7 +7810,7 @@
         <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C118">
         <v>22</v>
@@ -7801,7 +7819,7 @@
         <v>2.65</v>
       </c>
       <c r="E118" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -7851,7 +7869,7 @@
         <v>108</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C119">
         <v>178</v>
@@ -7860,7 +7878,7 @@
         <v>13.54</v>
       </c>
       <c r="E119" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -7910,7 +7928,7 @@
         <v>108</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -7919,7 +7937,7 @@
         <v>0.04</v>
       </c>
       <c r="E120" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -7969,7 +7987,7 @@
         <v>109</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C121">
         <v>31</v>
@@ -7978,7 +7996,7 @@
         <v>2.5</v>
       </c>
       <c r="E121" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -8028,7 +8046,7 @@
         <v>110</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C122">
         <v>29</v>
@@ -8037,7 +8055,7 @@
         <v>1.65</v>
       </c>
       <c r="E122" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -8087,7 +8105,7 @@
         <v>111</v>
       </c>
       <c r="B123" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C123">
         <v>219</v>
@@ -8096,7 +8114,7 @@
         <v>11.1</v>
       </c>
       <c r="E123" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -8146,7 +8164,7 @@
         <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C124">
         <v>254</v>
@@ -8155,7 +8173,7 @@
         <v>17.37</v>
       </c>
       <c r="E124" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -8205,7 +8223,7 @@
         <v>113</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -8214,7 +8232,7 @@
         <v>0.49</v>
       </c>
       <c r="E125" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -8264,7 +8282,7 @@
         <v>113</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C126">
         <v>153</v>
@@ -8273,7 +8291,7 @@
         <v>13.54</v>
       </c>
       <c r="E126" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8323,7 +8341,7 @@
         <v>114</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C127">
         <v>179</v>
@@ -8332,7 +8350,7 @@
         <v>16.21</v>
       </c>
       <c r="E127" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -8382,7 +8400,7 @@
         <v>115</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C128">
         <v>43</v>
@@ -8391,7 +8409,7 @@
         <v>3.67</v>
       </c>
       <c r="E128" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -8441,7 +8459,7 @@
         <v>116</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C129">
         <v>19</v>
@@ -8450,7 +8468,7 @@
         <v>0.83</v>
       </c>
       <c r="E129" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8500,7 +8518,7 @@
         <v>116</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C130">
         <v>80</v>
@@ -8509,7 +8527,7 @@
         <v>5.37</v>
       </c>
       <c r="E130" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -8559,7 +8577,7 @@
         <v>117</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C131">
         <v>57</v>
@@ -8568,7 +8586,7 @@
         <v>3.47</v>
       </c>
       <c r="E131" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -8618,7 +8636,7 @@
         <v>118</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C132">
         <v>133</v>
@@ -8627,7 +8645,7 @@
         <v>8.34</v>
       </c>
       <c r="E132" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -8677,7 +8695,7 @@
         <v>119</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C133">
         <v>213</v>
@@ -8686,7 +8704,7 @@
         <v>19.24</v>
       </c>
       <c r="E133" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -8736,7 +8754,7 @@
         <v>120</v>
       </c>
       <c r="B134" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C134">
         <v>34</v>
@@ -8745,7 +8763,7 @@
         <v>2.76</v>
       </c>
       <c r="E134" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -8795,7 +8813,7 @@
         <v>120</v>
       </c>
       <c r="B135" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C135">
         <v>196</v>
@@ -8804,7 +8822,7 @@
         <v>13.27</v>
       </c>
       <c r="E135" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -8854,7 +8872,7 @@
         <v>121</v>
       </c>
       <c r="B136" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C136">
         <v>170</v>
@@ -8863,7 +8881,7 @@
         <v>13.93</v>
       </c>
       <c r="E136" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -8913,7 +8931,7 @@
         <v>122</v>
       </c>
       <c r="B137" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C137">
         <v>153</v>
@@ -8922,7 +8940,7 @@
         <v>9.32</v>
       </c>
       <c r="E137" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -8972,7 +8990,7 @@
         <v>123</v>
       </c>
       <c r="B138" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C138">
         <v>138</v>
@@ -8981,7 +8999,7 @@
         <v>11.68</v>
       </c>
       <c r="E138" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -9031,7 +9049,7 @@
         <v>123</v>
       </c>
       <c r="B139" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C139">
         <v>26</v>
@@ -9040,7 +9058,7 @@
         <v>1.12</v>
       </c>
       <c r="E139" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9090,58 +9108,294 @@
         <v>124</v>
       </c>
       <c r="B140" t="s">
-        <v>143</v>
-      </c>
-      <c r="C140" t="s">
-        <v>144</v>
-      </c>
-      <c r="D140" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="C140">
+        <v>153</v>
+      </c>
+      <c r="D140">
+        <v>13.64</v>
       </c>
       <c r="E140" t="s">
+        <v>153</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>8</v>
+      </c>
+      <c r="H140">
+        <v>17</v>
+      </c>
+      <c r="I140">
+        <v>17</v>
+      </c>
+      <c r="J140">
+        <v>17</v>
+      </c>
+      <c r="K140">
+        <v>9</v>
+      </c>
+      <c r="L140">
+        <v>4</v>
+      </c>
+      <c r="M140">
+        <v>273</v>
+      </c>
+      <c r="N140">
+        <v>5</v>
+      </c>
+      <c r="O140">
+        <v>4</v>
+      </c>
+      <c r="P140">
+        <v>3</v>
+      </c>
+      <c r="Q140">
+        <v>20</v>
+      </c>
+      <c r="R140">
+        <v>1</v>
+      </c>
+      <c r="S140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19">
+      <c r="A141" t="s">
+        <v>125</v>
+      </c>
+      <c r="B141" t="s">
+        <v>148</v>
+      </c>
+      <c r="C141">
+        <v>106</v>
+      </c>
+      <c r="D141">
+        <v>2.34</v>
+      </c>
+      <c r="E141" t="s">
+        <v>156</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>8</v>
+      </c>
+      <c r="H141">
+        <v>9</v>
+      </c>
+      <c r="I141">
+        <v>9</v>
+      </c>
+      <c r="J141">
+        <v>9</v>
+      </c>
+      <c r="K141">
+        <v>8</v>
+      </c>
+      <c r="L141">
+        <v>4</v>
+      </c>
+      <c r="M141">
+        <v>281</v>
+      </c>
+      <c r="N141">
+        <v>2</v>
+      </c>
+      <c r="O141">
+        <v>2</v>
+      </c>
+      <c r="P141">
+        <v>3</v>
+      </c>
+      <c r="Q141">
+        <v>10</v>
+      </c>
+      <c r="R141">
+        <v>1</v>
+      </c>
+      <c r="S141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19">
+      <c r="A142" t="s">
+        <v>126</v>
+      </c>
+      <c r="B142" t="s">
+        <v>141</v>
+      </c>
+      <c r="C142">
+        <v>133</v>
+      </c>
+      <c r="D142">
+        <v>2.95</v>
+      </c>
+      <c r="E142" t="s">
+        <v>155</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>10</v>
+      </c>
+      <c r="H142">
+        <v>19</v>
+      </c>
+      <c r="I142">
+        <v>18</v>
+      </c>
+      <c r="J142">
+        <v>18</v>
+      </c>
+      <c r="K142">
+        <v>9</v>
+      </c>
+      <c r="L142">
+        <v>4</v>
+      </c>
+      <c r="M142">
+        <v>389</v>
+      </c>
+      <c r="N142">
+        <v>3</v>
+      </c>
+      <c r="O142">
+        <v>3</v>
+      </c>
+      <c r="P142">
+        <v>2</v>
+      </c>
+      <c r="Q142">
+        <v>22</v>
+      </c>
+      <c r="R142">
+        <v>1</v>
+      </c>
+      <c r="S142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19">
+      <c r="A143" t="s">
+        <v>127</v>
+      </c>
+      <c r="B143" t="s">
         <v>147</v>
       </c>
-      <c r="F140" t="s">
-        <v>161</v>
-      </c>
-      <c r="G140" t="s">
-        <v>162</v>
-      </c>
-      <c r="H140" t="s">
-        <v>163</v>
-      </c>
-      <c r="I140" t="s">
-        <v>163</v>
-      </c>
-      <c r="J140" t="s">
-        <v>163</v>
-      </c>
-      <c r="K140" t="s">
-        <v>164</v>
-      </c>
-      <c r="L140" t="s">
-        <v>165</v>
-      </c>
-      <c r="M140" t="s">
-        <v>166</v>
-      </c>
-      <c r="N140" t="s">
+      <c r="C143">
+        <v>141</v>
+      </c>
+      <c r="D143">
+        <v>3.21</v>
+      </c>
+      <c r="E143" t="s">
+        <v>153</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>9</v>
+      </c>
+      <c r="H143">
+        <v>19</v>
+      </c>
+      <c r="I143">
+        <v>19</v>
+      </c>
+      <c r="J143">
+        <v>19</v>
+      </c>
+      <c r="K143">
+        <v>9</v>
+      </c>
+      <c r="L143">
+        <v>6</v>
+      </c>
+      <c r="M143">
+        <v>382</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143">
+        <v>2</v>
+      </c>
+      <c r="P143">
+        <v>2</v>
+      </c>
+      <c r="Q143">
+        <v>22</v>
+      </c>
+      <c r="R143">
+        <v>1</v>
+      </c>
+      <c r="S143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19">
+      <c r="A144" t="s">
+        <v>128</v>
+      </c>
+      <c r="B144" t="s">
+        <v>149</v>
+      </c>
+      <c r="C144" t="s">
+        <v>150</v>
+      </c>
+      <c r="D144" t="s">
+        <v>151</v>
+      </c>
+      <c r="E144" t="s">
+        <v>153</v>
+      </c>
+      <c r="F144" t="s">
         <v>167</v>
       </c>
-      <c r="O140" t="s">
-        <v>165</v>
-      </c>
-      <c r="P140" t="s">
+      <c r="G144" t="s">
         <v>168</v>
       </c>
-      <c r="Q140" t="s">
+      <c r="H144" t="s">
         <v>169</v>
       </c>
-      <c r="R140" t="s">
-        <v>161</v>
-      </c>
-      <c r="S140" t="s">
+      <c r="I144" t="s">
+        <v>169</v>
+      </c>
+      <c r="J144" t="s">
+        <v>169</v>
+      </c>
+      <c r="K144" t="s">
+        <v>170</v>
+      </c>
+      <c r="L144" t="s">
+        <v>171</v>
+      </c>
+      <c r="M144" t="s">
+        <v>172</v>
+      </c>
+      <c r="N144" t="s">
+        <v>173</v>
+      </c>
+      <c r="O144" t="s">
+        <v>173</v>
+      </c>
+      <c r="P144" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>174</v>
+      </c>
+      <c r="R144" t="s">
         <v>167</v>
+      </c>
+      <c r="S144" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="266">
   <si>
     <t>Date</t>
   </si>
@@ -403,6 +403,153 @@
     <t>2025-09-20</t>
   </si>
   <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2025-09-29</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>2025-10-05</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>2025-10-14</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>2025-10-18</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
+    <t>2025-10-25</t>
+  </si>
+  <si>
+    <t>2025-10-28</t>
+  </si>
+  <si>
+    <t>2025-10-30</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-01</t>
+  </si>
+  <si>
+    <t>2025-11-02</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>2025-11-06</t>
+  </si>
+  <si>
+    <t>2025-11-08</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-11</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-17</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>2025-11-25</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>2025-11-27</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -466,10 +613,139 @@
     <t>5118</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>2.64</t>
+    <t>5413</t>
+  </si>
+  <si>
+    <t>2513</t>
+  </si>
+  <si>
+    <t>5212</t>
+  </si>
+  <si>
+    <t>3402</t>
+  </si>
+  <si>
+    <t>5128</t>
+  </si>
+  <si>
+    <t>5404</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>5120</t>
+  </si>
+  <si>
+    <t>5509</t>
+  </si>
+  <si>
+    <t>5411</t>
+  </si>
+  <si>
+    <t>4319</t>
+  </si>
+  <si>
+    <t>1220</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>5214</t>
+  </si>
+  <si>
+    <t>5435</t>
+  </si>
+  <si>
+    <t>5390</t>
+  </si>
+  <si>
+    <t>5291</t>
+  </si>
+  <si>
+    <t>5508</t>
+  </si>
+  <si>
+    <t>5461</t>
+  </si>
+  <si>
+    <t>3413</t>
+  </si>
+  <si>
+    <t>3113</t>
+  </si>
+  <si>
+    <t>1219</t>
+  </si>
+  <si>
+    <t>4320</t>
+  </si>
+  <si>
+    <t>4390</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>4126</t>
+  </si>
+  <si>
+    <t>5304</t>
+  </si>
+  <si>
+    <t>5652</t>
+  </si>
+  <si>
+    <t>5653</t>
+  </si>
+  <si>
+    <t>5108</t>
+  </si>
+  <si>
+    <t>4124</t>
+  </si>
+  <si>
+    <t>5490</t>
+  </si>
+  <si>
+    <t>3111</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>5632</t>
+  </si>
+  <si>
+    <t>3313</t>
+  </si>
+  <si>
+    <t>5502</t>
+  </si>
+  <si>
+    <t>5307</t>
+  </si>
+  <si>
+    <t>5313</t>
+  </si>
+  <si>
+    <t>4314</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2215</t>
+  </si>
+  <si>
+    <t>2321</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>0.18</t>
   </si>
   <si>
     <t>N14</t>
@@ -520,28 +796,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>20</t>
+    <t>6</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>79</t>
   </si>
 </sst>
 </file>
@@ -899,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S144"/>
+  <dimension ref="A1:S207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -975,7 +1245,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1034,7 +1304,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1093,7 +1363,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1152,7 +1422,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1211,7 +1481,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1270,7 +1540,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1329,7 +1599,7 @@
         <v>18.6</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1388,7 +1658,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1447,7 +1717,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1506,7 +1776,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1565,7 +1835,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1624,7 +1894,7 @@
         <v>4.6</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1683,7 +1953,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1742,7 +2012,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1801,7 +2071,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1860,7 +2130,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1919,7 +2189,7 @@
         <v>2.3</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1978,7 +2248,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2037,7 +2307,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2096,7 +2366,7 @@
         <v>4.4</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2155,7 +2425,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2214,7 +2484,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2273,7 +2543,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2332,7 +2602,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2391,7 +2661,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2450,7 +2720,7 @@
         <v>4.06</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2509,7 +2779,7 @@
         <v>7.95</v>
       </c>
       <c r="E28" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2568,7 +2838,7 @@
         <v>2.2</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2627,7 +2897,7 @@
         <v>3.27</v>
       </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2686,7 +2956,7 @@
         <v>8.31</v>
       </c>
       <c r="E31" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2745,7 +3015,7 @@
         <v>3.59</v>
       </c>
       <c r="E32" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2804,7 +3074,7 @@
         <v>2.13</v>
       </c>
       <c r="E33" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2863,7 +3133,7 @@
         <v>4.8</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -2922,7 +3192,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2981,7 +3251,7 @@
         <v>6.45</v>
       </c>
       <c r="E36" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3040,7 +3310,7 @@
         <v>4.72</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3099,7 +3369,7 @@
         <v>1.8</v>
       </c>
       <c r="E38" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3158,7 +3428,7 @@
         <v>5.86</v>
       </c>
       <c r="E39" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3217,7 +3487,7 @@
         <v>6.18</v>
       </c>
       <c r="E40" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3276,7 +3546,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3335,7 +3605,7 @@
         <v>7.13</v>
       </c>
       <c r="E42" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3394,7 +3664,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="E43" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3453,7 +3723,7 @@
         <v>5.81</v>
       </c>
       <c r="E44" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3512,7 +3782,7 @@
         <v>4.09</v>
       </c>
       <c r="E45" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3571,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3630,7 +3900,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3689,7 +3959,7 @@
         <v>5.13</v>
       </c>
       <c r="E48" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3748,7 +4018,7 @@
         <v>1.81</v>
       </c>
       <c r="E49" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -3807,7 +4077,7 @@
         <v>7.95</v>
       </c>
       <c r="E50" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -3866,7 +4136,7 @@
         <v>0.64</v>
       </c>
       <c r="E51" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -3925,7 +4195,7 @@
         <v>6.13</v>
       </c>
       <c r="E52" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3984,7 +4254,7 @@
         <v>2.77</v>
       </c>
       <c r="E53" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4043,7 +4313,7 @@
         <v>4.35</v>
       </c>
       <c r="E54" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4102,7 +4372,7 @@
         <v>5.24</v>
       </c>
       <c r="E55" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4161,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4220,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4279,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4338,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4397,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4456,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4515,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4574,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4633,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4692,7 +4962,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4751,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4810,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4869,7 +5139,7 @@
         <v>6.54</v>
       </c>
       <c r="E68" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4928,7 +5198,7 @@
         <v>6.31</v>
       </c>
       <c r="E69" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4987,7 +5257,7 @@
         <v>3.72</v>
       </c>
       <c r="E70" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -5046,7 +5316,7 @@
         <v>3.56</v>
       </c>
       <c r="E71" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5105,7 +5375,7 @@
         <v>19.54</v>
       </c>
       <c r="E72" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5164,7 +5434,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5223,7 +5493,7 @@
         <v>5.41</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5282,7 +5552,7 @@
         <v>5.32</v>
       </c>
       <c r="E75" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5341,7 +5611,7 @@
         <v>7.32</v>
       </c>
       <c r="E76" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5400,7 +5670,7 @@
         <v>13.1</v>
       </c>
       <c r="E77" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5459,7 +5729,7 @@
         <v>4.35</v>
       </c>
       <c r="E78" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5518,7 +5788,7 @@
         <v>3.12</v>
       </c>
       <c r="E79" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5577,7 +5847,7 @@
         <v>1.15</v>
       </c>
       <c r="E80" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5636,7 +5906,7 @@
         <v>4.68</v>
       </c>
       <c r="E81" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5695,7 +5965,7 @@
         <v>0.85</v>
       </c>
       <c r="E82" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -5754,7 +6024,7 @@
         <v>5.36</v>
       </c>
       <c r="E83" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -5813,7 +6083,7 @@
         <v>3.64</v>
       </c>
       <c r="E84" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -5872,7 +6142,7 @@
         <v>1.22</v>
       </c>
       <c r="E85" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5931,7 +6201,7 @@
         <v>7.13</v>
       </c>
       <c r="E86" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -5990,7 +6260,7 @@
         <v>3.81</v>
       </c>
       <c r="E87" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -6049,7 +6319,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E88" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -6108,7 +6378,7 @@
         <v>2.35</v>
       </c>
       <c r="E89" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -6167,7 +6437,7 @@
         <v>6.36</v>
       </c>
       <c r="E90" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6226,7 +6496,7 @@
         <v>7.26</v>
       </c>
       <c r="E91" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -6285,7 +6555,7 @@
         <v>1.02</v>
       </c>
       <c r="E92" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6344,7 +6614,7 @@
         <v>4.02</v>
       </c>
       <c r="E93" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -6403,7 +6673,7 @@
         <v>3.71</v>
       </c>
       <c r="E94" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6462,7 +6732,7 @@
         <v>4.6</v>
       </c>
       <c r="E95" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6521,7 +6791,7 @@
         <v>16.21</v>
       </c>
       <c r="E96" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -6580,7 +6850,7 @@
         <v>3.12</v>
       </c>
       <c r="E97" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6639,7 +6909,7 @@
         <v>0.03</v>
       </c>
       <c r="E98" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -6698,7 +6968,7 @@
         <v>4.23</v>
       </c>
       <c r="E99" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -6757,7 +7027,7 @@
         <v>2.72</v>
       </c>
       <c r="E100" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -6816,7 +7086,7 @@
         <v>9.32</v>
       </c>
       <c r="E101" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -6875,7 +7145,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="E102" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -6934,7 +7204,7 @@
         <v>5.07</v>
       </c>
       <c r="E103" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -6993,7 +7263,7 @@
         <v>1.27</v>
       </c>
       <c r="E104" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -7052,7 +7322,7 @@
         <v>0.05</v>
       </c>
       <c r="E105" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -7111,7 +7381,7 @@
         <v>6.75</v>
       </c>
       <c r="E106" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -7170,7 +7440,7 @@
         <v>5.39</v>
       </c>
       <c r="E107" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -7229,7 +7499,7 @@
         <v>2.66</v>
       </c>
       <c r="E108" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -7288,7 +7558,7 @@
         <v>22.78</v>
       </c>
       <c r="E109" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7347,7 +7617,7 @@
         <v>12.71</v>
       </c>
       <c r="E110" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -7406,7 +7676,7 @@
         <v>5.35</v>
       </c>
       <c r="E111" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -7465,7 +7735,7 @@
         <v>16.98</v>
       </c>
       <c r="E112" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -7524,7 +7794,7 @@
         <v>6.32</v>
       </c>
       <c r="E113" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -7583,7 +7853,7 @@
         <v>3.35</v>
       </c>
       <c r="E114" t="s">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7642,7 +7912,7 @@
         <v>0.24</v>
       </c>
       <c r="E115" t="s">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -7701,7 +7971,7 @@
         <v>4.32</v>
       </c>
       <c r="E116" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -7751,7 +8021,7 @@
         <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="C117">
         <v>132</v>
@@ -7760,7 +8030,7 @@
         <v>9.23</v>
       </c>
       <c r="E117" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -7810,7 +8080,7 @@
         <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="C118">
         <v>22</v>
@@ -7819,7 +8089,7 @@
         <v>2.65</v>
       </c>
       <c r="E118" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -7869,7 +8139,7 @@
         <v>108</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="C119">
         <v>178</v>
@@ -7878,7 +8148,7 @@
         <v>13.54</v>
       </c>
       <c r="E119" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -7928,7 +8198,7 @@
         <v>108</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -7937,7 +8207,7 @@
         <v>0.04</v>
       </c>
       <c r="E120" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -7987,7 +8257,7 @@
         <v>109</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="C121">
         <v>31</v>
@@ -7996,7 +8266,7 @@
         <v>2.5</v>
       </c>
       <c r="E121" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -8046,7 +8316,7 @@
         <v>110</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="C122">
         <v>29</v>
@@ -8055,7 +8325,7 @@
         <v>1.65</v>
       </c>
       <c r="E122" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -8105,7 +8375,7 @@
         <v>111</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="C123">
         <v>219</v>
@@ -8114,7 +8384,7 @@
         <v>11.1</v>
       </c>
       <c r="E123" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -8164,7 +8434,7 @@
         <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="C124">
         <v>254</v>
@@ -8173,7 +8443,7 @@
         <v>17.37</v>
       </c>
       <c r="E124" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -8223,7 +8493,7 @@
         <v>113</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -8232,7 +8502,7 @@
         <v>0.49</v>
       </c>
       <c r="E125" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -8282,7 +8552,7 @@
         <v>113</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="C126">
         <v>153</v>
@@ -8291,7 +8561,7 @@
         <v>13.54</v>
       </c>
       <c r="E126" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8341,7 +8611,7 @@
         <v>114</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="C127">
         <v>179</v>
@@ -8350,7 +8620,7 @@
         <v>16.21</v>
       </c>
       <c r="E127" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -8400,7 +8670,7 @@
         <v>115</v>
       </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="C128">
         <v>43</v>
@@ -8409,7 +8679,7 @@
         <v>3.67</v>
       </c>
       <c r="E128" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -8459,7 +8729,7 @@
         <v>116</v>
       </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="C129">
         <v>19</v>
@@ -8468,7 +8738,7 @@
         <v>0.83</v>
       </c>
       <c r="E129" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8518,7 +8788,7 @@
         <v>116</v>
       </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="C130">
         <v>80</v>
@@ -8527,7 +8797,7 @@
         <v>5.37</v>
       </c>
       <c r="E130" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -8577,7 +8847,7 @@
         <v>117</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="C131">
         <v>57</v>
@@ -8586,7 +8856,7 @@
         <v>3.47</v>
       </c>
       <c r="E131" t="s">
-        <v>162</v>
+        <v>254</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -8636,7 +8906,7 @@
         <v>118</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="C132">
         <v>133</v>
@@ -8645,7 +8915,7 @@
         <v>8.34</v>
       </c>
       <c r="E132" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -8695,7 +8965,7 @@
         <v>119</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="C133">
         <v>213</v>
@@ -8704,7 +8974,7 @@
         <v>19.24</v>
       </c>
       <c r="E133" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -8754,7 +9024,7 @@
         <v>120</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="C134">
         <v>34</v>
@@ -8763,7 +9033,7 @@
         <v>2.76</v>
       </c>
       <c r="E134" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -8813,7 +9083,7 @@
         <v>120</v>
       </c>
       <c r="B135" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="C135">
         <v>196</v>
@@ -8822,7 +9092,7 @@
         <v>13.27</v>
       </c>
       <c r="E135" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -8872,7 +9142,7 @@
         <v>121</v>
       </c>
       <c r="B136" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="C136">
         <v>170</v>
@@ -8881,7 +9151,7 @@
         <v>13.93</v>
       </c>
       <c r="E136" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -8931,7 +9201,7 @@
         <v>122</v>
       </c>
       <c r="B137" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="C137">
         <v>153</v>
@@ -8940,7 +9210,7 @@
         <v>9.32</v>
       </c>
       <c r="E137" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -8990,7 +9260,7 @@
         <v>123</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="C138">
         <v>138</v>
@@ -8999,7 +9269,7 @@
         <v>11.68</v>
       </c>
       <c r="E138" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -9049,7 +9319,7 @@
         <v>123</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="C139">
         <v>26</v>
@@ -9058,7 +9328,7 @@
         <v>1.12</v>
       </c>
       <c r="E139" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9108,7 +9378,7 @@
         <v>124</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="C140">
         <v>153</v>
@@ -9117,7 +9387,7 @@
         <v>13.64</v>
       </c>
       <c r="E140" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -9167,7 +9437,7 @@
         <v>125</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="C141">
         <v>106</v>
@@ -9176,7 +9446,7 @@
         <v>2.34</v>
       </c>
       <c r="E141" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -9226,7 +9496,7 @@
         <v>126</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="C142">
         <v>133</v>
@@ -9235,7 +9505,7 @@
         <v>2.95</v>
       </c>
       <c r="E142" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -9285,7 +9555,7 @@
         <v>127</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="C143">
         <v>141</v>
@@ -9294,7 +9564,7 @@
         <v>3.21</v>
       </c>
       <c r="E143" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -9344,58 +9614,3775 @@
         <v>128</v>
       </c>
       <c r="B144" t="s">
+        <v>198</v>
+      </c>
+      <c r="C144">
+        <v>117</v>
+      </c>
+      <c r="D144">
+        <v>2.64</v>
+      </c>
+      <c r="E144" t="s">
+        <v>245</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>9</v>
+      </c>
+      <c r="H144">
+        <v>10</v>
+      </c>
+      <c r="I144">
+        <v>10</v>
+      </c>
+      <c r="J144">
+        <v>10</v>
+      </c>
+      <c r="K144">
+        <v>8</v>
+      </c>
+      <c r="L144">
+        <v>4</v>
+      </c>
+      <c r="M144">
+        <v>208</v>
+      </c>
+      <c r="N144">
+        <v>2</v>
+      </c>
+      <c r="O144">
+        <v>2</v>
+      </c>
+      <c r="P144">
+        <v>2</v>
+      </c>
+      <c r="Q144">
+        <v>20</v>
+      </c>
+      <c r="R144">
+        <v>1</v>
+      </c>
+      <c r="S144">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19">
+      <c r="A145" t="s">
+        <v>129</v>
+      </c>
+      <c r="B145" t="s">
+        <v>199</v>
+      </c>
+      <c r="C145">
+        <v>78</v>
+      </c>
+      <c r="D145">
+        <v>4.3</v>
+      </c>
+      <c r="E145" t="s">
+        <v>248</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>8</v>
+      </c>
+      <c r="H145">
+        <v>9</v>
+      </c>
+      <c r="I145">
+        <v>9</v>
+      </c>
+      <c r="J145">
+        <v>9</v>
+      </c>
+      <c r="K145">
+        <v>9</v>
+      </c>
+      <c r="L145">
+        <v>4</v>
+      </c>
+      <c r="M145">
+        <v>264</v>
+      </c>
+      <c r="N145">
+        <v>4</v>
+      </c>
+      <c r="O145">
+        <v>2</v>
+      </c>
+      <c r="P145">
+        <v>2</v>
+      </c>
+      <c r="Q145">
+        <v>20</v>
+      </c>
+      <c r="R145">
+        <v>1</v>
+      </c>
+      <c r="S145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19">
+      <c r="A146" t="s">
+        <v>130</v>
+      </c>
+      <c r="B146" t="s">
+        <v>200</v>
+      </c>
+      <c r="C146">
+        <v>172</v>
+      </c>
+      <c r="D146">
+        <v>11.3</v>
+      </c>
+      <c r="E146" t="s">
+        <v>247</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>8</v>
+      </c>
+      <c r="H146">
+        <v>17</v>
+      </c>
+      <c r="I146">
+        <v>17</v>
+      </c>
+      <c r="J146">
+        <v>17</v>
+      </c>
+      <c r="K146">
+        <v>9</v>
+      </c>
+      <c r="L146">
+        <v>4</v>
+      </c>
+      <c r="M146">
+        <v>296</v>
+      </c>
+      <c r="N146">
+        <v>2</v>
+      </c>
+      <c r="O146">
+        <v>2</v>
+      </c>
+      <c r="P146">
+        <v>2</v>
+      </c>
+      <c r="Q146">
+        <v>20</v>
+      </c>
+      <c r="R146">
+        <v>1</v>
+      </c>
+      <c r="S146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19">
+      <c r="A147" t="s">
+        <v>131</v>
+      </c>
+      <c r="B147" t="s">
+        <v>200</v>
+      </c>
+      <c r="C147">
+        <v>171</v>
+      </c>
+      <c r="D147">
+        <v>11.5</v>
+      </c>
+      <c r="E147" t="s">
+        <v>247</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>8</v>
+      </c>
+      <c r="H147">
+        <v>17</v>
+      </c>
+      <c r="I147">
+        <v>17</v>
+      </c>
+      <c r="J147">
+        <v>17</v>
+      </c>
+      <c r="K147">
+        <v>8</v>
+      </c>
+      <c r="L147">
+        <v>4</v>
+      </c>
+      <c r="M147">
+        <v>280</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147">
+        <v>2</v>
+      </c>
+      <c r="P147">
+        <v>2</v>
+      </c>
+      <c r="Q147">
+        <v>22</v>
+      </c>
+      <c r="R147">
+        <v>1</v>
+      </c>
+      <c r="S147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19">
+      <c r="A148" t="s">
+        <v>132</v>
+      </c>
+      <c r="B148" t="s">
+        <v>200</v>
+      </c>
+      <c r="C148">
+        <v>7</v>
+      </c>
+      <c r="D148">
+        <v>0.2</v>
+      </c>
+      <c r="E148" t="s">
+        <v>247</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>2</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>3</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>32</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148">
+        <v>1</v>
+      </c>
+      <c r="P148">
+        <v>1</v>
+      </c>
+      <c r="Q148">
+        <v>1</v>
+      </c>
+      <c r="R148">
+        <v>0</v>
+      </c>
+      <c r="S148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19">
+      <c r="A149" t="s">
+        <v>132</v>
+      </c>
+      <c r="B149" t="s">
+        <v>201</v>
+      </c>
+      <c r="C149">
+        <v>157</v>
+      </c>
+      <c r="D149">
+        <v>13.21</v>
+      </c>
+      <c r="E149" t="s">
+        <v>248</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>8</v>
+      </c>
+      <c r="H149">
+        <v>15</v>
+      </c>
+      <c r="I149">
+        <v>15</v>
+      </c>
+      <c r="J149">
+        <v>15</v>
+      </c>
+      <c r="K149">
+        <v>8</v>
+      </c>
+      <c r="L149">
+        <v>4</v>
+      </c>
+      <c r="M149">
+        <v>277</v>
+      </c>
+      <c r="N149">
+        <v>2</v>
+      </c>
+      <c r="O149">
+        <v>2</v>
+      </c>
+      <c r="P149">
+        <v>2</v>
+      </c>
+      <c r="Q149">
+        <v>20</v>
+      </c>
+      <c r="R149">
+        <v>1</v>
+      </c>
+      <c r="S149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19">
+      <c r="A150" t="s">
+        <v>133</v>
+      </c>
+      <c r="B150" t="s">
+        <v>201</v>
+      </c>
+      <c r="C150">
+        <v>72</v>
+      </c>
+      <c r="D150">
+        <v>5.32</v>
+      </c>
+      <c r="E150" t="s">
+        <v>248</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>4</v>
+      </c>
+      <c r="H150">
+        <v>8</v>
+      </c>
+      <c r="I150">
+        <v>8</v>
+      </c>
+      <c r="J150">
+        <v>8</v>
+      </c>
+      <c r="K150">
+        <v>4</v>
+      </c>
+      <c r="L150">
+        <v>2</v>
+      </c>
+      <c r="M150">
+        <v>144</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150">
+        <v>1</v>
+      </c>
+      <c r="P150">
+        <v>1</v>
+      </c>
+      <c r="Q150">
+        <v>5</v>
+      </c>
+      <c r="R150">
+        <v>0</v>
+      </c>
+      <c r="S150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19">
+      <c r="A151" t="s">
+        <v>133</v>
+      </c>
+      <c r="B151" t="s">
+        <v>202</v>
+      </c>
+      <c r="C151">
+        <v>96</v>
+      </c>
+      <c r="D151">
+        <v>4.36</v>
+      </c>
+      <c r="E151" t="s">
+        <v>247</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>5</v>
+      </c>
+      <c r="H151">
+        <v>10</v>
+      </c>
+      <c r="I151">
+        <v>10</v>
+      </c>
+      <c r="J151">
+        <v>10</v>
+      </c>
+      <c r="K151">
+        <v>5</v>
+      </c>
+      <c r="L151">
+        <v>3</v>
+      </c>
+      <c r="M151">
+        <v>193</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151">
+        <v>1</v>
+      </c>
+      <c r="P151">
+        <v>2</v>
+      </c>
+      <c r="Q151">
+        <v>14</v>
+      </c>
+      <c r="R151">
+        <v>1</v>
+      </c>
+      <c r="S151">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19">
+      <c r="A152" t="s">
+        <v>134</v>
+      </c>
+      <c r="B152" t="s">
+        <v>203</v>
+      </c>
+      <c r="C152">
+        <v>153</v>
+      </c>
+      <c r="D152">
+        <v>13.41</v>
+      </c>
+      <c r="E152" t="s">
+        <v>247</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>9</v>
+      </c>
+      <c r="H152">
+        <v>18</v>
+      </c>
+      <c r="I152">
+        <v>18</v>
+      </c>
+      <c r="J152">
+        <v>18</v>
+      </c>
+      <c r="K152">
+        <v>9</v>
+      </c>
+      <c r="L152">
+        <v>4</v>
+      </c>
+      <c r="M152">
+        <v>365</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152">
+        <v>3</v>
+      </c>
+      <c r="P152">
+        <v>3</v>
+      </c>
+      <c r="Q152">
+        <v>21</v>
+      </c>
+      <c r="R152">
+        <v>1</v>
+      </c>
+      <c r="S152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19">
+      <c r="A153" t="s">
+        <v>135</v>
+      </c>
+      <c r="B153" t="s">
+        <v>204</v>
+      </c>
+      <c r="C153">
+        <v>111</v>
+      </c>
+      <c r="D153">
+        <v>12.74</v>
+      </c>
+      <c r="E153" t="s">
+        <v>254</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>9</v>
+      </c>
+      <c r="H153">
+        <v>10</v>
+      </c>
+      <c r="I153">
+        <v>10</v>
+      </c>
+      <c r="J153">
+        <v>10</v>
+      </c>
+      <c r="K153">
+        <v>9</v>
+      </c>
+      <c r="L153">
+        <v>4</v>
+      </c>
+      <c r="M153">
+        <v>395</v>
+      </c>
+      <c r="N153">
+        <v>3</v>
+      </c>
+      <c r="O153">
+        <v>3</v>
+      </c>
+      <c r="P153">
+        <v>3</v>
+      </c>
+      <c r="Q153">
+        <v>21</v>
+      </c>
+      <c r="R153">
+        <v>1</v>
+      </c>
+      <c r="S153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19">
+      <c r="A154" t="s">
+        <v>136</v>
+      </c>
+      <c r="B154" t="s">
+        <v>205</v>
+      </c>
+      <c r="C154">
+        <v>199</v>
+      </c>
+      <c r="D154">
+        <v>17.62</v>
+      </c>
+      <c r="E154" t="s">
+        <v>247</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>9</v>
+      </c>
+      <c r="H154">
+        <v>10</v>
+      </c>
+      <c r="I154">
+        <v>10</v>
+      </c>
+      <c r="J154">
+        <v>10</v>
+      </c>
+      <c r="K154">
+        <v>9</v>
+      </c>
+      <c r="L154">
+        <v>6</v>
+      </c>
+      <c r="M154">
+        <v>365</v>
+      </c>
+      <c r="N154">
+        <v>4</v>
+      </c>
+      <c r="O154">
+        <v>3</v>
+      </c>
+      <c r="P154">
+        <v>3</v>
+      </c>
+      <c r="Q154">
+        <v>21</v>
+      </c>
+      <c r="R154">
+        <v>1</v>
+      </c>
+      <c r="S154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19">
+      <c r="A155" t="s">
+        <v>137</v>
+      </c>
+      <c r="B155" t="s">
+        <v>206</v>
+      </c>
+      <c r="C155">
+        <v>206</v>
+      </c>
+      <c r="D155">
+        <v>18.89</v>
+      </c>
+      <c r="E155" t="s">
+        <v>248</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>9</v>
+      </c>
+      <c r="H155">
+        <v>10</v>
+      </c>
+      <c r="I155">
+        <v>10</v>
+      </c>
+      <c r="J155">
+        <v>10</v>
+      </c>
+      <c r="K155">
+        <v>9</v>
+      </c>
+      <c r="L155">
+        <v>4</v>
+      </c>
+      <c r="M155">
+        <v>362</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155">
+        <v>3</v>
+      </c>
+      <c r="P155">
+        <v>3</v>
+      </c>
+      <c r="Q155">
+        <v>21</v>
+      </c>
+      <c r="R155">
+        <v>1</v>
+      </c>
+      <c r="S155">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19">
+      <c r="A156" t="s">
+        <v>138</v>
+      </c>
+      <c r="B156" t="s">
+        <v>207</v>
+      </c>
+      <c r="C156">
+        <v>181</v>
+      </c>
+      <c r="D156">
+        <v>16.74</v>
+      </c>
+      <c r="E156" t="s">
+        <v>245</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>9</v>
+      </c>
+      <c r="H156">
+        <v>19</v>
+      </c>
+      <c r="I156">
+        <v>19</v>
+      </c>
+      <c r="J156">
+        <v>19</v>
+      </c>
+      <c r="K156">
+        <v>9</v>
+      </c>
+      <c r="L156">
+        <v>4</v>
+      </c>
+      <c r="M156">
+        <v>371</v>
+      </c>
+      <c r="N156">
+        <v>2</v>
+      </c>
+      <c r="O156">
+        <v>3</v>
+      </c>
+      <c r="P156">
+        <v>3</v>
+      </c>
+      <c r="Q156">
+        <v>16</v>
+      </c>
+      <c r="R156">
+        <v>1</v>
+      </c>
+      <c r="S156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19">
+      <c r="A157" t="s">
+        <v>138</v>
+      </c>
+      <c r="B157" t="s">
+        <v>208</v>
+      </c>
+      <c r="C157">
+        <v>5</v>
+      </c>
+      <c r="D157">
+        <v>0.1</v>
+      </c>
+      <c r="E157" t="s">
+        <v>245</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>10</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+      <c r="Q157">
+        <v>0</v>
+      </c>
+      <c r="R157">
+        <v>0</v>
+      </c>
+      <c r="S157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
+      <c r="A158" t="s">
+        <v>139</v>
+      </c>
+      <c r="B158" t="s">
+        <v>209</v>
+      </c>
+      <c r="C158">
+        <v>57</v>
+      </c>
+      <c r="D158">
+        <v>3.42</v>
+      </c>
+      <c r="E158" t="s">
+        <v>248</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>5</v>
+      </c>
+      <c r="H158">
+        <v>9</v>
+      </c>
+      <c r="I158">
+        <v>7</v>
+      </c>
+      <c r="J158">
+        <v>7</v>
+      </c>
+      <c r="K158">
+        <v>5</v>
+      </c>
+      <c r="L158">
+        <v>2</v>
+      </c>
+      <c r="M158">
+        <v>161</v>
+      </c>
+      <c r="N158">
+        <v>3</v>
+      </c>
+      <c r="O158">
+        <v>2</v>
+      </c>
+      <c r="P158">
+        <v>2</v>
+      </c>
+      <c r="Q158">
+        <v>17</v>
+      </c>
+      <c r="R158">
+        <v>1</v>
+      </c>
+      <c r="S158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
+      <c r="A159" t="s">
+        <v>140</v>
+      </c>
+      <c r="B159" t="s">
+        <v>210</v>
+      </c>
+      <c r="C159">
+        <v>116</v>
+      </c>
+      <c r="D159">
+        <v>11.36</v>
+      </c>
+      <c r="E159" t="s">
+        <v>245</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>6</v>
+      </c>
+      <c r="H159">
+        <v>12</v>
+      </c>
+      <c r="I159">
+        <v>12</v>
+      </c>
+      <c r="J159">
+        <v>12</v>
+      </c>
+      <c r="K159">
+        <v>6</v>
+      </c>
+      <c r="L159">
+        <v>4</v>
+      </c>
+      <c r="M159">
+        <v>240</v>
+      </c>
+      <c r="N159">
+        <v>2</v>
+      </c>
+      <c r="O159">
+        <v>2</v>
+      </c>
+      <c r="P159">
+        <v>2</v>
+      </c>
+      <c r="Q159">
+        <v>14</v>
+      </c>
+      <c r="R159">
+        <v>1</v>
+      </c>
+      <c r="S159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
+      <c r="A160" t="s">
+        <v>140</v>
+      </c>
+      <c r="B160" t="s">
+        <v>211</v>
+      </c>
+      <c r="C160">
+        <v>59</v>
+      </c>
+      <c r="D160">
+        <v>4.3</v>
+      </c>
+      <c r="E160" t="s">
+        <v>245</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>3</v>
+      </c>
+      <c r="H160">
+        <v>6</v>
+      </c>
+      <c r="I160">
+        <v>4</v>
+      </c>
+      <c r="J160">
+        <v>6</v>
+      </c>
+      <c r="K160">
+        <v>3</v>
+      </c>
+      <c r="L160">
+        <v>2</v>
+      </c>
+      <c r="M160">
+        <v>125</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160">
+        <v>1</v>
+      </c>
+      <c r="P160">
+        <v>1</v>
+      </c>
+      <c r="Q160">
+        <v>7</v>
+      </c>
+      <c r="R160">
+        <v>1</v>
+      </c>
+      <c r="S160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19">
+      <c r="A161" t="s">
+        <v>141</v>
+      </c>
+      <c r="B161" t="s">
+        <v>210</v>
+      </c>
+      <c r="C161">
+        <v>118</v>
+      </c>
+      <c r="D161">
+        <v>9.32</v>
+      </c>
+      <c r="E161" t="s">
+        <v>245</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>9</v>
+      </c>
+      <c r="H161">
+        <v>10</v>
+      </c>
+      <c r="I161">
+        <v>10</v>
+      </c>
+      <c r="J161">
+        <v>10</v>
+      </c>
+      <c r="K161">
+        <v>9</v>
+      </c>
+      <c r="L161">
+        <v>3</v>
+      </c>
+      <c r="M161">
+        <v>360</v>
+      </c>
+      <c r="N161">
+        <v>3</v>
+      </c>
+      <c r="O161">
+        <v>3</v>
+      </c>
+      <c r="P161">
+        <v>3</v>
+      </c>
+      <c r="Q161">
+        <v>20</v>
+      </c>
+      <c r="R161">
+        <v>1</v>
+      </c>
+      <c r="S161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19">
+      <c r="A162" t="s">
+        <v>142</v>
+      </c>
+      <c r="B162" t="s">
+        <v>212</v>
+      </c>
+      <c r="C162">
+        <v>58</v>
+      </c>
+      <c r="D162">
+        <v>4.12</v>
+      </c>
+      <c r="E162" t="s">
+        <v>245</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>8</v>
+      </c>
+      <c r="H162">
+        <v>6</v>
+      </c>
+      <c r="I162">
+        <v>6</v>
+      </c>
+      <c r="J162">
+        <v>6</v>
+      </c>
+      <c r="K162">
+        <v>5</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>196</v>
+      </c>
+      <c r="N162">
+        <v>3</v>
+      </c>
+      <c r="O162">
+        <v>4</v>
+      </c>
+      <c r="P162">
+        <v>3</v>
+      </c>
+      <c r="Q162">
+        <v>20</v>
+      </c>
+      <c r="R162">
+        <v>1</v>
+      </c>
+      <c r="S162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19">
+      <c r="A163" t="s">
+        <v>143</v>
+      </c>
+      <c r="B163" t="s">
+        <v>213</v>
+      </c>
+      <c r="C163">
+        <v>105</v>
+      </c>
+      <c r="D163">
+        <v>10.21</v>
+      </c>
+      <c r="E163" t="s">
+        <v>248</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>6</v>
+      </c>
+      <c r="H163">
+        <v>12</v>
+      </c>
+      <c r="I163">
+        <v>13</v>
+      </c>
+      <c r="J163">
+        <v>13</v>
+      </c>
+      <c r="K163">
+        <v>6</v>
+      </c>
+      <c r="L163">
+        <v>2</v>
+      </c>
+      <c r="M163">
+        <v>248</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163">
+        <v>2</v>
+      </c>
+      <c r="P163">
+        <v>2</v>
+      </c>
+      <c r="Q163">
+        <v>12</v>
+      </c>
+      <c r="R163">
+        <v>1</v>
+      </c>
+      <c r="S163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19">
+      <c r="A164" t="s">
+        <v>143</v>
+      </c>
+      <c r="B164" t="s">
+        <v>214</v>
+      </c>
+      <c r="C164">
+        <v>49</v>
+      </c>
+      <c r="D164">
+        <v>3.65</v>
+      </c>
+      <c r="E164" t="s">
+        <v>248</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>3</v>
+      </c>
+      <c r="H164">
+        <v>7</v>
+      </c>
+      <c r="I164">
+        <v>6</v>
+      </c>
+      <c r="J164">
+        <v>6</v>
+      </c>
+      <c r="K164">
+        <v>3</v>
+      </c>
+      <c r="L164">
+        <v>2</v>
+      </c>
+      <c r="M164">
+        <v>125</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164">
+        <v>1</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
+      </c>
+      <c r="Q164">
+        <v>8</v>
+      </c>
+      <c r="R164">
+        <v>0</v>
+      </c>
+      <c r="S164">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19">
+      <c r="A165" t="s">
+        <v>144</v>
+      </c>
+      <c r="B165" t="s">
+        <v>215</v>
+      </c>
+      <c r="C165">
+        <v>141</v>
+      </c>
+      <c r="D165">
+        <v>9.65</v>
+      </c>
+      <c r="E165" t="s">
+        <v>248</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165">
+        <v>9</v>
+      </c>
+      <c r="H165">
+        <v>18</v>
+      </c>
+      <c r="I165">
+        <v>18</v>
+      </c>
+      <c r="J165">
+        <v>18</v>
+      </c>
+      <c r="K165">
+        <v>10</v>
+      </c>
+      <c r="L165">
+        <v>3</v>
+      </c>
+      <c r="M165">
+        <v>302</v>
+      </c>
+      <c r="N165">
+        <v>2</v>
+      </c>
+      <c r="O165">
+        <v>2</v>
+      </c>
+      <c r="P165">
+        <v>2</v>
+      </c>
+      <c r="Q165">
+        <v>20</v>
+      </c>
+      <c r="R165">
+        <v>1</v>
+      </c>
+      <c r="S165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19">
+      <c r="A166" t="s">
+        <v>145</v>
+      </c>
+      <c r="B166" t="s">
+        <v>215</v>
+      </c>
+      <c r="C166">
+        <v>180</v>
+      </c>
+      <c r="D166">
+        <v>14.98</v>
+      </c>
+      <c r="E166" t="s">
+        <v>247</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166">
+        <v>9</v>
+      </c>
+      <c r="H166">
+        <v>18</v>
+      </c>
+      <c r="I166">
+        <v>17</v>
+      </c>
+      <c r="J166">
+        <v>18</v>
+      </c>
+      <c r="K166">
+        <v>9</v>
+      </c>
+      <c r="L166">
+        <v>5</v>
+      </c>
+      <c r="M166">
+        <v>313</v>
+      </c>
+      <c r="N166">
+        <v>3</v>
+      </c>
+      <c r="O166">
+        <v>3</v>
+      </c>
+      <c r="P166">
+        <v>3</v>
+      </c>
+      <c r="Q166">
+        <v>21</v>
+      </c>
+      <c r="R166">
+        <v>1</v>
+      </c>
+      <c r="S166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19">
+      <c r="A167" t="s">
+        <v>146</v>
+      </c>
+      <c r="B167" t="s">
+        <v>216</v>
+      </c>
+      <c r="C167">
+        <v>193</v>
+      </c>
+      <c r="D167">
+        <v>14.38</v>
+      </c>
+      <c r="E167" t="s">
+        <v>248</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <v>9</v>
+      </c>
+      <c r="H167">
+        <v>19</v>
+      </c>
+      <c r="I167">
+        <v>19</v>
+      </c>
+      <c r="J167">
+        <v>19</v>
+      </c>
+      <c r="K167">
+        <v>10</v>
+      </c>
+      <c r="L167">
+        <v>5</v>
+      </c>
+      <c r="M167">
+        <v>379</v>
+      </c>
+      <c r="N167">
+        <v>4</v>
+      </c>
+      <c r="O167">
+        <v>2</v>
+      </c>
+      <c r="P167">
+        <v>3</v>
+      </c>
+      <c r="Q167">
+        <v>20</v>
+      </c>
+      <c r="R167">
+        <v>1</v>
+      </c>
+      <c r="S167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19">
+      <c r="A168" t="s">
+        <v>147</v>
+      </c>
+      <c r="B168" t="s">
+        <v>217</v>
+      </c>
+      <c r="C168">
+        <v>116</v>
+      </c>
+      <c r="D168">
+        <v>11.32</v>
+      </c>
+      <c r="E168" t="s">
+        <v>247</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>8</v>
+      </c>
+      <c r="H168">
+        <v>9</v>
+      </c>
+      <c r="I168">
+        <v>9</v>
+      </c>
+      <c r="J168">
+        <v>9</v>
+      </c>
+      <c r="K168">
+        <v>8</v>
+      </c>
+      <c r="L168">
+        <v>4</v>
+      </c>
+      <c r="M168">
+        <v>236</v>
+      </c>
+      <c r="N168">
+        <v>4</v>
+      </c>
+      <c r="O168">
+        <v>3</v>
+      </c>
+      <c r="P168">
+        <v>3</v>
+      </c>
+      <c r="Q168">
+        <v>20</v>
+      </c>
+      <c r="R168">
+        <v>1</v>
+      </c>
+      <c r="S168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19">
+      <c r="A169" t="s">
+        <v>148</v>
+      </c>
+      <c r="B169" t="s">
+        <v>218</v>
+      </c>
+      <c r="C169">
+        <v>159</v>
+      </c>
+      <c r="D169">
+        <v>15.32</v>
+      </c>
+      <c r="E169" t="s">
+        <v>247</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>7</v>
+      </c>
+      <c r="H169">
+        <v>17</v>
+      </c>
+      <c r="I169">
+        <v>17</v>
+      </c>
+      <c r="J169">
+        <v>17</v>
+      </c>
+      <c r="K169">
+        <v>7</v>
+      </c>
+      <c r="L169">
+        <v>3</v>
+      </c>
+      <c r="M169">
+        <v>262</v>
+      </c>
+      <c r="N169">
+        <v>2</v>
+      </c>
+      <c r="O169">
+        <v>2</v>
+      </c>
+      <c r="P169">
+        <v>2</v>
+      </c>
+      <c r="Q169">
+        <v>18</v>
+      </c>
+      <c r="R169">
+        <v>1</v>
+      </c>
+      <c r="S169">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19">
+      <c r="A170" t="s">
+        <v>148</v>
+      </c>
+      <c r="B170" t="s">
+        <v>217</v>
+      </c>
+      <c r="C170">
+        <v>26</v>
+      </c>
+      <c r="D170">
+        <v>0.9</v>
+      </c>
+      <c r="E170" t="s">
+        <v>247</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>2</v>
+      </c>
+      <c r="H170">
+        <v>4</v>
+      </c>
+      <c r="I170">
+        <v>3</v>
+      </c>
+      <c r="J170">
+        <v>4</v>
+      </c>
+      <c r="K170">
+        <v>2</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>72</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170">
+        <v>1</v>
+      </c>
+      <c r="P170">
+        <v>1</v>
+      </c>
+      <c r="Q170">
+        <v>2</v>
+      </c>
+      <c r="R170">
+        <v>0</v>
+      </c>
+      <c r="S170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19">
+      <c r="A171" t="s">
         <v>149</v>
       </c>
-      <c r="C144" t="s">
+      <c r="B171" t="s">
+        <v>217</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+      <c r="D171">
+        <v>0.12</v>
+      </c>
+      <c r="E171" t="s">
+        <v>247</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>6</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
+      </c>
+      <c r="S171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19">
+      <c r="A172" t="s">
+        <v>149</v>
+      </c>
+      <c r="B172" t="s">
+        <v>219</v>
+      </c>
+      <c r="C172">
+        <v>171</v>
+      </c>
+      <c r="D172">
+        <v>17.32</v>
+      </c>
+      <c r="E172" t="s">
+        <v>254</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
+        <v>9</v>
+      </c>
+      <c r="H172">
+        <v>18</v>
+      </c>
+      <c r="I172">
+        <v>18</v>
+      </c>
+      <c r="J172">
+        <v>17</v>
+      </c>
+      <c r="K172">
+        <v>9</v>
+      </c>
+      <c r="L172">
+        <v>4</v>
+      </c>
+      <c r="M172">
+        <v>376</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172">
+        <v>3</v>
+      </c>
+      <c r="P172">
+        <v>3</v>
+      </c>
+      <c r="Q172">
+        <v>21</v>
+      </c>
+      <c r="R172">
+        <v>1</v>
+      </c>
+      <c r="S172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19">
+      <c r="A173" t="s">
         <v>150</v>
       </c>
-      <c r="D144" t="s">
+      <c r="B173" t="s">
+        <v>220</v>
+      </c>
+      <c r="C173">
+        <v>142</v>
+      </c>
+      <c r="D173">
+        <v>11.98</v>
+      </c>
+      <c r="E173" t="s">
+        <v>245</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173">
+        <v>9</v>
+      </c>
+      <c r="H173">
+        <v>18</v>
+      </c>
+      <c r="I173">
+        <v>17</v>
+      </c>
+      <c r="J173">
+        <v>18</v>
+      </c>
+      <c r="K173">
+        <v>9</v>
+      </c>
+      <c r="L173">
+        <v>4</v>
+      </c>
+      <c r="M173">
+        <v>273</v>
+      </c>
+      <c r="N173">
+        <v>3</v>
+      </c>
+      <c r="O173">
+        <v>3</v>
+      </c>
+      <c r="P173">
+        <v>3</v>
+      </c>
+      <c r="Q173">
+        <v>21</v>
+      </c>
+      <c r="R173">
+        <v>1</v>
+      </c>
+      <c r="S173">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19">
+      <c r="A174" t="s">
         <v>151</v>
       </c>
-      <c r="E144" t="s">
+      <c r="B174" t="s">
+        <v>221</v>
+      </c>
+      <c r="C174">
+        <v>103</v>
+      </c>
+      <c r="D174">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="E174" t="s">
+        <v>248</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174">
+        <v>9</v>
+      </c>
+      <c r="H174">
+        <v>10</v>
+      </c>
+      <c r="I174">
+        <v>10</v>
+      </c>
+      <c r="J174">
+        <v>10</v>
+      </c>
+      <c r="K174">
+        <v>10</v>
+      </c>
+      <c r="L174">
+        <v>3</v>
+      </c>
+      <c r="M174">
+        <v>290</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174">
+        <v>3</v>
+      </c>
+      <c r="P174">
+        <v>3</v>
+      </c>
+      <c r="Q174">
+        <v>21</v>
+      </c>
+      <c r="R174">
+        <v>1</v>
+      </c>
+      <c r="S174">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19">
+      <c r="A175" t="s">
+        <v>152</v>
+      </c>
+      <c r="B175" t="s">
+        <v>222</v>
+      </c>
+      <c r="C175">
+        <v>11</v>
+      </c>
+      <c r="D175">
+        <v>0.32</v>
+      </c>
+      <c r="E175" t="s">
+        <v>247</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>2</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175">
+        <v>2</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>22</v>
+      </c>
+      <c r="N175">
+        <v>1</v>
+      </c>
+      <c r="O175">
+        <v>1</v>
+      </c>
+      <c r="P175">
+        <v>1</v>
+      </c>
+      <c r="Q175">
+        <v>3</v>
+      </c>
+      <c r="R175">
+        <v>1</v>
+      </c>
+      <c r="S175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19">
+      <c r="A176" t="s">
         <v>153</v>
       </c>
-      <c r="F144" t="s">
+      <c r="B176" t="s">
+        <v>223</v>
+      </c>
+      <c r="C176">
+        <v>204</v>
+      </c>
+      <c r="D176">
+        <v>20.89</v>
+      </c>
+      <c r="E176" t="s">
+        <v>247</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176">
+        <v>9</v>
+      </c>
+      <c r="H176">
+        <v>19</v>
+      </c>
+      <c r="I176">
+        <v>19</v>
+      </c>
+      <c r="J176">
+        <v>19</v>
+      </c>
+      <c r="K176">
+        <v>10</v>
+      </c>
+      <c r="L176">
+        <v>4</v>
+      </c>
+      <c r="M176">
+        <v>340</v>
+      </c>
+      <c r="N176">
+        <v>4</v>
+      </c>
+      <c r="O176">
+        <v>4</v>
+      </c>
+      <c r="P176">
+        <v>3</v>
+      </c>
+      <c r="Q176">
+        <v>21</v>
+      </c>
+      <c r="R176">
+        <v>1</v>
+      </c>
+      <c r="S176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19">
+      <c r="A177" t="s">
+        <v>154</v>
+      </c>
+      <c r="B177" t="s">
+        <v>224</v>
+      </c>
+      <c r="C177">
+        <v>186</v>
+      </c>
+      <c r="D177">
+        <v>13.65</v>
+      </c>
+      <c r="E177" t="s">
+        <v>245</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>9</v>
+      </c>
+      <c r="H177">
+        <v>19</v>
+      </c>
+      <c r="I177">
+        <v>19</v>
+      </c>
+      <c r="J177">
+        <v>19</v>
+      </c>
+      <c r="K177">
+        <v>10</v>
+      </c>
+      <c r="L177">
+        <v>4</v>
+      </c>
+      <c r="M177">
+        <v>338</v>
+      </c>
+      <c r="N177">
+        <v>3</v>
+      </c>
+      <c r="O177">
+        <v>4</v>
+      </c>
+      <c r="P177">
+        <v>3</v>
+      </c>
+      <c r="Q177">
+        <v>21</v>
+      </c>
+      <c r="R177">
+        <v>1</v>
+      </c>
+      <c r="S177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19">
+      <c r="A178" t="s">
+        <v>154</v>
+      </c>
+      <c r="B178" t="s">
+        <v>222</v>
+      </c>
+      <c r="C178">
+        <v>5</v>
+      </c>
+      <c r="D178">
+        <v>0.32</v>
+      </c>
+      <c r="E178" t="s">
+        <v>247</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>15</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+      <c r="Q178">
+        <v>0</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+      <c r="S178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19">
+      <c r="A179" t="s">
+        <v>155</v>
+      </c>
+      <c r="B179" t="s">
+        <v>225</v>
+      </c>
+      <c r="C179">
+        <v>190</v>
+      </c>
+      <c r="D179">
+        <v>16.27</v>
+      </c>
+      <c r="E179" t="s">
+        <v>245</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>10</v>
+      </c>
+      <c r="H179">
+        <v>19</v>
+      </c>
+      <c r="I179">
+        <v>19</v>
+      </c>
+      <c r="J179">
+        <v>19</v>
+      </c>
+      <c r="K179">
+        <v>10</v>
+      </c>
+      <c r="L179">
+        <v>5</v>
+      </c>
+      <c r="M179">
+        <v>340</v>
+      </c>
+      <c r="N179">
+        <v>4</v>
+      </c>
+      <c r="O179">
+        <v>3</v>
+      </c>
+      <c r="P179">
+        <v>3</v>
+      </c>
+      <c r="Q179">
+        <v>12</v>
+      </c>
+      <c r="R179">
+        <v>1</v>
+      </c>
+      <c r="S179">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19">
+      <c r="A180" t="s">
+        <v>156</v>
+      </c>
+      <c r="B180" t="s">
+        <v>225</v>
+      </c>
+      <c r="C180">
+        <v>125</v>
+      </c>
+      <c r="D180">
+        <v>15.32</v>
+      </c>
+      <c r="E180" t="s">
+        <v>245</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>9</v>
+      </c>
+      <c r="H180">
+        <v>19</v>
+      </c>
+      <c r="I180">
+        <v>19</v>
+      </c>
+      <c r="J180">
+        <v>19</v>
+      </c>
+      <c r="K180">
+        <v>9</v>
+      </c>
+      <c r="L180">
+        <v>3</v>
+      </c>
+      <c r="M180">
+        <v>234</v>
+      </c>
+      <c r="N180">
+        <v>5</v>
+      </c>
+      <c r="O180">
+        <v>3</v>
+      </c>
+      <c r="P180">
+        <v>3</v>
+      </c>
+      <c r="Q180">
+        <v>21</v>
+      </c>
+      <c r="R180">
+        <v>1</v>
+      </c>
+      <c r="S180">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19">
+      <c r="A181" t="s">
+        <v>157</v>
+      </c>
+      <c r="B181" t="s">
+        <v>222</v>
+      </c>
+      <c r="C181">
+        <v>59</v>
+      </c>
+      <c r="D181">
+        <v>3.54</v>
+      </c>
+      <c r="E181" t="s">
+        <v>247</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>5</v>
+      </c>
+      <c r="H181">
+        <v>10</v>
+      </c>
+      <c r="I181">
+        <v>10</v>
+      </c>
+      <c r="J181">
+        <v>10</v>
+      </c>
+      <c r="K181">
+        <v>5</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>132</v>
+      </c>
+      <c r="N181">
+        <v>2</v>
+      </c>
+      <c r="O181">
+        <v>2</v>
+      </c>
+      <c r="P181">
+        <v>2</v>
+      </c>
+      <c r="Q181">
+        <v>14</v>
+      </c>
+      <c r="R181">
+        <v>1</v>
+      </c>
+      <c r="S181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19">
+      <c r="A182" t="s">
+        <v>158</v>
+      </c>
+      <c r="B182" t="s">
+        <v>222</v>
+      </c>
+      <c r="C182">
+        <v>27</v>
+      </c>
+      <c r="D182">
+        <v>1.21</v>
+      </c>
+      <c r="E182" t="s">
+        <v>247</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>3</v>
+      </c>
+      <c r="H182">
+        <v>5</v>
+      </c>
+      <c r="I182">
+        <v>3</v>
+      </c>
+      <c r="J182">
+        <v>4</v>
+      </c>
+      <c r="K182">
+        <v>3</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>75</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182">
+        <v>1</v>
+      </c>
+      <c r="P182">
+        <v>1</v>
+      </c>
+      <c r="Q182">
+        <v>11</v>
+      </c>
+      <c r="R182">
+        <v>1</v>
+      </c>
+      <c r="S182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19">
+      <c r="A183" t="s">
+        <v>159</v>
+      </c>
+      <c r="B183" t="s">
+        <v>226</v>
+      </c>
+      <c r="C183">
+        <v>54</v>
+      </c>
+      <c r="D183">
+        <v>3.17</v>
+      </c>
+      <c r="E183" t="s">
+        <v>245</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>5</v>
+      </c>
+      <c r="H183">
+        <v>6</v>
+      </c>
+      <c r="I183">
+        <v>6</v>
+      </c>
+      <c r="J183">
+        <v>6</v>
+      </c>
+      <c r="K183">
+        <v>5</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>186</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183">
+        <v>3</v>
+      </c>
+      <c r="P183">
+        <v>2</v>
+      </c>
+      <c r="Q183">
+        <v>14</v>
+      </c>
+      <c r="R183">
+        <v>1</v>
+      </c>
+      <c r="S183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19">
+      <c r="A184" t="s">
+        <v>160</v>
+      </c>
+      <c r="B184" t="s">
+        <v>227</v>
+      </c>
+      <c r="C184">
+        <v>192</v>
+      </c>
+      <c r="D184">
+        <v>17.98</v>
+      </c>
+      <c r="E184" t="s">
+        <v>245</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>9</v>
+      </c>
+      <c r="H184">
+        <v>19</v>
+      </c>
+      <c r="I184">
+        <v>19</v>
+      </c>
+      <c r="J184">
+        <v>19</v>
+      </c>
+      <c r="K184">
+        <v>10</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>325</v>
+      </c>
+      <c r="N184">
+        <v>5</v>
+      </c>
+      <c r="O184">
+        <v>3</v>
+      </c>
+      <c r="P184">
+        <v>3</v>
+      </c>
+      <c r="Q184">
+        <v>21</v>
+      </c>
+      <c r="R184">
+        <v>1</v>
+      </c>
+      <c r="S184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19">
+      <c r="A185" t="s">
+        <v>161</v>
+      </c>
+      <c r="B185" t="s">
+        <v>228</v>
+      </c>
+      <c r="C185">
+        <v>67</v>
+      </c>
+      <c r="D185">
+        <v>4.35</v>
+      </c>
+      <c r="E185" t="s">
+        <v>248</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>7</v>
+      </c>
+      <c r="H185">
+        <v>10</v>
+      </c>
+      <c r="I185">
+        <v>7</v>
+      </c>
+      <c r="J185">
+        <v>9</v>
+      </c>
+      <c r="K185">
+        <v>7</v>
+      </c>
+      <c r="L185">
+        <v>3</v>
+      </c>
+      <c r="M185">
+        <v>213</v>
+      </c>
+      <c r="N185">
+        <v>5</v>
+      </c>
+      <c r="O185">
+        <v>3</v>
+      </c>
+      <c r="P185">
+        <v>3</v>
+      </c>
+      <c r="Q185">
+        <v>21</v>
+      </c>
+      <c r="R185">
+        <v>1</v>
+      </c>
+      <c r="S185">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19">
+      <c r="A186" t="s">
+        <v>161</v>
+      </c>
+      <c r="B186" t="s">
+        <v>227</v>
+      </c>
+      <c r="C186">
+        <v>8</v>
+      </c>
+      <c r="D186">
+        <v>0.54</v>
+      </c>
+      <c r="E186" t="s">
+        <v>245</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>16</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+      <c r="P186">
+        <v>0</v>
+      </c>
+      <c r="Q186">
+        <v>0</v>
+      </c>
+      <c r="R186">
+        <v>0</v>
+      </c>
+      <c r="S186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19">
+      <c r="A187" t="s">
+        <v>162</v>
+      </c>
+      <c r="B187" t="s">
+        <v>229</v>
+      </c>
+      <c r="C187">
+        <v>185</v>
+      </c>
+      <c r="D187">
+        <v>16.87</v>
+      </c>
+      <c r="E187" t="s">
+        <v>248</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>9</v>
+      </c>
+      <c r="H187">
+        <v>10</v>
+      </c>
+      <c r="I187">
+        <v>10</v>
+      </c>
+      <c r="J187">
+        <v>10</v>
+      </c>
+      <c r="K187">
+        <v>9</v>
+      </c>
+      <c r="L187">
+        <v>3</v>
+      </c>
+      <c r="M187">
+        <v>365</v>
+      </c>
+      <c r="N187">
+        <v>4</v>
+      </c>
+      <c r="O187">
+        <v>3</v>
+      </c>
+      <c r="P187">
+        <v>3</v>
+      </c>
+      <c r="Q187">
+        <v>21</v>
+      </c>
+      <c r="R187">
+        <v>1</v>
+      </c>
+      <c r="S187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19">
+      <c r="A188" t="s">
+        <v>163</v>
+      </c>
+      <c r="B188" t="s">
+        <v>230</v>
+      </c>
+      <c r="C188">
+        <v>181</v>
+      </c>
+      <c r="D188">
+        <v>21.5</v>
+      </c>
+      <c r="E188" t="s">
+        <v>248</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>9</v>
+      </c>
+      <c r="H188">
+        <v>19</v>
+      </c>
+      <c r="I188">
+        <v>19</v>
+      </c>
+      <c r="J188">
+        <v>19</v>
+      </c>
+      <c r="K188">
+        <v>10</v>
+      </c>
+      <c r="L188">
+        <v>7</v>
+      </c>
+      <c r="M188">
+        <v>387</v>
+      </c>
+      <c r="N188">
+        <v>5</v>
+      </c>
+      <c r="O188">
+        <v>4</v>
+      </c>
+      <c r="P188">
+        <v>3</v>
+      </c>
+      <c r="Q188">
+        <v>21</v>
+      </c>
+      <c r="R188">
+        <v>1</v>
+      </c>
+      <c r="S188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19">
+      <c r="A189" t="s">
+        <v>164</v>
+      </c>
+      <c r="B189" t="s">
+        <v>231</v>
+      </c>
+      <c r="C189">
+        <v>178</v>
+      </c>
+      <c r="D189">
+        <v>20.21</v>
+      </c>
+      <c r="E189" t="s">
+        <v>248</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>9</v>
+      </c>
+      <c r="H189">
+        <v>19</v>
+      </c>
+      <c r="I189">
+        <v>19</v>
+      </c>
+      <c r="J189">
+        <v>19</v>
+      </c>
+      <c r="K189">
+        <v>10</v>
+      </c>
+      <c r="L189">
+        <v>4</v>
+      </c>
+      <c r="M189">
+        <v>352</v>
+      </c>
+      <c r="N189">
+        <v>4</v>
+      </c>
+      <c r="O189">
+        <v>3</v>
+      </c>
+      <c r="P189">
+        <v>3</v>
+      </c>
+      <c r="Q189">
+        <v>23</v>
+      </c>
+      <c r="R189">
+        <v>1</v>
+      </c>
+      <c r="S189">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19">
+      <c r="A190" t="s">
+        <v>165</v>
+      </c>
+      <c r="B190" t="s">
+        <v>231</v>
+      </c>
+      <c r="C190">
+        <v>165</v>
+      </c>
+      <c r="D190">
+        <v>17.54</v>
+      </c>
+      <c r="E190" t="s">
+        <v>248</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190">
+        <v>9</v>
+      </c>
+      <c r="H190">
+        <v>19</v>
+      </c>
+      <c r="I190">
+        <v>19</v>
+      </c>
+      <c r="J190">
+        <v>19</v>
+      </c>
+      <c r="K190">
+        <v>9</v>
+      </c>
+      <c r="L190">
+        <v>4</v>
+      </c>
+      <c r="M190">
+        <v>350</v>
+      </c>
+      <c r="N190">
+        <v>4</v>
+      </c>
+      <c r="O190">
+        <v>3</v>
+      </c>
+      <c r="P190">
+        <v>3</v>
+      </c>
+      <c r="Q190">
+        <v>21</v>
+      </c>
+      <c r="R190">
+        <v>1</v>
+      </c>
+      <c r="S190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19">
+      <c r="A191" t="s">
+        <v>166</v>
+      </c>
+      <c r="B191" t="s">
+        <v>232</v>
+      </c>
+      <c r="C191">
+        <v>138</v>
+      </c>
+      <c r="D191">
+        <v>15.32</v>
+      </c>
+      <c r="E191" t="s">
+        <v>248</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>7</v>
+      </c>
+      <c r="H191">
+        <v>15</v>
+      </c>
+      <c r="I191">
+        <v>15</v>
+      </c>
+      <c r="J191">
+        <v>15</v>
+      </c>
+      <c r="K191">
+        <v>8</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>277</v>
+      </c>
+      <c r="N191">
+        <v>3</v>
+      </c>
+      <c r="O191">
+        <v>2</v>
+      </c>
+      <c r="P191">
+        <v>2</v>
+      </c>
+      <c r="Q191">
+        <v>13</v>
+      </c>
+      <c r="R191">
+        <v>1</v>
+      </c>
+      <c r="S191">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19">
+      <c r="A192" t="s">
         <v>167</v>
       </c>
-      <c r="G144" t="s">
+      <c r="B192" t="s">
+        <v>233</v>
+      </c>
+      <c r="C192">
+        <v>36</v>
+      </c>
+      <c r="D192">
+        <v>3.21</v>
+      </c>
+      <c r="E192" t="s">
+        <v>245</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>4</v>
+      </c>
+      <c r="H192">
+        <v>8</v>
+      </c>
+      <c r="I192">
+        <v>8</v>
+      </c>
+      <c r="J192">
+        <v>8</v>
+      </c>
+      <c r="K192">
+        <v>4</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>73</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192">
+        <v>1</v>
+      </c>
+      <c r="P192">
+        <v>1</v>
+      </c>
+      <c r="Q192">
+        <v>8</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+      <c r="S192">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19">
+      <c r="A193" t="s">
         <v>168</v>
       </c>
-      <c r="H144" t="s">
+      <c r="B193" t="s">
+        <v>233</v>
+      </c>
+      <c r="C193">
+        <v>119</v>
+      </c>
+      <c r="D193">
+        <v>18.32</v>
+      </c>
+      <c r="E193" t="s">
+        <v>245</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193">
+        <v>7</v>
+      </c>
+      <c r="H193">
+        <v>14</v>
+      </c>
+      <c r="I193">
+        <v>14</v>
+      </c>
+      <c r="J193">
+        <v>14</v>
+      </c>
+      <c r="K193">
+        <v>7</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>224</v>
+      </c>
+      <c r="N193">
+        <v>2</v>
+      </c>
+      <c r="O193">
+        <v>2</v>
+      </c>
+      <c r="P193">
+        <v>1</v>
+      </c>
+      <c r="Q193">
+        <v>16</v>
+      </c>
+      <c r="R193">
+        <v>1</v>
+      </c>
+      <c r="S193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19">
+      <c r="A194" t="s">
         <v>169</v>
       </c>
-      <c r="I144" t="s">
-        <v>169</v>
-      </c>
-      <c r="J144" t="s">
-        <v>169</v>
-      </c>
-      <c r="K144" t="s">
+      <c r="B194" t="s">
+        <v>233</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194">
+        <v>0.04</v>
+      </c>
+      <c r="E194" t="s">
+        <v>245</v>
+      </c>
+      <c r="F194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>3</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+      <c r="P194">
+        <v>0</v>
+      </c>
+      <c r="Q194">
+        <v>0</v>
+      </c>
+      <c r="R194">
+        <v>0</v>
+      </c>
+      <c r="S194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19">
+      <c r="A195" t="s">
         <v>170</v>
       </c>
-      <c r="L144" t="s">
+      <c r="B195" t="s">
+        <v>234</v>
+      </c>
+      <c r="C195">
+        <v>177</v>
+      </c>
+      <c r="D195">
+        <v>17.98</v>
+      </c>
+      <c r="E195" t="s">
+        <v>247</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195">
+        <v>9</v>
+      </c>
+      <c r="H195">
+        <v>19</v>
+      </c>
+      <c r="I195">
+        <v>19</v>
+      </c>
+      <c r="J195">
+        <v>19</v>
+      </c>
+      <c r="K195">
+        <v>10</v>
+      </c>
+      <c r="L195">
+        <v>4</v>
+      </c>
+      <c r="M195">
+        <v>340</v>
+      </c>
+      <c r="N195">
+        <v>4</v>
+      </c>
+      <c r="O195">
+        <v>3</v>
+      </c>
+      <c r="P195">
+        <v>3</v>
+      </c>
+      <c r="Q195">
+        <v>21</v>
+      </c>
+      <c r="R195">
+        <v>1</v>
+      </c>
+      <c r="S195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19">
+      <c r="A196" t="s">
         <v>171</v>
       </c>
-      <c r="M144" t="s">
+      <c r="B196" t="s">
+        <v>235</v>
+      </c>
+      <c r="C196">
+        <v>118</v>
+      </c>
+      <c r="D196">
+        <v>17.34</v>
+      </c>
+      <c r="E196" t="s">
+        <v>248</v>
+      </c>
+      <c r="F196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>5</v>
+      </c>
+      <c r="H196">
+        <v>10</v>
+      </c>
+      <c r="I196">
+        <v>10</v>
+      </c>
+      <c r="J196">
+        <v>10</v>
+      </c>
+      <c r="K196">
+        <v>5</v>
+      </c>
+      <c r="L196">
+        <v>3</v>
+      </c>
+      <c r="M196">
+        <v>184</v>
+      </c>
+      <c r="N196">
+        <v>1</v>
+      </c>
+      <c r="O196">
+        <v>1</v>
+      </c>
+      <c r="P196">
+        <v>1</v>
+      </c>
+      <c r="Q196">
+        <v>12</v>
+      </c>
+      <c r="R196">
+        <v>1</v>
+      </c>
+      <c r="S196">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19">
+      <c r="A197" t="s">
+        <v>171</v>
+      </c>
+      <c r="B197" t="s">
+        <v>236</v>
+      </c>
+      <c r="C197">
+        <v>69</v>
+      </c>
+      <c r="D197">
+        <v>5.21</v>
+      </c>
+      <c r="E197" t="s">
+        <v>248</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>3</v>
+      </c>
+      <c r="H197">
+        <v>6</v>
+      </c>
+      <c r="I197">
+        <v>6</v>
+      </c>
+      <c r="J197">
+        <v>6</v>
+      </c>
+      <c r="K197">
+        <v>3</v>
+      </c>
+      <c r="L197">
+        <v>2</v>
+      </c>
+      <c r="M197">
+        <v>115</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197">
+        <v>1</v>
+      </c>
+      <c r="P197">
+        <v>1</v>
+      </c>
+      <c r="Q197">
+        <v>8</v>
+      </c>
+      <c r="R197">
+        <v>0</v>
+      </c>
+      <c r="S197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19">
+      <c r="A198" t="s">
+        <v>171</v>
+      </c>
+      <c r="B198" t="s">
+        <v>237</v>
+      </c>
+      <c r="C198">
+        <v>11</v>
+      </c>
+      <c r="D198">
+        <v>0.79</v>
+      </c>
+      <c r="E198" t="s">
+        <v>247</v>
+      </c>
+      <c r="F198">
+        <v>0</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>2</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
+        <v>2</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>22</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198">
+        <v>1</v>
+      </c>
+      <c r="P198">
+        <v>1</v>
+      </c>
+      <c r="Q198">
+        <v>0</v>
+      </c>
+      <c r="R198">
+        <v>0</v>
+      </c>
+      <c r="S198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19">
+      <c r="A199" t="s">
         <v>172</v>
       </c>
-      <c r="N144" t="s">
+      <c r="B199" t="s">
+        <v>236</v>
+      </c>
+      <c r="C199">
+        <v>44</v>
+      </c>
+      <c r="D199">
+        <v>3.24</v>
+      </c>
+      <c r="E199" t="s">
+        <v>248</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>2</v>
+      </c>
+      <c r="H199">
+        <v>4</v>
+      </c>
+      <c r="I199">
+        <v>4</v>
+      </c>
+      <c r="J199">
+        <v>4</v>
+      </c>
+      <c r="K199">
+        <v>2</v>
+      </c>
+      <c r="L199">
+        <v>2</v>
+      </c>
+      <c r="M199">
+        <v>67</v>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199">
+        <v>1</v>
+      </c>
+      <c r="P199">
+        <v>1</v>
+      </c>
+      <c r="Q199">
+        <v>4</v>
+      </c>
+      <c r="R199">
+        <v>0</v>
+      </c>
+      <c r="S199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19">
+      <c r="A200" t="s">
+        <v>172</v>
+      </c>
+      <c r="B200" t="s">
+        <v>235</v>
+      </c>
+      <c r="C200">
+        <v>21</v>
+      </c>
+      <c r="D200">
+        <v>1.17</v>
+      </c>
+      <c r="E200" t="s">
+        <v>248</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>2</v>
+      </c>
+      <c r="H200">
+        <v>5</v>
+      </c>
+      <c r="I200">
+        <v>4</v>
+      </c>
+      <c r="J200">
+        <v>4</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>65</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200">
+        <v>1</v>
+      </c>
+      <c r="P200">
+        <v>1</v>
+      </c>
+      <c r="Q200">
+        <v>0</v>
+      </c>
+      <c r="R200">
+        <v>0</v>
+      </c>
+      <c r="S200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19">
+      <c r="A201" t="s">
         <v>173</v>
       </c>
-      <c r="O144" t="s">
-        <v>173</v>
-      </c>
-      <c r="P144" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q144" t="s">
+      <c r="B201" t="s">
+        <v>238</v>
+      </c>
+      <c r="C201">
+        <v>85</v>
+      </c>
+      <c r="D201">
+        <v>7.32</v>
+      </c>
+      <c r="E201" t="s">
+        <v>248</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>9</v>
+      </c>
+      <c r="H201">
+        <v>10</v>
+      </c>
+      <c r="I201">
+        <v>10</v>
+      </c>
+      <c r="J201">
+        <v>10</v>
+      </c>
+      <c r="K201">
+        <v>9</v>
+      </c>
+      <c r="L201">
+        <v>4</v>
+      </c>
+      <c r="M201">
+        <v>239</v>
+      </c>
+      <c r="N201">
+        <v>3</v>
+      </c>
+      <c r="O201">
+        <v>2</v>
+      </c>
+      <c r="P201">
+        <v>3</v>
+      </c>
+      <c r="Q201">
+        <v>20</v>
+      </c>
+      <c r="R201">
+        <v>1</v>
+      </c>
+      <c r="S201">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19">
+      <c r="A202" t="s">
         <v>174</v>
       </c>
-      <c r="R144" t="s">
-        <v>167</v>
-      </c>
-      <c r="S144" t="s">
+      <c r="B202" t="s">
+        <v>222</v>
+      </c>
+      <c r="C202">
+        <v>91</v>
+      </c>
+      <c r="D202">
+        <v>9.32</v>
+      </c>
+      <c r="E202" t="s">
+        <v>247</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202">
+        <v>9</v>
+      </c>
+      <c r="H202">
+        <v>10</v>
+      </c>
+      <c r="I202">
+        <v>10</v>
+      </c>
+      <c r="J202">
+        <v>10</v>
+      </c>
+      <c r="K202">
+        <v>9</v>
+      </c>
+      <c r="L202">
+        <v>3</v>
+      </c>
+      <c r="M202">
+        <v>170</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202">
+        <v>3</v>
+      </c>
+      <c r="P202">
+        <v>3</v>
+      </c>
+      <c r="Q202">
+        <v>20</v>
+      </c>
+      <c r="R202">
+        <v>1</v>
+      </c>
+      <c r="S202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19">
+      <c r="A203" t="s">
         <v>175</v>
+      </c>
+      <c r="B203" t="s">
+        <v>239</v>
+      </c>
+      <c r="C203">
+        <v>69</v>
+      </c>
+      <c r="D203">
+        <v>4.32</v>
+      </c>
+      <c r="E203" t="s">
+        <v>247</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>4</v>
+      </c>
+      <c r="H203">
+        <v>8</v>
+      </c>
+      <c r="I203">
+        <v>7</v>
+      </c>
+      <c r="J203">
+        <v>7</v>
+      </c>
+      <c r="K203">
+        <v>4</v>
+      </c>
+      <c r="L203">
+        <v>2</v>
+      </c>
+      <c r="M203">
+        <v>123</v>
+      </c>
+      <c r="N203">
+        <v>2</v>
+      </c>
+      <c r="O203">
+        <v>1</v>
+      </c>
+      <c r="P203">
+        <v>1</v>
+      </c>
+      <c r="Q203">
+        <v>11</v>
+      </c>
+      <c r="R203">
+        <v>1</v>
+      </c>
+      <c r="S203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19">
+      <c r="A204" t="s">
+        <v>176</v>
+      </c>
+      <c r="B204" t="s">
+        <v>239</v>
+      </c>
+      <c r="C204">
+        <v>24</v>
+      </c>
+      <c r="D204">
+        <v>1.11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>247</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>2</v>
+      </c>
+      <c r="H204">
+        <v>4</v>
+      </c>
+      <c r="I204">
+        <v>4</v>
+      </c>
+      <c r="J204">
+        <v>4</v>
+      </c>
+      <c r="K204">
+        <v>2</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>67</v>
+      </c>
+      <c r="N204">
+        <v>1</v>
+      </c>
+      <c r="O204">
+        <v>1</v>
+      </c>
+      <c r="P204">
+        <v>1</v>
+      </c>
+      <c r="Q204">
+        <v>4</v>
+      </c>
+      <c r="R204">
+        <v>0</v>
+      </c>
+      <c r="S204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19">
+      <c r="A205" t="s">
+        <v>176</v>
+      </c>
+      <c r="B205" t="s">
+        <v>240</v>
+      </c>
+      <c r="C205">
+        <v>80</v>
+      </c>
+      <c r="D205">
+        <v>5.32</v>
+      </c>
+      <c r="E205" t="s">
+        <v>254</v>
+      </c>
+      <c r="F205">
+        <v>1</v>
+      </c>
+      <c r="G205">
+        <v>3</v>
+      </c>
+      <c r="H205">
+        <v>4</v>
+      </c>
+      <c r="I205">
+        <v>4</v>
+      </c>
+      <c r="J205">
+        <v>4</v>
+      </c>
+      <c r="K205">
+        <v>3</v>
+      </c>
+      <c r="L205">
+        <v>2</v>
+      </c>
+      <c r="M205">
+        <v>91</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205">
+        <v>1</v>
+      </c>
+      <c r="P205">
+        <v>1</v>
+      </c>
+      <c r="Q205">
+        <v>4</v>
+      </c>
+      <c r="R205">
+        <v>1</v>
+      </c>
+      <c r="S205">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19">
+      <c r="A206" t="s">
+        <v>177</v>
+      </c>
+      <c r="B206" t="s">
+        <v>241</v>
+      </c>
+      <c r="C206">
+        <v>105</v>
+      </c>
+      <c r="D206">
+        <v>11.32</v>
+      </c>
+      <c r="E206" t="s">
+        <v>245</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>7</v>
+      </c>
+      <c r="H206">
+        <v>14</v>
+      </c>
+      <c r="I206">
+        <v>14</v>
+      </c>
+      <c r="J206">
+        <v>14</v>
+      </c>
+      <c r="K206">
+        <v>7</v>
+      </c>
+      <c r="L206">
+        <v>3</v>
+      </c>
+      <c r="M206">
+        <v>236</v>
+      </c>
+      <c r="N206">
+        <v>3</v>
+      </c>
+      <c r="O206">
+        <v>1</v>
+      </c>
+      <c r="P206">
+        <v>2</v>
+      </c>
+      <c r="Q206">
+        <v>19</v>
+      </c>
+      <c r="R206">
+        <v>1</v>
+      </c>
+      <c r="S206">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19">
+      <c r="A207" t="s">
+        <v>177</v>
+      </c>
+      <c r="B207" t="s">
+        <v>240</v>
+      </c>
+      <c r="C207" t="s">
+        <v>242</v>
+      </c>
+      <c r="D207" t="s">
+        <v>243</v>
+      </c>
+      <c r="E207" t="s">
+        <v>254</v>
+      </c>
+      <c r="F207" t="s">
+        <v>259</v>
+      </c>
+      <c r="G207" t="s">
+        <v>260</v>
+      </c>
+      <c r="H207" t="s">
+        <v>261</v>
+      </c>
+      <c r="I207" t="s">
+        <v>262</v>
+      </c>
+      <c r="J207" t="s">
+        <v>262</v>
+      </c>
+      <c r="K207" t="s">
+        <v>263</v>
+      </c>
+      <c r="L207" t="s">
+        <v>264</v>
+      </c>
+      <c r="M207" t="s">
+        <v>265</v>
+      </c>
+      <c r="N207" t="s">
+        <v>259</v>
+      </c>
+      <c r="O207" t="s">
+        <v>259</v>
+      </c>
+      <c r="P207" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>260</v>
+      </c>
+      <c r="R207" t="s">
+        <v>264</v>
+      </c>
+      <c r="S207" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="277">
   <si>
     <t>Date</t>
   </si>
@@ -550,6 +550,18 @@
     <t>2025-11-27</t>
   </si>
   <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -742,10 +754,25 @@
     <t>2321</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>0.18</t>
+    <t>3416</t>
+  </si>
+  <si>
+    <t>5631</t>
+  </si>
+  <si>
+    <t>4214</t>
+  </si>
+  <si>
+    <t>5459</t>
+  </si>
+  <si>
+    <t>5633</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>3.21</t>
   </si>
   <si>
     <t>N14</t>
@@ -793,25 +820,31 @@
     <t>xx</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>79</t>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S207"/>
+  <dimension ref="A1:S215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1245,7 +1278,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1304,7 +1337,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1363,7 +1396,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1422,7 +1455,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1481,7 +1514,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1540,7 +1573,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1599,7 +1632,7 @@
         <v>18.6</v>
       </c>
       <c r="E8" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1658,7 +1691,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1717,7 +1750,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1776,7 +1809,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1835,7 +1868,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1894,7 +1927,7 @@
         <v>4.6</v>
       </c>
       <c r="E13" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1953,7 +1986,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2012,7 +2045,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2071,7 +2104,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2130,7 +2163,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2189,7 +2222,7 @@
         <v>2.3</v>
       </c>
       <c r="E18" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2248,7 +2281,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2307,7 +2340,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2366,7 +2399,7 @@
         <v>4.4</v>
       </c>
       <c r="E21" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2425,7 +2458,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2484,7 +2517,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2543,7 +2576,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2602,7 +2635,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2661,7 +2694,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2720,7 +2753,7 @@
         <v>4.06</v>
       </c>
       <c r="E27" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2779,7 +2812,7 @@
         <v>7.95</v>
       </c>
       <c r="E28" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2838,7 +2871,7 @@
         <v>2.2</v>
       </c>
       <c r="E29" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2897,7 +2930,7 @@
         <v>3.27</v>
       </c>
       <c r="E30" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2956,7 +2989,7 @@
         <v>8.31</v>
       </c>
       <c r="E31" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3015,7 +3048,7 @@
         <v>3.59</v>
       </c>
       <c r="E32" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3074,7 +3107,7 @@
         <v>2.13</v>
       </c>
       <c r="E33" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3133,7 +3166,7 @@
         <v>4.8</v>
       </c>
       <c r="E34" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3192,7 +3225,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3251,7 +3284,7 @@
         <v>6.45</v>
       </c>
       <c r="E36" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3310,7 +3343,7 @@
         <v>4.72</v>
       </c>
       <c r="E37" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3369,7 +3402,7 @@
         <v>1.8</v>
       </c>
       <c r="E38" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3428,7 +3461,7 @@
         <v>5.86</v>
       </c>
       <c r="E39" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3487,7 +3520,7 @@
         <v>6.18</v>
       </c>
       <c r="E40" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3546,7 +3579,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3605,7 +3638,7 @@
         <v>7.13</v>
       </c>
       <c r="E42" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3664,7 +3697,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="E43" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3723,7 +3756,7 @@
         <v>5.81</v>
       </c>
       <c r="E44" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3782,7 +3815,7 @@
         <v>4.09</v>
       </c>
       <c r="E45" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3841,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3900,7 +3933,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3959,7 +3992,7 @@
         <v>5.13</v>
       </c>
       <c r="E48" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4018,7 +4051,7 @@
         <v>1.81</v>
       </c>
       <c r="E49" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -4077,7 +4110,7 @@
         <v>7.95</v>
       </c>
       <c r="E50" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -4136,7 +4169,7 @@
         <v>0.64</v>
       </c>
       <c r="E51" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -4195,7 +4228,7 @@
         <v>6.13</v>
       </c>
       <c r="E52" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4254,7 +4287,7 @@
         <v>2.77</v>
       </c>
       <c r="E53" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4313,7 +4346,7 @@
         <v>4.35</v>
       </c>
       <c r="E54" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4372,7 +4405,7 @@
         <v>5.24</v>
       </c>
       <c r="E55" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4431,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4490,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4549,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4608,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4667,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4726,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4785,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4844,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4903,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4962,7 +4995,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -5021,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -5080,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -5139,7 +5172,7 @@
         <v>6.54</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -5198,7 +5231,7 @@
         <v>6.31</v>
       </c>
       <c r="E69" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -5257,7 +5290,7 @@
         <v>3.72</v>
       </c>
       <c r="E70" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -5316,7 +5349,7 @@
         <v>3.56</v>
       </c>
       <c r="E71" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5375,7 +5408,7 @@
         <v>19.54</v>
       </c>
       <c r="E72" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5434,7 +5467,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5493,7 +5526,7 @@
         <v>5.41</v>
       </c>
       <c r="E74" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5552,7 +5585,7 @@
         <v>5.32</v>
       </c>
       <c r="E75" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5611,7 +5644,7 @@
         <v>7.32</v>
       </c>
       <c r="E76" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5670,7 +5703,7 @@
         <v>13.1</v>
       </c>
       <c r="E77" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5729,7 +5762,7 @@
         <v>4.35</v>
       </c>
       <c r="E78" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5788,7 +5821,7 @@
         <v>3.12</v>
       </c>
       <c r="E79" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5847,7 +5880,7 @@
         <v>1.15</v>
       </c>
       <c r="E80" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5906,7 +5939,7 @@
         <v>4.68</v>
       </c>
       <c r="E81" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5965,7 +5998,7 @@
         <v>0.85</v>
       </c>
       <c r="E82" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -6024,7 +6057,7 @@
         <v>5.36</v>
       </c>
       <c r="E83" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -6083,7 +6116,7 @@
         <v>3.64</v>
       </c>
       <c r="E84" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -6142,7 +6175,7 @@
         <v>1.22</v>
       </c>
       <c r="E85" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -6201,7 +6234,7 @@
         <v>7.13</v>
       </c>
       <c r="E86" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -6260,7 +6293,7 @@
         <v>3.81</v>
       </c>
       <c r="E87" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -6319,7 +6352,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E88" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -6378,7 +6411,7 @@
         <v>2.35</v>
       </c>
       <c r="E89" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -6437,7 +6470,7 @@
         <v>6.36</v>
       </c>
       <c r="E90" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6496,7 +6529,7 @@
         <v>7.26</v>
       </c>
       <c r="E91" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -6555,7 +6588,7 @@
         <v>1.02</v>
       </c>
       <c r="E92" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6614,7 +6647,7 @@
         <v>4.02</v>
       </c>
       <c r="E93" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -6673,7 +6706,7 @@
         <v>3.71</v>
       </c>
       <c r="E94" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6732,7 +6765,7 @@
         <v>4.6</v>
       </c>
       <c r="E95" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6791,7 +6824,7 @@
         <v>16.21</v>
       </c>
       <c r="E96" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -6850,7 +6883,7 @@
         <v>3.12</v>
       </c>
       <c r="E97" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6909,7 +6942,7 @@
         <v>0.03</v>
       </c>
       <c r="E98" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -6968,7 +7001,7 @@
         <v>4.23</v>
       </c>
       <c r="E99" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -7027,7 +7060,7 @@
         <v>2.72</v>
       </c>
       <c r="E100" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -7086,7 +7119,7 @@
         <v>9.32</v>
       </c>
       <c r="E101" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -7145,7 +7178,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="E102" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -7204,7 +7237,7 @@
         <v>5.07</v>
       </c>
       <c r="E103" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -7263,7 +7296,7 @@
         <v>1.27</v>
       </c>
       <c r="E104" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -7322,7 +7355,7 @@
         <v>0.05</v>
       </c>
       <c r="E105" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -7381,7 +7414,7 @@
         <v>6.75</v>
       </c>
       <c r="E106" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -7440,7 +7473,7 @@
         <v>5.39</v>
       </c>
       <c r="E107" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -7499,7 +7532,7 @@
         <v>2.66</v>
       </c>
       <c r="E108" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -7558,7 +7591,7 @@
         <v>22.78</v>
       </c>
       <c r="E109" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7617,7 +7650,7 @@
         <v>12.71</v>
       </c>
       <c r="E110" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -7676,7 +7709,7 @@
         <v>5.35</v>
       </c>
       <c r="E111" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -7735,7 +7768,7 @@
         <v>16.98</v>
       </c>
       <c r="E112" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -7794,7 +7827,7 @@
         <v>6.32</v>
       </c>
       <c r="E113" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -7853,7 +7886,7 @@
         <v>3.35</v>
       </c>
       <c r="E114" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7912,7 +7945,7 @@
         <v>0.24</v>
       </c>
       <c r="E115" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -7971,7 +8004,7 @@
         <v>4.32</v>
       </c>
       <c r="E116" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -8021,7 +8054,7 @@
         <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C117">
         <v>132</v>
@@ -8030,7 +8063,7 @@
         <v>9.23</v>
       </c>
       <c r="E117" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -8080,7 +8113,7 @@
         <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C118">
         <v>22</v>
@@ -8089,7 +8122,7 @@
         <v>2.65</v>
       </c>
       <c r="E118" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -8139,7 +8172,7 @@
         <v>108</v>
       </c>
       <c r="B119" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C119">
         <v>178</v>
@@ -8148,7 +8181,7 @@
         <v>13.54</v>
       </c>
       <c r="E119" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -8198,7 +8231,7 @@
         <v>108</v>
       </c>
       <c r="B120" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -8207,7 +8240,7 @@
         <v>0.04</v>
       </c>
       <c r="E120" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -8257,7 +8290,7 @@
         <v>109</v>
       </c>
       <c r="B121" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C121">
         <v>31</v>
@@ -8266,7 +8299,7 @@
         <v>2.5</v>
       </c>
       <c r="E121" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -8316,7 +8349,7 @@
         <v>110</v>
       </c>
       <c r="B122" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C122">
         <v>29</v>
@@ -8325,7 +8358,7 @@
         <v>1.65</v>
       </c>
       <c r="E122" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -8375,7 +8408,7 @@
         <v>111</v>
       </c>
       <c r="B123" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C123">
         <v>219</v>
@@ -8384,7 +8417,7 @@
         <v>11.1</v>
       </c>
       <c r="E123" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -8434,7 +8467,7 @@
         <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C124">
         <v>254</v>
@@ -8443,7 +8476,7 @@
         <v>17.37</v>
       </c>
       <c r="E124" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -8493,7 +8526,7 @@
         <v>113</v>
       </c>
       <c r="B125" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -8502,7 +8535,7 @@
         <v>0.49</v>
       </c>
       <c r="E125" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -8552,7 +8585,7 @@
         <v>113</v>
       </c>
       <c r="B126" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C126">
         <v>153</v>
@@ -8561,7 +8594,7 @@
         <v>13.54</v>
       </c>
       <c r="E126" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8611,7 +8644,7 @@
         <v>114</v>
       </c>
       <c r="B127" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C127">
         <v>179</v>
@@ -8620,7 +8653,7 @@
         <v>16.21</v>
       </c>
       <c r="E127" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -8670,7 +8703,7 @@
         <v>115</v>
       </c>
       <c r="B128" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C128">
         <v>43</v>
@@ -8679,7 +8712,7 @@
         <v>3.67</v>
       </c>
       <c r="E128" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -8729,7 +8762,7 @@
         <v>116</v>
       </c>
       <c r="B129" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C129">
         <v>19</v>
@@ -8738,7 +8771,7 @@
         <v>0.83</v>
       </c>
       <c r="E129" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8788,7 +8821,7 @@
         <v>116</v>
       </c>
       <c r="B130" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C130">
         <v>80</v>
@@ -8797,7 +8830,7 @@
         <v>5.37</v>
       </c>
       <c r="E130" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -8847,7 +8880,7 @@
         <v>117</v>
       </c>
       <c r="B131" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C131">
         <v>57</v>
@@ -8856,7 +8889,7 @@
         <v>3.47</v>
       </c>
       <c r="E131" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -8906,7 +8939,7 @@
         <v>118</v>
       </c>
       <c r="B132" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C132">
         <v>133</v>
@@ -8915,7 +8948,7 @@
         <v>8.34</v>
       </c>
       <c r="E132" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -8965,7 +8998,7 @@
         <v>119</v>
       </c>
       <c r="B133" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C133">
         <v>213</v>
@@ -8974,7 +9007,7 @@
         <v>19.24</v>
       </c>
       <c r="E133" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -9024,7 +9057,7 @@
         <v>120</v>
       </c>
       <c r="B134" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C134">
         <v>34</v>
@@ -9033,7 +9066,7 @@
         <v>2.76</v>
       </c>
       <c r="E134" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9083,7 +9116,7 @@
         <v>120</v>
       </c>
       <c r="B135" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C135">
         <v>196</v>
@@ -9092,7 +9125,7 @@
         <v>13.27</v>
       </c>
       <c r="E135" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -9142,7 +9175,7 @@
         <v>121</v>
       </c>
       <c r="B136" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C136">
         <v>170</v>
@@ -9151,7 +9184,7 @@
         <v>13.93</v>
       </c>
       <c r="E136" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -9201,7 +9234,7 @@
         <v>122</v>
       </c>
       <c r="B137" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C137">
         <v>153</v>
@@ -9210,7 +9243,7 @@
         <v>9.32</v>
       </c>
       <c r="E137" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -9260,7 +9293,7 @@
         <v>123</v>
       </c>
       <c r="B138" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C138">
         <v>138</v>
@@ -9269,7 +9302,7 @@
         <v>11.68</v>
       </c>
       <c r="E138" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -9319,7 +9352,7 @@
         <v>123</v>
       </c>
       <c r="B139" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C139">
         <v>26</v>
@@ -9328,7 +9361,7 @@
         <v>1.12</v>
       </c>
       <c r="E139" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9378,7 +9411,7 @@
         <v>124</v>
       </c>
       <c r="B140" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C140">
         <v>153</v>
@@ -9387,7 +9420,7 @@
         <v>13.64</v>
       </c>
       <c r="E140" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -9437,7 +9470,7 @@
         <v>125</v>
       </c>
       <c r="B141" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C141">
         <v>106</v>
@@ -9446,7 +9479,7 @@
         <v>2.34</v>
       </c>
       <c r="E141" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -9496,7 +9529,7 @@
         <v>126</v>
       </c>
       <c r="B142" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C142">
         <v>133</v>
@@ -9505,7 +9538,7 @@
         <v>2.95</v>
       </c>
       <c r="E142" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -9555,7 +9588,7 @@
         <v>127</v>
       </c>
       <c r="B143" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C143">
         <v>141</v>
@@ -9564,7 +9597,7 @@
         <v>3.21</v>
       </c>
       <c r="E143" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -9614,7 +9647,7 @@
         <v>128</v>
       </c>
       <c r="B144" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C144">
         <v>117</v>
@@ -9623,7 +9656,7 @@
         <v>2.64</v>
       </c>
       <c r="E144" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -9673,7 +9706,7 @@
         <v>129</v>
       </c>
       <c r="B145" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C145">
         <v>78</v>
@@ -9682,7 +9715,7 @@
         <v>4.3</v>
       </c>
       <c r="E145" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -9732,7 +9765,7 @@
         <v>130</v>
       </c>
       <c r="B146" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C146">
         <v>172</v>
@@ -9741,7 +9774,7 @@
         <v>11.3</v>
       </c>
       <c r="E146" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -9791,7 +9824,7 @@
         <v>131</v>
       </c>
       <c r="B147" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C147">
         <v>171</v>
@@ -9800,7 +9833,7 @@
         <v>11.5</v>
       </c>
       <c r="E147" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -9850,7 +9883,7 @@
         <v>132</v>
       </c>
       <c r="B148" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -9859,7 +9892,7 @@
         <v>0.2</v>
       </c>
       <c r="E148" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9909,7 +9942,7 @@
         <v>132</v>
       </c>
       <c r="B149" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C149">
         <v>157</v>
@@ -9918,7 +9951,7 @@
         <v>13.21</v>
       </c>
       <c r="E149" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -9968,7 +10001,7 @@
         <v>133</v>
       </c>
       <c r="B150" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C150">
         <v>72</v>
@@ -9977,7 +10010,7 @@
         <v>5.32</v>
       </c>
       <c r="E150" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -10027,7 +10060,7 @@
         <v>133</v>
       </c>
       <c r="B151" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C151">
         <v>96</v>
@@ -10036,7 +10069,7 @@
         <v>4.36</v>
       </c>
       <c r="E151" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -10086,7 +10119,7 @@
         <v>134</v>
       </c>
       <c r="B152" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C152">
         <v>153</v>
@@ -10095,7 +10128,7 @@
         <v>13.41</v>
       </c>
       <c r="E152" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -10145,7 +10178,7 @@
         <v>135</v>
       </c>
       <c r="B153" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C153">
         <v>111</v>
@@ -10154,7 +10187,7 @@
         <v>12.74</v>
       </c>
       <c r="E153" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -10204,7 +10237,7 @@
         <v>136</v>
       </c>
       <c r="B154" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C154">
         <v>199</v>
@@ -10213,7 +10246,7 @@
         <v>17.62</v>
       </c>
       <c r="E154" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -10263,7 +10296,7 @@
         <v>137</v>
       </c>
       <c r="B155" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C155">
         <v>206</v>
@@ -10272,7 +10305,7 @@
         <v>18.89</v>
       </c>
       <c r="E155" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -10322,7 +10355,7 @@
         <v>138</v>
       </c>
       <c r="B156" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C156">
         <v>181</v>
@@ -10331,7 +10364,7 @@
         <v>16.74</v>
       </c>
       <c r="E156" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -10381,7 +10414,7 @@
         <v>138</v>
       </c>
       <c r="B157" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C157">
         <v>5</v>
@@ -10390,7 +10423,7 @@
         <v>0.1</v>
       </c>
       <c r="E157" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -10440,7 +10473,7 @@
         <v>139</v>
       </c>
       <c r="B158" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C158">
         <v>57</v>
@@ -10449,7 +10482,7 @@
         <v>3.42</v>
       </c>
       <c r="E158" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -10499,7 +10532,7 @@
         <v>140</v>
       </c>
       <c r="B159" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C159">
         <v>116</v>
@@ -10508,7 +10541,7 @@
         <v>11.36</v>
       </c>
       <c r="E159" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -10558,7 +10591,7 @@
         <v>140</v>
       </c>
       <c r="B160" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C160">
         <v>59</v>
@@ -10567,7 +10600,7 @@
         <v>4.3</v>
       </c>
       <c r="E160" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -10617,7 +10650,7 @@
         <v>141</v>
       </c>
       <c r="B161" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C161">
         <v>118</v>
@@ -10626,7 +10659,7 @@
         <v>9.32</v>
       </c>
       <c r="E161" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -10676,7 +10709,7 @@
         <v>142</v>
       </c>
       <c r="B162" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C162">
         <v>58</v>
@@ -10685,7 +10718,7 @@
         <v>4.12</v>
       </c>
       <c r="E162" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -10735,7 +10768,7 @@
         <v>143</v>
       </c>
       <c r="B163" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C163">
         <v>105</v>
@@ -10744,7 +10777,7 @@
         <v>10.21</v>
       </c>
       <c r="E163" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -10794,7 +10827,7 @@
         <v>143</v>
       </c>
       <c r="B164" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C164">
         <v>49</v>
@@ -10803,7 +10836,7 @@
         <v>3.65</v>
       </c>
       <c r="E164" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -10853,7 +10886,7 @@
         <v>144</v>
       </c>
       <c r="B165" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C165">
         <v>141</v>
@@ -10862,7 +10895,7 @@
         <v>9.65</v>
       </c>
       <c r="E165" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -10912,7 +10945,7 @@
         <v>145</v>
       </c>
       <c r="B166" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C166">
         <v>180</v>
@@ -10921,7 +10954,7 @@
         <v>14.98</v>
       </c>
       <c r="E166" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -10971,7 +11004,7 @@
         <v>146</v>
       </c>
       <c r="B167" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C167">
         <v>193</v>
@@ -10980,7 +11013,7 @@
         <v>14.38</v>
       </c>
       <c r="E167" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -11030,7 +11063,7 @@
         <v>147</v>
       </c>
       <c r="B168" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C168">
         <v>116</v>
@@ -11039,7 +11072,7 @@
         <v>11.32</v>
       </c>
       <c r="E168" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -11089,7 +11122,7 @@
         <v>148</v>
       </c>
       <c r="B169" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C169">
         <v>159</v>
@@ -11098,7 +11131,7 @@
         <v>15.32</v>
       </c>
       <c r="E169" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -11148,7 +11181,7 @@
         <v>148</v>
       </c>
       <c r="B170" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C170">
         <v>26</v>
@@ -11157,7 +11190,7 @@
         <v>0.9</v>
       </c>
       <c r="E170" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -11207,7 +11240,7 @@
         <v>149</v>
       </c>
       <c r="B171" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -11216,7 +11249,7 @@
         <v>0.12</v>
       </c>
       <c r="E171" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -11266,7 +11299,7 @@
         <v>149</v>
       </c>
       <c r="B172" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C172">
         <v>171</v>
@@ -11275,7 +11308,7 @@
         <v>17.32</v>
       </c>
       <c r="E172" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -11325,7 +11358,7 @@
         <v>150</v>
       </c>
       <c r="B173" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C173">
         <v>142</v>
@@ -11334,7 +11367,7 @@
         <v>11.98</v>
       </c>
       <c r="E173" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -11384,7 +11417,7 @@
         <v>151</v>
       </c>
       <c r="B174" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C174">
         <v>103</v>
@@ -11393,7 +11426,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="E174" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -11443,7 +11476,7 @@
         <v>152</v>
       </c>
       <c r="B175" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C175">
         <v>11</v>
@@ -11452,7 +11485,7 @@
         <v>0.32</v>
       </c>
       <c r="E175" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -11502,7 +11535,7 @@
         <v>153</v>
       </c>
       <c r="B176" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C176">
         <v>204</v>
@@ -11511,7 +11544,7 @@
         <v>20.89</v>
       </c>
       <c r="E176" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -11561,7 +11594,7 @@
         <v>154</v>
       </c>
       <c r="B177" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C177">
         <v>186</v>
@@ -11570,7 +11603,7 @@
         <v>13.65</v>
       </c>
       <c r="E177" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -11620,7 +11653,7 @@
         <v>154</v>
       </c>
       <c r="B178" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -11629,7 +11662,7 @@
         <v>0.32</v>
       </c>
       <c r="E178" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -11679,7 +11712,7 @@
         <v>155</v>
       </c>
       <c r="B179" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C179">
         <v>190</v>
@@ -11688,7 +11721,7 @@
         <v>16.27</v>
       </c>
       <c r="E179" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -11738,7 +11771,7 @@
         <v>156</v>
       </c>
       <c r="B180" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C180">
         <v>125</v>
@@ -11747,7 +11780,7 @@
         <v>15.32</v>
       </c>
       <c r="E180" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -11797,7 +11830,7 @@
         <v>157</v>
       </c>
       <c r="B181" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C181">
         <v>59</v>
@@ -11806,7 +11839,7 @@
         <v>3.54</v>
       </c>
       <c r="E181" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -11856,7 +11889,7 @@
         <v>158</v>
       </c>
       <c r="B182" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C182">
         <v>27</v>
@@ -11865,7 +11898,7 @@
         <v>1.21</v>
       </c>
       <c r="E182" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -11915,7 +11948,7 @@
         <v>159</v>
       </c>
       <c r="B183" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C183">
         <v>54</v>
@@ -11924,7 +11957,7 @@
         <v>3.17</v>
       </c>
       <c r="E183" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -11974,7 +12007,7 @@
         <v>160</v>
       </c>
       <c r="B184" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C184">
         <v>192</v>
@@ -11983,7 +12016,7 @@
         <v>17.98</v>
       </c>
       <c r="E184" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -12033,7 +12066,7 @@
         <v>161</v>
       </c>
       <c r="B185" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C185">
         <v>67</v>
@@ -12042,7 +12075,7 @@
         <v>4.35</v>
       </c>
       <c r="E185" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -12092,7 +12125,7 @@
         <v>161</v>
       </c>
       <c r="B186" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C186">
         <v>8</v>
@@ -12101,7 +12134,7 @@
         <v>0.54</v>
       </c>
       <c r="E186" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -12151,7 +12184,7 @@
         <v>162</v>
       </c>
       <c r="B187" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C187">
         <v>185</v>
@@ -12160,7 +12193,7 @@
         <v>16.87</v>
       </c>
       <c r="E187" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -12210,7 +12243,7 @@
         <v>163</v>
       </c>
       <c r="B188" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C188">
         <v>181</v>
@@ -12219,7 +12252,7 @@
         <v>21.5</v>
       </c>
       <c r="E188" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -12269,7 +12302,7 @@
         <v>164</v>
       </c>
       <c r="B189" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C189">
         <v>178</v>
@@ -12278,7 +12311,7 @@
         <v>20.21</v>
       </c>
       <c r="E189" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -12328,7 +12361,7 @@
         <v>165</v>
       </c>
       <c r="B190" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C190">
         <v>165</v>
@@ -12337,7 +12370,7 @@
         <v>17.54</v>
       </c>
       <c r="E190" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -12387,7 +12420,7 @@
         <v>166</v>
       </c>
       <c r="B191" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C191">
         <v>138</v>
@@ -12396,7 +12429,7 @@
         <v>15.32</v>
       </c>
       <c r="E191" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -12446,7 +12479,7 @@
         <v>167</v>
       </c>
       <c r="B192" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C192">
         <v>36</v>
@@ -12455,7 +12488,7 @@
         <v>3.21</v>
       </c>
       <c r="E192" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -12505,7 +12538,7 @@
         <v>168</v>
       </c>
       <c r="B193" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C193">
         <v>119</v>
@@ -12514,7 +12547,7 @@
         <v>18.32</v>
       </c>
       <c r="E193" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -12564,7 +12597,7 @@
         <v>169</v>
       </c>
       <c r="B194" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -12573,7 +12606,7 @@
         <v>0.04</v>
       </c>
       <c r="E194" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -12623,7 +12656,7 @@
         <v>170</v>
       </c>
       <c r="B195" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C195">
         <v>177</v>
@@ -12632,7 +12665,7 @@
         <v>17.98</v>
       </c>
       <c r="E195" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -12682,7 +12715,7 @@
         <v>171</v>
       </c>
       <c r="B196" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C196">
         <v>118</v>
@@ -12691,7 +12724,7 @@
         <v>17.34</v>
       </c>
       <c r="E196" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -12741,7 +12774,7 @@
         <v>171</v>
       </c>
       <c r="B197" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C197">
         <v>69</v>
@@ -12750,7 +12783,7 @@
         <v>5.21</v>
       </c>
       <c r="E197" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -12800,7 +12833,7 @@
         <v>171</v>
       </c>
       <c r="B198" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C198">
         <v>11</v>
@@ -12809,7 +12842,7 @@
         <v>0.79</v>
       </c>
       <c r="E198" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -12859,7 +12892,7 @@
         <v>172</v>
       </c>
       <c r="B199" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C199">
         <v>44</v>
@@ -12868,7 +12901,7 @@
         <v>3.24</v>
       </c>
       <c r="E199" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -12918,7 +12951,7 @@
         <v>172</v>
       </c>
       <c r="B200" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C200">
         <v>21</v>
@@ -12927,7 +12960,7 @@
         <v>1.17</v>
       </c>
       <c r="E200" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -12977,7 +13010,7 @@
         <v>173</v>
       </c>
       <c r="B201" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C201">
         <v>85</v>
@@ -12986,7 +13019,7 @@
         <v>7.32</v>
       </c>
       <c r="E201" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -13036,7 +13069,7 @@
         <v>174</v>
       </c>
       <c r="B202" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>91</v>
@@ -13045,7 +13078,7 @@
         <v>9.32</v>
       </c>
       <c r="E202" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -13095,7 +13128,7 @@
         <v>175</v>
       </c>
       <c r="B203" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C203">
         <v>69</v>
@@ -13104,7 +13137,7 @@
         <v>4.32</v>
       </c>
       <c r="E203" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -13154,7 +13187,7 @@
         <v>176</v>
       </c>
       <c r="B204" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C204">
         <v>24</v>
@@ -13163,7 +13196,7 @@
         <v>1.11</v>
       </c>
       <c r="E204" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -13213,7 +13246,7 @@
         <v>176</v>
       </c>
       <c r="B205" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C205">
         <v>80</v>
@@ -13222,7 +13255,7 @@
         <v>5.32</v>
       </c>
       <c r="E205" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -13272,7 +13305,7 @@
         <v>177</v>
       </c>
       <c r="B206" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C206">
         <v>105</v>
@@ -13281,7 +13314,7 @@
         <v>11.32</v>
       </c>
       <c r="E206" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -13331,58 +13364,530 @@
         <v>177</v>
       </c>
       <c r="B207" t="s">
-        <v>240</v>
-      </c>
-      <c r="C207" t="s">
-        <v>242</v>
-      </c>
-      <c r="D207" t="s">
-        <v>243</v>
+        <v>244</v>
+      </c>
+      <c r="C207">
+        <v>17</v>
+      </c>
+      <c r="D207">
+        <v>0.18</v>
       </c>
       <c r="E207" t="s">
+        <v>263</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207">
+        <v>2</v>
+      </c>
+      <c r="H207">
+        <v>6</v>
+      </c>
+      <c r="I207">
+        <v>5</v>
+      </c>
+      <c r="J207">
+        <v>5</v>
+      </c>
+      <c r="K207">
+        <v>3</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>79</v>
+      </c>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207">
+        <v>1</v>
+      </c>
+      <c r="P207">
+        <v>1</v>
+      </c>
+      <c r="Q207">
+        <v>2</v>
+      </c>
+      <c r="R207">
+        <v>0</v>
+      </c>
+      <c r="S207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19">
+      <c r="A208" t="s">
+        <v>178</v>
+      </c>
+      <c r="B208" t="s">
+        <v>246</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208" t="s">
+        <v>268</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>6</v>
+      </c>
+      <c r="H208">
+        <v>10</v>
+      </c>
+      <c r="I208">
+        <v>10</v>
+      </c>
+      <c r="J208">
+        <v>10</v>
+      </c>
+      <c r="K208">
+        <v>6</v>
+      </c>
+      <c r="L208">
+        <v>2</v>
+      </c>
+      <c r="M208">
+        <v>149</v>
+      </c>
+      <c r="N208">
+        <v>2</v>
+      </c>
+      <c r="O208">
+        <v>2</v>
+      </c>
+      <c r="P208">
+        <v>2</v>
+      </c>
+      <c r="Q208">
+        <v>14</v>
+      </c>
+      <c r="R208">
+        <v>1</v>
+      </c>
+      <c r="S208">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19">
+      <c r="A209" t="s">
+        <v>178</v>
+      </c>
+      <c r="B209" t="s">
+        <v>237</v>
+      </c>
+      <c r="C209">
+        <v>40</v>
+      </c>
+      <c r="D209">
+        <v>3.21</v>
+      </c>
+      <c r="E209" t="s">
         <v>254</v>
       </c>
-      <c r="F207" t="s">
-        <v>259</v>
-      </c>
-      <c r="G207" t="s">
-        <v>260</v>
-      </c>
-      <c r="H207" t="s">
-        <v>261</v>
-      </c>
-      <c r="I207" t="s">
-        <v>262</v>
-      </c>
-      <c r="J207" t="s">
-        <v>262</v>
-      </c>
-      <c r="K207" t="s">
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>3</v>
+      </c>
+      <c r="H209">
+        <v>6</v>
+      </c>
+      <c r="I209">
+        <v>6</v>
+      </c>
+      <c r="J209">
+        <v>6</v>
+      </c>
+      <c r="K209">
+        <v>3</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>77</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209">
+        <v>1</v>
+      </c>
+      <c r="P209">
+        <v>2</v>
+      </c>
+      <c r="Q209">
+        <v>8</v>
+      </c>
+      <c r="R209">
+        <v>0</v>
+      </c>
+      <c r="S209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19">
+      <c r="A210" t="s">
+        <v>178</v>
+      </c>
+      <c r="B210" t="s">
+        <v>247</v>
+      </c>
+      <c r="C210">
+        <v>2</v>
+      </c>
+      <c r="D210">
+        <v>0.01</v>
+      </c>
+      <c r="E210" t="s">
+        <v>254</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>4</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210">
+        <v>0</v>
+      </c>
+      <c r="P210">
+        <v>0</v>
+      </c>
+      <c r="Q210">
+        <v>0</v>
+      </c>
+      <c r="R210">
+        <v>0</v>
+      </c>
+      <c r="S210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19">
+      <c r="A211" t="s">
+        <v>179</v>
+      </c>
+      <c r="B211" t="s">
+        <v>248</v>
+      </c>
+      <c r="C211">
+        <v>125</v>
+      </c>
+      <c r="D211">
+        <v>19.32</v>
+      </c>
+      <c r="E211" t="s">
+        <v>254</v>
+      </c>
+      <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>7</v>
+      </c>
+      <c r="H211">
+        <v>14</v>
+      </c>
+      <c r="I211">
+        <v>14</v>
+      </c>
+      <c r="J211">
+        <v>14</v>
+      </c>
+      <c r="K211">
+        <v>7</v>
+      </c>
+      <c r="L211">
+        <v>2</v>
+      </c>
+      <c r="M211">
+        <v>237</v>
+      </c>
+      <c r="N211">
+        <v>2</v>
+      </c>
+      <c r="O211">
+        <v>2</v>
+      </c>
+      <c r="P211">
+        <v>2</v>
+      </c>
+      <c r="Q211">
+        <v>20</v>
+      </c>
+      <c r="R211">
+        <v>1</v>
+      </c>
+      <c r="S211">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19">
+      <c r="A212" t="s">
+        <v>179</v>
+      </c>
+      <c r="B212" t="s">
+        <v>237</v>
+      </c>
+      <c r="C212">
+        <v>12</v>
+      </c>
+      <c r="D212">
+        <v>0.02</v>
+      </c>
+      <c r="E212" t="s">
+        <v>254</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>2</v>
+      </c>
+      <c r="I212">
+        <v>2</v>
+      </c>
+      <c r="J212">
+        <v>2</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>33</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212">
+        <v>0</v>
+      </c>
+      <c r="P212">
+        <v>1</v>
+      </c>
+      <c r="Q212">
+        <v>4</v>
+      </c>
+      <c r="R212">
+        <v>0</v>
+      </c>
+      <c r="S212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19">
+      <c r="A213" t="s">
+        <v>180</v>
+      </c>
+      <c r="B213" t="s">
+        <v>249</v>
+      </c>
+      <c r="C213">
+        <v>124</v>
+      </c>
+      <c r="D213">
+        <v>19.35</v>
+      </c>
+      <c r="E213" t="s">
         <v>263</v>
       </c>
-      <c r="L207" t="s">
-        <v>264</v>
-      </c>
-      <c r="M207" t="s">
-        <v>265</v>
-      </c>
-      <c r="N207" t="s">
-        <v>259</v>
-      </c>
-      <c r="O207" t="s">
-        <v>259</v>
-      </c>
-      <c r="P207" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>260</v>
-      </c>
-      <c r="R207" t="s">
-        <v>264</v>
-      </c>
-      <c r="S207" t="s">
-        <v>259</v>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213">
+        <v>8</v>
+      </c>
+      <c r="H213">
+        <v>16</v>
+      </c>
+      <c r="I213">
+        <v>16</v>
+      </c>
+      <c r="J213">
+        <v>16</v>
+      </c>
+      <c r="K213">
+        <v>8</v>
+      </c>
+      <c r="L213">
+        <v>4</v>
+      </c>
+      <c r="M213">
+        <v>236</v>
+      </c>
+      <c r="N213">
+        <v>2</v>
+      </c>
+      <c r="O213">
+        <v>3</v>
+      </c>
+      <c r="P213">
+        <v>2</v>
+      </c>
+      <c r="Q213">
+        <v>10</v>
+      </c>
+      <c r="R213">
+        <v>1</v>
+      </c>
+      <c r="S213">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19">
+      <c r="A214" t="s">
+        <v>180</v>
+      </c>
+      <c r="B214" t="s">
+        <v>250</v>
+      </c>
+      <c r="C214">
+        <v>8</v>
+      </c>
+      <c r="D214">
+        <v>0.03</v>
+      </c>
+      <c r="E214" t="s">
+        <v>254</v>
+      </c>
+      <c r="F214">
+        <v>0</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>25</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214">
+        <v>1</v>
+      </c>
+      <c r="P214">
+        <v>1</v>
+      </c>
+      <c r="Q214">
+        <v>2</v>
+      </c>
+      <c r="R214">
+        <v>0</v>
+      </c>
+      <c r="S214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19">
+      <c r="A215" t="s">
+        <v>181</v>
+      </c>
+      <c r="B215" t="s">
+        <v>249</v>
+      </c>
+      <c r="C215" t="s">
+        <v>251</v>
+      </c>
+      <c r="D215" t="s">
+        <v>252</v>
+      </c>
+      <c r="E215" t="s">
+        <v>263</v>
+      </c>
+      <c r="F215" t="s">
+        <v>269</v>
+      </c>
+      <c r="G215" t="s">
+        <v>270</v>
+      </c>
+      <c r="H215" t="s">
+        <v>271</v>
+      </c>
+      <c r="I215" t="s">
+        <v>272</v>
+      </c>
+      <c r="J215" t="s">
+        <v>272</v>
+      </c>
+      <c r="K215" t="s">
+        <v>270</v>
+      </c>
+      <c r="L215" t="s">
+        <v>273</v>
+      </c>
+      <c r="M215" t="s">
+        <v>274</v>
+      </c>
+      <c r="N215" t="s">
+        <v>275</v>
+      </c>
+      <c r="O215" t="s">
+        <v>275</v>
+      </c>
+      <c r="P215" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>276</v>
+      </c>
+      <c r="R215" t="s">
+        <v>269</v>
+      </c>
+      <c r="S215" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="284">
   <si>
     <t>Date</t>
   </si>
@@ -562,6 +562,15 @@
     <t>2025-12-03</t>
   </si>
   <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -769,10 +778,16 @@
     <t>5633</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>3.21</t>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>17.92</t>
   </si>
   <si>
     <t>N14</t>
@@ -823,28 +838,34 @@
     <t>X</t>
   </si>
   <si>
-    <t>0</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>6</t>
+    <t>21</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S215"/>
+  <dimension ref="A1:S218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1278,7 +1299,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1337,7 +1358,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1396,7 +1417,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1455,7 +1476,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1514,7 +1535,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1573,7 +1594,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1632,7 +1653,7 @@
         <v>18.6</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1691,7 +1712,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1750,7 +1771,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1809,7 +1830,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1868,7 +1889,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1927,7 +1948,7 @@
         <v>4.6</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1986,7 +2007,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2045,7 +2066,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2104,7 +2125,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2163,7 +2184,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2222,7 +2243,7 @@
         <v>2.3</v>
       </c>
       <c r="E18" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2281,7 +2302,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2340,7 +2361,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2399,7 +2420,7 @@
         <v>4.4</v>
       </c>
       <c r="E21" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2458,7 +2479,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2517,7 +2538,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2576,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2635,7 +2656,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2694,7 +2715,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2753,7 +2774,7 @@
         <v>4.06</v>
       </c>
       <c r="E27" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2812,7 +2833,7 @@
         <v>7.95</v>
       </c>
       <c r="E28" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2871,7 +2892,7 @@
         <v>2.2</v>
       </c>
       <c r="E29" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2930,7 +2951,7 @@
         <v>3.27</v>
       </c>
       <c r="E30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2989,7 +3010,7 @@
         <v>8.31</v>
       </c>
       <c r="E31" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3048,7 +3069,7 @@
         <v>3.59</v>
       </c>
       <c r="E32" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3107,7 +3128,7 @@
         <v>2.13</v>
       </c>
       <c r="E33" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3166,7 +3187,7 @@
         <v>4.8</v>
       </c>
       <c r="E34" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3225,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3284,7 +3305,7 @@
         <v>6.45</v>
       </c>
       <c r="E36" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3343,7 +3364,7 @@
         <v>4.72</v>
       </c>
       <c r="E37" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3402,7 +3423,7 @@
         <v>1.8</v>
       </c>
       <c r="E38" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3461,7 +3482,7 @@
         <v>5.86</v>
       </c>
       <c r="E39" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3520,7 +3541,7 @@
         <v>6.18</v>
       </c>
       <c r="E40" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3579,7 +3600,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3638,7 +3659,7 @@
         <v>7.13</v>
       </c>
       <c r="E42" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3697,7 +3718,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="E43" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3756,7 +3777,7 @@
         <v>5.81</v>
       </c>
       <c r="E44" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3815,7 +3836,7 @@
         <v>4.09</v>
       </c>
       <c r="E45" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3874,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3933,7 +3954,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3992,7 +4013,7 @@
         <v>5.13</v>
       </c>
       <c r="E48" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4051,7 +4072,7 @@
         <v>1.81</v>
       </c>
       <c r="E49" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -4110,7 +4131,7 @@
         <v>7.95</v>
       </c>
       <c r="E50" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -4169,7 +4190,7 @@
         <v>0.64</v>
       </c>
       <c r="E51" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -4228,7 +4249,7 @@
         <v>6.13</v>
       </c>
       <c r="E52" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4287,7 +4308,7 @@
         <v>2.77</v>
       </c>
       <c r="E53" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4346,7 +4367,7 @@
         <v>4.35</v>
       </c>
       <c r="E54" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4405,7 +4426,7 @@
         <v>5.24</v>
       </c>
       <c r="E55" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4464,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4523,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4582,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4641,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4700,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4759,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4818,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4877,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4936,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4995,7 +5016,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -5054,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -5113,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -5172,7 +5193,7 @@
         <v>6.54</v>
       </c>
       <c r="E68" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -5231,7 +5252,7 @@
         <v>6.31</v>
       </c>
       <c r="E69" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -5290,7 +5311,7 @@
         <v>3.72</v>
       </c>
       <c r="E70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -5349,7 +5370,7 @@
         <v>3.56</v>
       </c>
       <c r="E71" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5408,7 +5429,7 @@
         <v>19.54</v>
       </c>
       <c r="E72" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5467,7 +5488,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5526,7 +5547,7 @@
         <v>5.41</v>
       </c>
       <c r="E74" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5585,7 +5606,7 @@
         <v>5.32</v>
       </c>
       <c r="E75" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5644,7 +5665,7 @@
         <v>7.32</v>
       </c>
       <c r="E76" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5703,7 +5724,7 @@
         <v>13.1</v>
       </c>
       <c r="E77" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5762,7 +5783,7 @@
         <v>4.35</v>
       </c>
       <c r="E78" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5821,7 +5842,7 @@
         <v>3.12</v>
       </c>
       <c r="E79" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5880,7 +5901,7 @@
         <v>1.15</v>
       </c>
       <c r="E80" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5939,7 +5960,7 @@
         <v>4.68</v>
       </c>
       <c r="E81" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5998,7 +6019,7 @@
         <v>0.85</v>
       </c>
       <c r="E82" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -6057,7 +6078,7 @@
         <v>5.36</v>
       </c>
       <c r="E83" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -6116,7 +6137,7 @@
         <v>3.64</v>
       </c>
       <c r="E84" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -6175,7 +6196,7 @@
         <v>1.22</v>
       </c>
       <c r="E85" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -6234,7 +6255,7 @@
         <v>7.13</v>
       </c>
       <c r="E86" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -6293,7 +6314,7 @@
         <v>3.81</v>
       </c>
       <c r="E87" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -6352,7 +6373,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E88" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -6411,7 +6432,7 @@
         <v>2.35</v>
       </c>
       <c r="E89" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -6470,7 +6491,7 @@
         <v>6.36</v>
       </c>
       <c r="E90" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6529,7 +6550,7 @@
         <v>7.26</v>
       </c>
       <c r="E91" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -6588,7 +6609,7 @@
         <v>1.02</v>
       </c>
       <c r="E92" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6647,7 +6668,7 @@
         <v>4.02</v>
       </c>
       <c r="E93" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -6706,7 +6727,7 @@
         <v>3.71</v>
       </c>
       <c r="E94" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6765,7 +6786,7 @@
         <v>4.6</v>
       </c>
       <c r="E95" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6824,7 +6845,7 @@
         <v>16.21</v>
       </c>
       <c r="E96" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -6883,7 +6904,7 @@
         <v>3.12</v>
       </c>
       <c r="E97" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6942,7 +6963,7 @@
         <v>0.03</v>
       </c>
       <c r="E98" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -7001,7 +7022,7 @@
         <v>4.23</v>
       </c>
       <c r="E99" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -7060,7 +7081,7 @@
         <v>2.72</v>
       </c>
       <c r="E100" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -7119,7 +7140,7 @@
         <v>9.32</v>
       </c>
       <c r="E101" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -7178,7 +7199,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="E102" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -7237,7 +7258,7 @@
         <v>5.07</v>
       </c>
       <c r="E103" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -7296,7 +7317,7 @@
         <v>1.27</v>
       </c>
       <c r="E104" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -7355,7 +7376,7 @@
         <v>0.05</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -7414,7 +7435,7 @@
         <v>6.75</v>
       </c>
       <c r="E106" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -7473,7 +7494,7 @@
         <v>5.39</v>
       </c>
       <c r="E107" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -7532,7 +7553,7 @@
         <v>2.66</v>
       </c>
       <c r="E108" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -7591,7 +7612,7 @@
         <v>22.78</v>
       </c>
       <c r="E109" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7650,7 +7671,7 @@
         <v>12.71</v>
       </c>
       <c r="E110" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -7709,7 +7730,7 @@
         <v>5.35</v>
       </c>
       <c r="E111" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -7768,7 +7789,7 @@
         <v>16.98</v>
       </c>
       <c r="E112" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -7827,7 +7848,7 @@
         <v>6.32</v>
       </c>
       <c r="E113" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -7886,7 +7907,7 @@
         <v>3.35</v>
       </c>
       <c r="E114" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7945,7 +7966,7 @@
         <v>0.24</v>
       </c>
       <c r="E115" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -8004,7 +8025,7 @@
         <v>4.32</v>
       </c>
       <c r="E116" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -8054,7 +8075,7 @@
         <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C117">
         <v>132</v>
@@ -8063,7 +8084,7 @@
         <v>9.23</v>
       </c>
       <c r="E117" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -8113,7 +8134,7 @@
         <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C118">
         <v>22</v>
@@ -8122,7 +8143,7 @@
         <v>2.65</v>
       </c>
       <c r="E118" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -8172,7 +8193,7 @@
         <v>108</v>
       </c>
       <c r="B119" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C119">
         <v>178</v>
@@ -8181,7 +8202,7 @@
         <v>13.54</v>
       </c>
       <c r="E119" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -8231,7 +8252,7 @@
         <v>108</v>
       </c>
       <c r="B120" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -8240,7 +8261,7 @@
         <v>0.04</v>
       </c>
       <c r="E120" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -8290,7 +8311,7 @@
         <v>109</v>
       </c>
       <c r="B121" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C121">
         <v>31</v>
@@ -8299,7 +8320,7 @@
         <v>2.5</v>
       </c>
       <c r="E121" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -8349,7 +8370,7 @@
         <v>110</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C122">
         <v>29</v>
@@ -8358,7 +8379,7 @@
         <v>1.65</v>
       </c>
       <c r="E122" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -8408,7 +8429,7 @@
         <v>111</v>
       </c>
       <c r="B123" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C123">
         <v>219</v>
@@ -8417,7 +8438,7 @@
         <v>11.1</v>
       </c>
       <c r="E123" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -8467,7 +8488,7 @@
         <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C124">
         <v>254</v>
@@ -8476,7 +8497,7 @@
         <v>17.37</v>
       </c>
       <c r="E124" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -8526,7 +8547,7 @@
         <v>113</v>
       </c>
       <c r="B125" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -8535,7 +8556,7 @@
         <v>0.49</v>
       </c>
       <c r="E125" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -8585,7 +8606,7 @@
         <v>113</v>
       </c>
       <c r="B126" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C126">
         <v>153</v>
@@ -8594,7 +8615,7 @@
         <v>13.54</v>
       </c>
       <c r="E126" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8644,7 +8665,7 @@
         <v>114</v>
       </c>
       <c r="B127" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C127">
         <v>179</v>
@@ -8653,7 +8674,7 @@
         <v>16.21</v>
       </c>
       <c r="E127" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -8703,7 +8724,7 @@
         <v>115</v>
       </c>
       <c r="B128" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C128">
         <v>43</v>
@@ -8712,7 +8733,7 @@
         <v>3.67</v>
       </c>
       <c r="E128" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -8762,7 +8783,7 @@
         <v>116</v>
       </c>
       <c r="B129" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C129">
         <v>19</v>
@@ -8771,7 +8792,7 @@
         <v>0.83</v>
       </c>
       <c r="E129" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8821,7 +8842,7 @@
         <v>116</v>
       </c>
       <c r="B130" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C130">
         <v>80</v>
@@ -8830,7 +8851,7 @@
         <v>5.37</v>
       </c>
       <c r="E130" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -8880,7 +8901,7 @@
         <v>117</v>
       </c>
       <c r="B131" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C131">
         <v>57</v>
@@ -8889,7 +8910,7 @@
         <v>3.47</v>
       </c>
       <c r="E131" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -8939,7 +8960,7 @@
         <v>118</v>
       </c>
       <c r="B132" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C132">
         <v>133</v>
@@ -8948,7 +8969,7 @@
         <v>8.34</v>
       </c>
       <c r="E132" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -8998,7 +9019,7 @@
         <v>119</v>
       </c>
       <c r="B133" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C133">
         <v>213</v>
@@ -9007,7 +9028,7 @@
         <v>19.24</v>
       </c>
       <c r="E133" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -9057,7 +9078,7 @@
         <v>120</v>
       </c>
       <c r="B134" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C134">
         <v>34</v>
@@ -9066,7 +9087,7 @@
         <v>2.76</v>
       </c>
       <c r="E134" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9116,7 +9137,7 @@
         <v>120</v>
       </c>
       <c r="B135" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C135">
         <v>196</v>
@@ -9125,7 +9146,7 @@
         <v>13.27</v>
       </c>
       <c r="E135" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -9175,7 +9196,7 @@
         <v>121</v>
       </c>
       <c r="B136" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C136">
         <v>170</v>
@@ -9184,7 +9205,7 @@
         <v>13.93</v>
       </c>
       <c r="E136" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -9234,7 +9255,7 @@
         <v>122</v>
       </c>
       <c r="B137" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C137">
         <v>153</v>
@@ -9243,7 +9264,7 @@
         <v>9.32</v>
       </c>
       <c r="E137" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -9293,7 +9314,7 @@
         <v>123</v>
       </c>
       <c r="B138" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C138">
         <v>138</v>
@@ -9302,7 +9323,7 @@
         <v>11.68</v>
       </c>
       <c r="E138" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -9352,7 +9373,7 @@
         <v>123</v>
       </c>
       <c r="B139" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C139">
         <v>26</v>
@@ -9361,7 +9382,7 @@
         <v>1.12</v>
       </c>
       <c r="E139" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9411,7 +9432,7 @@
         <v>124</v>
       </c>
       <c r="B140" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C140">
         <v>153</v>
@@ -9420,7 +9441,7 @@
         <v>13.64</v>
       </c>
       <c r="E140" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -9470,7 +9491,7 @@
         <v>125</v>
       </c>
       <c r="B141" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C141">
         <v>106</v>
@@ -9479,7 +9500,7 @@
         <v>2.34</v>
       </c>
       <c r="E141" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -9529,7 +9550,7 @@
         <v>126</v>
       </c>
       <c r="B142" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C142">
         <v>133</v>
@@ -9538,7 +9559,7 @@
         <v>2.95</v>
       </c>
       <c r="E142" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -9588,7 +9609,7 @@
         <v>127</v>
       </c>
       <c r="B143" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C143">
         <v>141</v>
@@ -9597,7 +9618,7 @@
         <v>3.21</v>
       </c>
       <c r="E143" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -9647,7 +9668,7 @@
         <v>128</v>
       </c>
       <c r="B144" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C144">
         <v>117</v>
@@ -9656,7 +9677,7 @@
         <v>2.64</v>
       </c>
       <c r="E144" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -9706,7 +9727,7 @@
         <v>129</v>
       </c>
       <c r="B145" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C145">
         <v>78</v>
@@ -9715,7 +9736,7 @@
         <v>4.3</v>
       </c>
       <c r="E145" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -9765,7 +9786,7 @@
         <v>130</v>
       </c>
       <c r="B146" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C146">
         <v>172</v>
@@ -9774,7 +9795,7 @@
         <v>11.3</v>
       </c>
       <c r="E146" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -9824,7 +9845,7 @@
         <v>131</v>
       </c>
       <c r="B147" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C147">
         <v>171</v>
@@ -9833,7 +9854,7 @@
         <v>11.5</v>
       </c>
       <c r="E147" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -9883,7 +9904,7 @@
         <v>132</v>
       </c>
       <c r="B148" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -9892,7 +9913,7 @@
         <v>0.2</v>
       </c>
       <c r="E148" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9942,7 +9963,7 @@
         <v>132</v>
       </c>
       <c r="B149" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C149">
         <v>157</v>
@@ -9951,7 +9972,7 @@
         <v>13.21</v>
       </c>
       <c r="E149" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -10001,7 +10022,7 @@
         <v>133</v>
       </c>
       <c r="B150" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C150">
         <v>72</v>
@@ -10010,7 +10031,7 @@
         <v>5.32</v>
       </c>
       <c r="E150" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -10060,7 +10081,7 @@
         <v>133</v>
       </c>
       <c r="B151" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C151">
         <v>96</v>
@@ -10069,7 +10090,7 @@
         <v>4.36</v>
       </c>
       <c r="E151" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -10119,7 +10140,7 @@
         <v>134</v>
       </c>
       <c r="B152" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C152">
         <v>153</v>
@@ -10128,7 +10149,7 @@
         <v>13.41</v>
       </c>
       <c r="E152" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -10178,7 +10199,7 @@
         <v>135</v>
       </c>
       <c r="B153" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C153">
         <v>111</v>
@@ -10187,7 +10208,7 @@
         <v>12.74</v>
       </c>
       <c r="E153" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -10237,7 +10258,7 @@
         <v>136</v>
       </c>
       <c r="B154" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C154">
         <v>199</v>
@@ -10246,7 +10267,7 @@
         <v>17.62</v>
       </c>
       <c r="E154" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -10296,7 +10317,7 @@
         <v>137</v>
       </c>
       <c r="B155" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C155">
         <v>206</v>
@@ -10305,7 +10326,7 @@
         <v>18.89</v>
       </c>
       <c r="E155" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -10355,7 +10376,7 @@
         <v>138</v>
       </c>
       <c r="B156" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C156">
         <v>181</v>
@@ -10364,7 +10385,7 @@
         <v>16.74</v>
       </c>
       <c r="E156" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -10414,7 +10435,7 @@
         <v>138</v>
       </c>
       <c r="B157" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C157">
         <v>5</v>
@@ -10423,7 +10444,7 @@
         <v>0.1</v>
       </c>
       <c r="E157" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -10473,7 +10494,7 @@
         <v>139</v>
       </c>
       <c r="B158" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C158">
         <v>57</v>
@@ -10482,7 +10503,7 @@
         <v>3.42</v>
       </c>
       <c r="E158" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -10532,7 +10553,7 @@
         <v>140</v>
       </c>
       <c r="B159" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C159">
         <v>116</v>
@@ -10541,7 +10562,7 @@
         <v>11.36</v>
       </c>
       <c r="E159" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -10591,7 +10612,7 @@
         <v>140</v>
       </c>
       <c r="B160" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C160">
         <v>59</v>
@@ -10600,7 +10621,7 @@
         <v>4.3</v>
       </c>
       <c r="E160" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -10650,7 +10671,7 @@
         <v>141</v>
       </c>
       <c r="B161" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C161">
         <v>118</v>
@@ -10659,7 +10680,7 @@
         <v>9.32</v>
       </c>
       <c r="E161" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -10709,7 +10730,7 @@
         <v>142</v>
       </c>
       <c r="B162" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C162">
         <v>58</v>
@@ -10718,7 +10739,7 @@
         <v>4.12</v>
       </c>
       <c r="E162" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -10768,7 +10789,7 @@
         <v>143</v>
       </c>
       <c r="B163" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C163">
         <v>105</v>
@@ -10777,7 +10798,7 @@
         <v>10.21</v>
       </c>
       <c r="E163" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -10827,7 +10848,7 @@
         <v>143</v>
       </c>
       <c r="B164" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C164">
         <v>49</v>
@@ -10836,7 +10857,7 @@
         <v>3.65</v>
       </c>
       <c r="E164" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -10886,7 +10907,7 @@
         <v>144</v>
       </c>
       <c r="B165" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C165">
         <v>141</v>
@@ -10895,7 +10916,7 @@
         <v>9.65</v>
       </c>
       <c r="E165" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -10945,7 +10966,7 @@
         <v>145</v>
       </c>
       <c r="B166" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C166">
         <v>180</v>
@@ -10954,7 +10975,7 @@
         <v>14.98</v>
       </c>
       <c r="E166" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -11004,7 +11025,7 @@
         <v>146</v>
       </c>
       <c r="B167" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C167">
         <v>193</v>
@@ -11013,7 +11034,7 @@
         <v>14.38</v>
       </c>
       <c r="E167" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -11063,7 +11084,7 @@
         <v>147</v>
       </c>
       <c r="B168" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C168">
         <v>116</v>
@@ -11072,7 +11093,7 @@
         <v>11.32</v>
       </c>
       <c r="E168" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -11122,7 +11143,7 @@
         <v>148</v>
       </c>
       <c r="B169" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C169">
         <v>159</v>
@@ -11131,7 +11152,7 @@
         <v>15.32</v>
       </c>
       <c r="E169" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -11181,7 +11202,7 @@
         <v>148</v>
       </c>
       <c r="B170" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C170">
         <v>26</v>
@@ -11190,7 +11211,7 @@
         <v>0.9</v>
       </c>
       <c r="E170" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -11240,7 +11261,7 @@
         <v>149</v>
       </c>
       <c r="B171" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -11249,7 +11270,7 @@
         <v>0.12</v>
       </c>
       <c r="E171" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -11299,7 +11320,7 @@
         <v>149</v>
       </c>
       <c r="B172" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C172">
         <v>171</v>
@@ -11308,7 +11329,7 @@
         <v>17.32</v>
       </c>
       <c r="E172" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -11358,7 +11379,7 @@
         <v>150</v>
       </c>
       <c r="B173" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C173">
         <v>142</v>
@@ -11367,7 +11388,7 @@
         <v>11.98</v>
       </c>
       <c r="E173" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -11417,7 +11438,7 @@
         <v>151</v>
       </c>
       <c r="B174" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C174">
         <v>103</v>
@@ -11426,7 +11447,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="E174" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -11476,7 +11497,7 @@
         <v>152</v>
       </c>
       <c r="B175" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C175">
         <v>11</v>
@@ -11485,7 +11506,7 @@
         <v>0.32</v>
       </c>
       <c r="E175" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -11535,7 +11556,7 @@
         <v>153</v>
       </c>
       <c r="B176" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C176">
         <v>204</v>
@@ -11544,7 +11565,7 @@
         <v>20.89</v>
       </c>
       <c r="E176" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -11594,7 +11615,7 @@
         <v>154</v>
       </c>
       <c r="B177" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C177">
         <v>186</v>
@@ -11603,7 +11624,7 @@
         <v>13.65</v>
       </c>
       <c r="E177" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -11653,7 +11674,7 @@
         <v>154</v>
       </c>
       <c r="B178" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -11662,7 +11683,7 @@
         <v>0.32</v>
       </c>
       <c r="E178" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -11712,7 +11733,7 @@
         <v>155</v>
       </c>
       <c r="B179" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C179">
         <v>190</v>
@@ -11721,7 +11742,7 @@
         <v>16.27</v>
       </c>
       <c r="E179" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -11771,7 +11792,7 @@
         <v>156</v>
       </c>
       <c r="B180" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C180">
         <v>125</v>
@@ -11780,7 +11801,7 @@
         <v>15.32</v>
       </c>
       <c r="E180" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -11830,7 +11851,7 @@
         <v>157</v>
       </c>
       <c r="B181" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C181">
         <v>59</v>
@@ -11839,7 +11860,7 @@
         <v>3.54</v>
       </c>
       <c r="E181" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -11889,7 +11910,7 @@
         <v>158</v>
       </c>
       <c r="B182" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C182">
         <v>27</v>
@@ -11898,7 +11919,7 @@
         <v>1.21</v>
       </c>
       <c r="E182" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -11948,7 +11969,7 @@
         <v>159</v>
       </c>
       <c r="B183" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C183">
         <v>54</v>
@@ -11957,7 +11978,7 @@
         <v>3.17</v>
       </c>
       <c r="E183" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -12007,7 +12028,7 @@
         <v>160</v>
       </c>
       <c r="B184" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C184">
         <v>192</v>
@@ -12016,7 +12037,7 @@
         <v>17.98</v>
       </c>
       <c r="E184" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -12066,7 +12087,7 @@
         <v>161</v>
       </c>
       <c r="B185" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C185">
         <v>67</v>
@@ -12075,7 +12096,7 @@
         <v>4.35</v>
       </c>
       <c r="E185" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -12125,7 +12146,7 @@
         <v>161</v>
       </c>
       <c r="B186" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C186">
         <v>8</v>
@@ -12134,7 +12155,7 @@
         <v>0.54</v>
       </c>
       <c r="E186" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -12184,7 +12205,7 @@
         <v>162</v>
       </c>
       <c r="B187" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C187">
         <v>185</v>
@@ -12193,7 +12214,7 @@
         <v>16.87</v>
       </c>
       <c r="E187" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -12243,7 +12264,7 @@
         <v>163</v>
       </c>
       <c r="B188" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C188">
         <v>181</v>
@@ -12252,7 +12273,7 @@
         <v>21.5</v>
       </c>
       <c r="E188" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -12302,7 +12323,7 @@
         <v>164</v>
       </c>
       <c r="B189" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C189">
         <v>178</v>
@@ -12311,7 +12332,7 @@
         <v>20.21</v>
       </c>
       <c r="E189" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -12361,7 +12382,7 @@
         <v>165</v>
       </c>
       <c r="B190" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C190">
         <v>165</v>
@@ -12370,7 +12391,7 @@
         <v>17.54</v>
       </c>
       <c r="E190" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -12420,7 +12441,7 @@
         <v>166</v>
       </c>
       <c r="B191" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C191">
         <v>138</v>
@@ -12429,7 +12450,7 @@
         <v>15.32</v>
       </c>
       <c r="E191" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -12479,7 +12500,7 @@
         <v>167</v>
       </c>
       <c r="B192" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C192">
         <v>36</v>
@@ -12488,7 +12509,7 @@
         <v>3.21</v>
       </c>
       <c r="E192" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -12538,7 +12559,7 @@
         <v>168</v>
       </c>
       <c r="B193" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C193">
         <v>119</v>
@@ -12547,7 +12568,7 @@
         <v>18.32</v>
       </c>
       <c r="E193" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -12597,7 +12618,7 @@
         <v>169</v>
       </c>
       <c r="B194" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -12606,7 +12627,7 @@
         <v>0.04</v>
       </c>
       <c r="E194" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -12656,7 +12677,7 @@
         <v>170</v>
       </c>
       <c r="B195" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C195">
         <v>177</v>
@@ -12665,7 +12686,7 @@
         <v>17.98</v>
       </c>
       <c r="E195" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -12715,7 +12736,7 @@
         <v>171</v>
       </c>
       <c r="B196" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C196">
         <v>118</v>
@@ -12724,7 +12745,7 @@
         <v>17.34</v>
       </c>
       <c r="E196" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -12774,7 +12795,7 @@
         <v>171</v>
       </c>
       <c r="B197" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C197">
         <v>69</v>
@@ -12783,7 +12804,7 @@
         <v>5.21</v>
       </c>
       <c r="E197" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -12833,7 +12854,7 @@
         <v>171</v>
       </c>
       <c r="B198" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C198">
         <v>11</v>
@@ -12842,7 +12863,7 @@
         <v>0.79</v>
       </c>
       <c r="E198" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -12892,7 +12913,7 @@
         <v>172</v>
       </c>
       <c r="B199" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C199">
         <v>44</v>
@@ -12901,7 +12922,7 @@
         <v>3.24</v>
       </c>
       <c r="E199" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -12951,7 +12972,7 @@
         <v>172</v>
       </c>
       <c r="B200" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C200">
         <v>21</v>
@@ -12960,7 +12981,7 @@
         <v>1.17</v>
       </c>
       <c r="E200" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -13010,7 +13031,7 @@
         <v>173</v>
       </c>
       <c r="B201" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C201">
         <v>85</v>
@@ -13019,7 +13040,7 @@
         <v>7.32</v>
       </c>
       <c r="E201" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -13069,7 +13090,7 @@
         <v>174</v>
       </c>
       <c r="B202" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C202">
         <v>91</v>
@@ -13078,7 +13099,7 @@
         <v>9.32</v>
       </c>
       <c r="E202" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -13128,7 +13149,7 @@
         <v>175</v>
       </c>
       <c r="B203" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C203">
         <v>69</v>
@@ -13137,7 +13158,7 @@
         <v>4.32</v>
       </c>
       <c r="E203" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -13187,7 +13208,7 @@
         <v>176</v>
       </c>
       <c r="B204" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C204">
         <v>24</v>
@@ -13196,7 +13217,7 @@
         <v>1.11</v>
       </c>
       <c r="E204" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -13246,7 +13267,7 @@
         <v>176</v>
       </c>
       <c r="B205" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C205">
         <v>80</v>
@@ -13255,7 +13276,7 @@
         <v>5.32</v>
       </c>
       <c r="E205" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -13305,7 +13326,7 @@
         <v>177</v>
       </c>
       <c r="B206" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C206">
         <v>105</v>
@@ -13314,7 +13335,7 @@
         <v>11.32</v>
       </c>
       <c r="E206" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -13364,7 +13385,7 @@
         <v>177</v>
       </c>
       <c r="B207" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C207">
         <v>17</v>
@@ -13373,7 +13394,7 @@
         <v>0.18</v>
       </c>
       <c r="E207" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -13423,7 +13444,7 @@
         <v>178</v>
       </c>
       <c r="B208" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -13432,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -13482,7 +13503,7 @@
         <v>178</v>
       </c>
       <c r="B209" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C209">
         <v>40</v>
@@ -13491,7 +13512,7 @@
         <v>3.21</v>
       </c>
       <c r="E209" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -13541,7 +13562,7 @@
         <v>178</v>
       </c>
       <c r="B210" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C210">
         <v>2</v>
@@ -13550,7 +13571,7 @@
         <v>0.01</v>
       </c>
       <c r="E210" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -13600,7 +13621,7 @@
         <v>179</v>
       </c>
       <c r="B211" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C211">
         <v>125</v>
@@ -13609,7 +13630,7 @@
         <v>19.32</v>
       </c>
       <c r="E211" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -13659,7 +13680,7 @@
         <v>179</v>
       </c>
       <c r="B212" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C212">
         <v>12</v>
@@ -13668,7 +13689,7 @@
         <v>0.02</v>
       </c>
       <c r="E212" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -13718,7 +13739,7 @@
         <v>180</v>
       </c>
       <c r="B213" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C213">
         <v>124</v>
@@ -13727,7 +13748,7 @@
         <v>19.35</v>
       </c>
       <c r="E213" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -13777,7 +13798,7 @@
         <v>180</v>
       </c>
       <c r="B214" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C214">
         <v>8</v>
@@ -13786,7 +13807,7 @@
         <v>0.03</v>
       </c>
       <c r="E214" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -13836,58 +13857,235 @@
         <v>181</v>
       </c>
       <c r="B215" t="s">
-        <v>249</v>
-      </c>
-      <c r="C215" t="s">
-        <v>251</v>
-      </c>
-      <c r="D215" t="s">
         <v>252</v>
       </c>
+      <c r="C215">
+        <v>36</v>
+      </c>
+      <c r="D215">
+        <v>3.21</v>
+      </c>
       <c r="E215" t="s">
-        <v>263</v>
-      </c>
-      <c r="F215" t="s">
-        <v>269</v>
-      </c>
-      <c r="G215" t="s">
-        <v>270</v>
-      </c>
-      <c r="H215" t="s">
-        <v>271</v>
-      </c>
-      <c r="I215" t="s">
-        <v>272</v>
-      </c>
-      <c r="J215" t="s">
-        <v>272</v>
-      </c>
-      <c r="K215" t="s">
-        <v>270</v>
-      </c>
-      <c r="L215" t="s">
-        <v>273</v>
-      </c>
-      <c r="M215" t="s">
+        <v>268</v>
+      </c>
+      <c r="F215">
+        <v>0</v>
+      </c>
+      <c r="G215">
+        <v>3</v>
+      </c>
+      <c r="H215">
+        <v>6</v>
+      </c>
+      <c r="I215">
+        <v>5</v>
+      </c>
+      <c r="J215">
+        <v>5</v>
+      </c>
+      <c r="K215">
+        <v>3</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+      <c r="M215">
+        <v>67</v>
+      </c>
+      <c r="N215">
+        <v>1</v>
+      </c>
+      <c r="O215">
+        <v>1</v>
+      </c>
+      <c r="P215">
+        <v>1</v>
+      </c>
+      <c r="Q215">
+        <v>10</v>
+      </c>
+      <c r="R215">
+        <v>0</v>
+      </c>
+      <c r="S215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19">
+      <c r="A216" t="s">
+        <v>182</v>
+      </c>
+      <c r="B216" t="s">
+        <v>254</v>
+      </c>
+      <c r="C216">
+        <v>89</v>
+      </c>
+      <c r="D216">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="E216" t="s">
+        <v>259</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216">
+        <v>6</v>
+      </c>
+      <c r="H216">
+        <v>12</v>
+      </c>
+      <c r="I216">
+        <v>12</v>
+      </c>
+      <c r="J216">
+        <v>12</v>
+      </c>
+      <c r="K216">
+        <v>6</v>
+      </c>
+      <c r="L216">
+        <v>3</v>
+      </c>
+      <c r="M216">
+        <v>154</v>
+      </c>
+      <c r="N216">
+        <v>2</v>
+      </c>
+      <c r="O216">
+        <v>2</v>
+      </c>
+      <c r="P216">
+        <v>2</v>
+      </c>
+      <c r="Q216">
+        <v>16</v>
+      </c>
+      <c r="R216">
+        <v>1</v>
+      </c>
+      <c r="S216">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19">
+      <c r="A217" t="s">
+        <v>183</v>
+      </c>
+      <c r="B217" t="s">
+        <v>254</v>
+      </c>
+      <c r="C217">
+        <v>105</v>
+      </c>
+      <c r="D217">
+        <v>16.12</v>
+      </c>
+      <c r="E217" t="s">
+        <v>259</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217">
+        <v>7</v>
+      </c>
+      <c r="H217">
+        <v>14</v>
+      </c>
+      <c r="I217">
+        <v>14</v>
+      </c>
+      <c r="J217">
+        <v>14</v>
+      </c>
+      <c r="K217">
+        <v>7</v>
+      </c>
+      <c r="L217">
+        <v>3</v>
+      </c>
+      <c r="M217">
+        <v>200</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217">
+        <v>2</v>
+      </c>
+      <c r="P217">
+        <v>2</v>
+      </c>
+      <c r="Q217">
+        <v>10</v>
+      </c>
+      <c r="R217">
+        <v>1</v>
+      </c>
+      <c r="S217">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19">
+      <c r="A218" t="s">
+        <v>184</v>
+      </c>
+      <c r="B218" t="s">
+        <v>255</v>
+      </c>
+      <c r="C218" t="s">
+        <v>256</v>
+      </c>
+      <c r="D218" t="s">
+        <v>257</v>
+      </c>
+      <c r="E218" t="s">
+        <v>259</v>
+      </c>
+      <c r="F218" t="s">
         <v>274</v>
       </c>
-      <c r="N215" t="s">
+      <c r="G218" t="s">
         <v>275</v>
       </c>
-      <c r="O215" t="s">
-        <v>275</v>
-      </c>
-      <c r="P215" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q215" t="s">
+      <c r="H218" t="s">
         <v>276</v>
       </c>
-      <c r="R215" t="s">
-        <v>269</v>
-      </c>
-      <c r="S215" t="s">
-        <v>273</v>
+      <c r="I218" t="s">
+        <v>276</v>
+      </c>
+      <c r="J218" t="s">
+        <v>276</v>
+      </c>
+      <c r="K218" t="s">
+        <v>277</v>
+      </c>
+      <c r="L218" t="s">
+        <v>278</v>
+      </c>
+      <c r="M218" t="s">
+        <v>279</v>
+      </c>
+      <c r="N218" t="s">
+        <v>280</v>
+      </c>
+      <c r="O218" t="s">
+        <v>280</v>
+      </c>
+      <c r="P218" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>282</v>
+      </c>
+      <c r="R218" t="s">
+        <v>274</v>
+      </c>
+      <c r="S218" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_cutting.xlsx
+++ b/data/dsc_cane_cutting.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="285">
   <si>
     <t>Date</t>
   </si>
@@ -73,24 +78,39 @@
     <t>T/Transporter</t>
   </si>
   <si>
+    <t>Season</t>
+  </si>
+  <si>
     <t>2025-04-27</t>
   </si>
   <si>
+    <t>N14</t>
+  </si>
+  <si>
     <t>2025-04-30</t>
   </si>
   <si>
     <t>2025-05-03</t>
   </si>
   <si>
+    <t>R579</t>
+  </si>
+  <si>
     <t>2025-05-04</t>
   </si>
   <si>
+    <t>N41</t>
+  </si>
+  <si>
     <t>2025-05-06</t>
   </si>
   <si>
     <t>2025-05-08</t>
   </si>
   <si>
+    <t>R570</t>
+  </si>
+  <si>
     <t>2025-05-09</t>
   </si>
   <si>
@@ -103,6 +123,9 @@
     <t>2025-05-15</t>
   </si>
   <si>
+    <t>97F1692</t>
+  </si>
+  <si>
     <t>2025-05-16</t>
   </si>
   <si>
@@ -124,6 +147,9 @@
     <t>2025-05-26</t>
   </si>
   <si>
+    <t>XX</t>
+  </si>
+  <si>
     <t>2025-05-27</t>
   </si>
   <si>
@@ -133,9 +159,15 @@
     <t>2025-05-29</t>
   </si>
   <si>
+    <t>MN1</t>
+  </si>
+  <si>
     <t>2025-06-02</t>
   </si>
   <si>
+    <t>N23</t>
+  </si>
+  <si>
     <t>2025-06-03</t>
   </si>
   <si>
@@ -148,9 +180,15 @@
     <t>2025-06-08</t>
   </si>
   <si>
+    <t>N36</t>
+  </si>
+  <si>
     <t>2025-06-09</t>
   </si>
   <si>
+    <t>N25</t>
+  </si>
+  <si>
     <t>2025-06-10</t>
   </si>
   <si>
@@ -256,12 +294,18 @@
     <t>2025-07-23</t>
   </si>
   <si>
+    <t>MIX</t>
+  </si>
+  <si>
     <t>2025-07-24</t>
   </si>
   <si>
     <t>2025-07-25</t>
   </si>
   <si>
+    <t>XXX</t>
+  </si>
+  <si>
     <t>2025-07-26</t>
   </si>
   <si>
@@ -304,6 +348,9 @@
     <t>2025-08-10</t>
   </si>
   <si>
+    <t>CO62175</t>
+  </si>
+  <si>
     <t>2025-08-11</t>
   </si>
   <si>
@@ -331,6 +378,9 @@
     <t>2025-08-19</t>
   </si>
   <si>
+    <t>90F0613</t>
+  </si>
+  <si>
     <t>2025-08-20</t>
   </si>
   <si>
@@ -340,60 +390,123 @@
     <t>2025-08-23</t>
   </si>
   <si>
+    <t>5701C</t>
+  </si>
+  <si>
+    <t>5292</t>
+  </si>
+  <si>
     <t>2025-08-24</t>
   </si>
   <si>
+    <t>3122</t>
+  </si>
+  <si>
     <t>2025-08-25</t>
   </si>
   <si>
+    <t>2102</t>
+  </si>
+  <si>
     <t>2025-08-26</t>
   </si>
   <si>
+    <t>2303</t>
+  </si>
+  <si>
     <t>2025-08-27</t>
   </si>
   <si>
     <t>2025-08-28</t>
   </si>
   <si>
+    <t>5702</t>
+  </si>
+  <si>
     <t>2025-08-29</t>
   </si>
   <si>
+    <t>4212</t>
+  </si>
+  <si>
     <t>2025-08-30</t>
   </si>
   <si>
+    <t>2319</t>
+  </si>
+  <si>
     <t>2025-09-02</t>
   </si>
   <si>
     <t>2025-09-06</t>
   </si>
   <si>
+    <t>4291</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
     <t>2025-09-07</t>
   </si>
   <si>
+    <t>5406</t>
+  </si>
+  <si>
     <t>2025-09-08</t>
   </si>
   <si>
+    <t>5130</t>
+  </si>
+  <si>
     <t>2025-09-09</t>
   </si>
   <si>
+    <t>2516</t>
+  </si>
+  <si>
     <t>2025-09-10</t>
   </si>
   <si>
+    <t>5501</t>
+  </si>
+  <si>
     <t>2025-09-13</t>
   </si>
   <si>
+    <t>2107</t>
+  </si>
+  <si>
     <t>2025-09-14</t>
   </si>
   <si>
+    <t>5507</t>
+  </si>
+  <si>
     <t>2025-09-15</t>
   </si>
   <si>
+    <t>4230</t>
+  </si>
+  <si>
+    <t>4228</t>
+  </si>
+  <si>
     <t>2025-09-16</t>
   </si>
   <si>
+    <t>5106</t>
+  </si>
+  <si>
     <t>2025-09-17</t>
   </si>
   <si>
+    <t>4231</t>
+  </si>
+  <si>
     <t>2025-09-18</t>
   </si>
   <si>
@@ -403,87 +516,171 @@
     <t>2025-09-20</t>
   </si>
   <si>
+    <t>5118</t>
+  </si>
+  <si>
     <t>2025-09-23</t>
   </si>
   <si>
+    <t>5413</t>
+  </si>
+  <si>
     <t>2025-09-24</t>
   </si>
   <si>
+    <t>2513</t>
+  </si>
+  <si>
     <t>2025-09-25</t>
   </si>
   <si>
     <t>2025-09-26</t>
   </si>
   <si>
+    <t>5212</t>
+  </si>
+  <si>
     <t>2025-09-27</t>
   </si>
   <si>
+    <t>3402</t>
+  </si>
+  <si>
     <t>2025-09-29</t>
   </si>
   <si>
+    <t>5128</t>
+  </si>
+  <si>
     <t>2025-09-30</t>
   </si>
   <si>
+    <t>5404</t>
+  </si>
+  <si>
     <t>2025-10-01</t>
   </si>
   <si>
+    <t>2504</t>
+  </si>
+  <si>
     <t>2025-10-02</t>
   </si>
   <si>
+    <t>5120</t>
+  </si>
+  <si>
     <t>2025-10-03</t>
   </si>
   <si>
+    <t>5509</t>
+  </si>
+  <si>
+    <t>5411</t>
+  </si>
+  <si>
     <t>2025-10-05</t>
   </si>
   <si>
+    <t>4319</t>
+  </si>
+  <si>
     <t>2025-10-06</t>
   </si>
   <si>
+    <t>1220</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
     <t>2025-10-07</t>
   </si>
   <si>
     <t>2025-10-08</t>
   </si>
   <si>
+    <t>5214</t>
+  </si>
+  <si>
     <t>2025-10-09</t>
   </si>
   <si>
+    <t>5435</t>
+  </si>
+  <si>
+    <t>5390</t>
+  </si>
+  <si>
     <t>2025-10-10</t>
   </si>
   <si>
+    <t>5291</t>
+  </si>
+  <si>
     <t>2025-10-11</t>
   </si>
   <si>
     <t>2025-10-14</t>
   </si>
   <si>
+    <t>5508</t>
+  </si>
+  <si>
     <t>2025-10-15</t>
   </si>
   <si>
+    <t>5461</t>
+  </si>
+  <si>
     <t>2025-10-16</t>
   </si>
   <si>
+    <t>3413</t>
+  </si>
+  <si>
     <t>2025-10-17</t>
   </si>
   <si>
+    <t>3113</t>
+  </si>
+  <si>
     <t>2025-10-18</t>
   </si>
   <si>
+    <t>1219</t>
+  </si>
+  <si>
     <t>2025-10-19</t>
   </si>
   <si>
+    <t>4320</t>
+  </si>
+  <si>
     <t>2025-10-21</t>
   </si>
   <si>
+    <t>4390</t>
+  </si>
+  <si>
     <t>2025-10-22</t>
   </si>
   <si>
+    <t>2211</t>
+  </si>
+  <si>
     <t>2025-10-23</t>
   </si>
   <si>
+    <t>4126</t>
+  </si>
+  <si>
     <t>2025-10-24</t>
   </si>
   <si>
+    <t>5304</t>
+  </si>
+  <si>
     <t>2025-10-25</t>
   </si>
   <si>
@@ -496,30 +693,54 @@
     <t>2025-10-31</t>
   </si>
   <si>
+    <t>5652</t>
+  </si>
+  <si>
     <t>2025-11-01</t>
   </si>
   <si>
+    <t>5653</t>
+  </si>
+  <si>
     <t>2025-11-02</t>
   </si>
   <si>
+    <t>5108</t>
+  </si>
+  <si>
     <t>2025-11-03</t>
   </si>
   <si>
+    <t>4124</t>
+  </si>
+  <si>
     <t>2025-11-04</t>
   </si>
   <si>
+    <t>5490</t>
+  </si>
+  <si>
     <t>2025-11-05</t>
   </si>
   <si>
+    <t>3111</t>
+  </si>
+  <si>
     <t>2025-11-06</t>
   </si>
   <si>
     <t>2025-11-08</t>
   </si>
   <si>
+    <t>2210</t>
+  </si>
+  <si>
     <t>2025-11-10</t>
   </si>
   <si>
+    <t>5632</t>
+  </si>
+  <si>
     <t>2025-11-11</t>
   </si>
   <si>
@@ -529,313 +750,103 @@
     <t>2025-11-17</t>
   </si>
   <si>
+    <t>3313</t>
+  </si>
+  <si>
     <t>2025-11-18</t>
   </si>
   <si>
+    <t>5502</t>
+  </si>
+  <si>
+    <t>5307</t>
+  </si>
+  <si>
+    <t>5313</t>
+  </si>
+  <si>
     <t>2025-11-19</t>
   </si>
   <si>
     <t>2025-11-20</t>
   </si>
   <si>
+    <t>4314</t>
+  </si>
+  <si>
     <t>2025-11-21</t>
   </si>
   <si>
     <t>2025-11-25</t>
   </si>
   <si>
+    <t>2509</t>
+  </si>
+  <si>
     <t>2025-11-26</t>
   </si>
   <si>
+    <t>2215</t>
+  </si>
+  <si>
     <t>2025-11-27</t>
   </si>
   <si>
+    <t>2321</t>
+  </si>
+  <si>
     <t>2025-11-30</t>
   </si>
   <si>
+    <t>3416</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>5631</t>
+  </si>
+  <si>
     <t>2025-12-01</t>
   </si>
   <si>
+    <t>4214</t>
+  </si>
+  <si>
     <t>2025-12-02</t>
   </si>
   <si>
+    <t>5459</t>
+  </si>
+  <si>
+    <t>5633</t>
+  </si>
+  <si>
     <t>2025-12-03</t>
   </si>
   <si>
     <t>2025-12-07</t>
   </si>
   <si>
+    <t>2112</t>
+  </si>
+  <si>
     <t>2025-12-08</t>
   </si>
   <si>
     <t>2025-12-09</t>
   </si>
   <si>
-    <t>5701C</t>
-  </si>
-  <si>
-    <t>5292</t>
-  </si>
-  <si>
-    <t>3122</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>5702</t>
-  </si>
-  <si>
-    <t>4212</t>
-  </si>
-  <si>
-    <t>2319</t>
-  </si>
-  <si>
-    <t>4291</t>
-  </si>
-  <si>
-    <t>3406</t>
-  </si>
-  <si>
-    <t>5406</t>
-  </si>
-  <si>
-    <t>5130</t>
-  </si>
-  <si>
-    <t>2516</t>
-  </si>
-  <si>
-    <t>5501</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>5507</t>
-  </si>
-  <si>
-    <t>4230</t>
-  </si>
-  <si>
-    <t>4228</t>
-  </si>
-  <si>
-    <t>5106</t>
-  </si>
-  <si>
-    <t>4231</t>
-  </si>
-  <si>
-    <t>5118</t>
-  </si>
-  <si>
-    <t>5413</t>
-  </si>
-  <si>
-    <t>2513</t>
-  </si>
-  <si>
-    <t>5212</t>
-  </si>
-  <si>
-    <t>3402</t>
-  </si>
-  <si>
-    <t>5128</t>
-  </si>
-  <si>
-    <t>5404</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>5120</t>
-  </si>
-  <si>
-    <t>5509</t>
-  </si>
-  <si>
-    <t>5411</t>
-  </si>
-  <si>
-    <t>4319</t>
-  </si>
-  <si>
-    <t>1220</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>5214</t>
-  </si>
-  <si>
-    <t>5435</t>
-  </si>
-  <si>
-    <t>5390</t>
-  </si>
-  <si>
-    <t>5291</t>
-  </si>
-  <si>
-    <t>5508</t>
-  </si>
-  <si>
-    <t>5461</t>
-  </si>
-  <si>
-    <t>3413</t>
-  </si>
-  <si>
-    <t>3113</t>
-  </si>
-  <si>
-    <t>1219</t>
-  </si>
-  <si>
-    <t>4320</t>
-  </si>
-  <si>
-    <t>4390</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>4126</t>
-  </si>
-  <si>
-    <t>5304</t>
-  </si>
-  <si>
-    <t>5652</t>
-  </si>
-  <si>
-    <t>5653</t>
-  </si>
-  <si>
-    <t>5108</t>
-  </si>
-  <si>
-    <t>4124</t>
-  </si>
-  <si>
-    <t>5490</t>
-  </si>
-  <si>
-    <t>3111</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>5632</t>
-  </si>
-  <si>
-    <t>3313</t>
-  </si>
-  <si>
-    <t>5502</t>
-  </si>
-  <si>
-    <t>5307</t>
-  </si>
-  <si>
-    <t>5313</t>
-  </si>
-  <si>
-    <t>4314</t>
-  </si>
-  <si>
-    <t>2509</t>
-  </si>
-  <si>
-    <t>2215</t>
-  </si>
-  <si>
-    <t>2321</t>
-  </si>
-  <si>
-    <t>3416</t>
-  </si>
-  <si>
-    <t>5631</t>
-  </si>
-  <si>
-    <t>4214</t>
-  </si>
-  <si>
-    <t>5459</t>
-  </si>
-  <si>
-    <t>5633</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
     <t>2113</t>
   </si>
   <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>17.92</t>
-  </si>
-  <si>
-    <t>N14</t>
-  </si>
-  <si>
-    <t>R579</t>
-  </si>
-  <si>
-    <t>N41</t>
-  </si>
-  <si>
-    <t>R570</t>
-  </si>
-  <si>
-    <t>97F1692</t>
-  </si>
-  <si>
-    <t>XX</t>
-  </si>
-  <si>
-    <t>MN1</t>
-  </si>
-  <si>
-    <t>N23</t>
-  </si>
-  <si>
-    <t>N36</t>
-  </si>
-  <si>
-    <t>N25</t>
-  </si>
-  <si>
-    <t>MIX</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>CO62175</t>
-  </si>
-  <si>
-    <t>90F0613</t>
-  </si>
-  <si>
-    <t>xx</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>1</t>
@@ -844,35 +855,32 @@
     <t>9</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>12</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>21</t>
+    <t>200</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>2025/26</t>
+  </si>
+  <si>
+    <t>2021/22</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -883,10 +891,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -935,6 +940,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1222,11 +1235,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S218"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T219"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1284,10 +1297,13 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>5290</v>
@@ -1299,7 +1315,7 @@
         <v>3.8</v>
       </c>
       <c r="E2" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1343,10 +1359,13 @@
       <c r="S2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>3109</v>
@@ -1358,7 +1377,7 @@
         <v>3.6</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1402,10 +1421,13 @@
       <c r="S3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>5217</v>
@@ -1417,7 +1439,7 @@
         <v>7.72</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1461,10 +1483,13 @@
       <c r="S4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>2405</v>
@@ -1476,7 +1501,7 @@
         <v>6.6</v>
       </c>
       <c r="E5" t="s">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1520,10 +1545,13 @@
       <c r="S5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>4222</v>
@@ -1535,7 +1563,7 @@
         <v>3.9</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1579,10 +1607,13 @@
       <c r="S6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>4224</v>
@@ -1594,7 +1625,7 @@
         <v>2.36</v>
       </c>
       <c r="E7" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1638,10 +1669,13 @@
       <c r="S7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>2205</v>
@@ -1650,10 +1684,10 @@
         <v>184</v>
       </c>
       <c r="D8">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1697,10 +1731,13 @@
       <c r="S8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>2207</v>
@@ -1712,7 +1749,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1756,10 +1793,13 @@
       <c r="S9">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10">
         <v>2205</v>
@@ -1771,7 +1811,7 @@
         <v>4.3</v>
       </c>
       <c r="E10" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1815,10 +1855,13 @@
       <c r="S10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>2207</v>
@@ -1830,7 +1873,7 @@
         <v>4.5</v>
       </c>
       <c r="E11" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1874,10 +1917,13 @@
       <c r="S11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>2304</v>
@@ -1889,7 +1935,7 @@
         <v>3.6</v>
       </c>
       <c r="E12" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1933,10 +1979,13 @@
       <c r="S12">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>1112</v>
@@ -1945,10 +1994,10 @@
         <v>102</v>
       </c>
       <c r="D13">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E13" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1992,10 +2041,13 @@
       <c r="S13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="T13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B14">
         <v>4107</v>
@@ -2007,7 +2059,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2051,10 +2103,13 @@
       <c r="S14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>5219</v>
@@ -2066,7 +2121,7 @@
         <v>3.9</v>
       </c>
       <c r="E15" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2110,10 +2165,13 @@
       <c r="S15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>5216</v>
@@ -2125,7 +2183,7 @@
         <v>3.8</v>
       </c>
       <c r="E16" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2169,10 +2227,13 @@
       <c r="S16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="T16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>4311</v>
@@ -2184,7 +2245,7 @@
         <v>5.7</v>
       </c>
       <c r="E17" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2228,10 +2289,13 @@
       <c r="S17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B18">
         <v>5513</v>
@@ -2240,10 +2304,10 @@
         <v>52</v>
       </c>
       <c r="D18">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E18" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2287,10 +2351,13 @@
       <c r="S18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="T18" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B19">
         <v>5510</v>
@@ -2302,7 +2369,7 @@
         <v>1.3</v>
       </c>
       <c r="E19" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2346,10 +2413,13 @@
       <c r="S19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B20">
         <v>2106</v>
@@ -2361,7 +2431,7 @@
         <v>2.5</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2405,10 +2475,13 @@
       <c r="S20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="T20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B21">
         <v>1125</v>
@@ -2417,10 +2490,10 @@
         <v>98</v>
       </c>
       <c r="D21">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E21" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2464,10 +2537,13 @@
       <c r="S21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:19">
+      <c r="T21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B22">
         <v>3308</v>
@@ -2479,7 +2555,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" t="s">
-        <v>263</v>
+        <v>42</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2523,10 +2599,13 @@
       <c r="S22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:19">
+      <c r="T22" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <v>2526</v>
@@ -2538,7 +2617,7 @@
         <v>23.7</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2582,10 +2661,13 @@
       <c r="S23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:19">
+      <c r="T23" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B24">
         <v>2526</v>
@@ -2597,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2641,10 +2723,13 @@
       <c r="S24">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:19">
+      <c r="T24" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>4104</v>
@@ -2656,7 +2741,7 @@
         <v>3.04</v>
       </c>
       <c r="E25" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2700,10 +2785,13 @@
       <c r="S25">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:19">
+      <c r="T25" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>5301</v>
@@ -2715,7 +2803,7 @@
         <v>5.5</v>
       </c>
       <c r="E26" t="s">
-        <v>265</v>
+        <v>48</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2759,10 +2847,13 @@
       <c r="S26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:19">
+      <c r="T26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B27">
         <v>5434</v>
@@ -2771,10 +2862,10 @@
         <v>78</v>
       </c>
       <c r="D27">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="E27" t="s">
-        <v>263</v>
+        <v>42</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2818,10 +2909,13 @@
       <c r="S27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="T27" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B28">
         <v>4211</v>
@@ -2833,7 +2927,7 @@
         <v>7.95</v>
       </c>
       <c r="E28" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2877,10 +2971,13 @@
       <c r="S28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="T28" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B29">
         <v>4211</v>
@@ -2889,10 +2986,10 @@
         <v>50</v>
       </c>
       <c r="D29">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E29" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2936,10 +3033,13 @@
       <c r="S29">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:19">
+      <c r="T29" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B30">
         <v>5442</v>
@@ -2951,7 +3051,7 @@
         <v>3.27</v>
       </c>
       <c r="E30" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2995,10 +3095,13 @@
       <c r="S30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:19">
+      <c r="T30" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B31">
         <v>3302</v>
@@ -3010,7 +3113,7 @@
         <v>8.31</v>
       </c>
       <c r="E31" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3054,10 +3157,13 @@
       <c r="S31">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="T31" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B32">
         <v>3302</v>
@@ -3069,7 +3175,7 @@
         <v>3.59</v>
       </c>
       <c r="E32" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3113,10 +3219,13 @@
       <c r="S32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="T32" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B33">
         <v>5211</v>
@@ -3128,7 +3237,7 @@
         <v>2.13</v>
       </c>
       <c r="E33" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3172,10 +3281,13 @@
       <c r="S33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="T33" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B34">
         <v>5218</v>
@@ -3187,7 +3299,7 @@
         <v>4.8</v>
       </c>
       <c r="E34" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3231,10 +3343,13 @@
       <c r="S34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="T34" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B35">
         <v>5454</v>
@@ -3246,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3290,10 +3405,13 @@
       <c r="S35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="T35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B36">
         <v>3493</v>
@@ -3305,7 +3423,7 @@
         <v>6.45</v>
       </c>
       <c r="E36" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3349,10 +3467,13 @@
       <c r="S36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="T36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B37">
         <v>3120</v>
@@ -3364,7 +3485,7 @@
         <v>4.72</v>
       </c>
       <c r="E37" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3408,10 +3529,13 @@
       <c r="S37">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="T37" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B38">
         <v>5454</v>
@@ -3423,7 +3547,7 @@
         <v>1.8</v>
       </c>
       <c r="E38" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3467,10 +3591,13 @@
       <c r="S38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="T38" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B39">
         <v>3120</v>
@@ -3482,7 +3609,7 @@
         <v>5.86</v>
       </c>
       <c r="E39" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3526,10 +3653,13 @@
       <c r="S39">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="T39" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B40">
         <v>1211</v>
@@ -3541,7 +3671,7 @@
         <v>6.18</v>
       </c>
       <c r="E40" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3585,10 +3715,13 @@
       <c r="S40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="T40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B41">
         <v>1211</v>
@@ -3600,7 +3733,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3644,10 +3777,13 @@
       <c r="S41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="T41" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B42">
         <v>2307</v>
@@ -3659,7 +3795,7 @@
         <v>7.13</v>
       </c>
       <c r="E42" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3703,10 +3839,13 @@
       <c r="S42">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="T42" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B43">
         <v>5204</v>
@@ -3715,10 +3854,10 @@
         <v>182</v>
       </c>
       <c r="D43">
-        <v>9.199999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="E43" t="s">
-        <v>265</v>
+        <v>48</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3762,10 +3901,13 @@
       <c r="S43">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:19">
+      <c r="T43" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B44">
         <v>4208</v>
@@ -3777,7 +3919,7 @@
         <v>5.81</v>
       </c>
       <c r="E44" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3821,10 +3963,13 @@
       <c r="S44">
         <v>9</v>
       </c>
-    </row>
-    <row r="45" spans="1:19">
+      <c r="T44" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B45">
         <v>2302</v>
@@ -3836,7 +3981,7 @@
         <v>4.09</v>
       </c>
       <c r="E45" t="s">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3880,10 +4025,13 @@
       <c r="S45">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="T45" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B46">
         <v>5117</v>
@@ -3895,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3939,10 +4087,13 @@
       <c r="S46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:19">
+      <c r="T46" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B47">
         <v>5101</v>
@@ -3951,10 +4102,10 @@
         <v>181</v>
       </c>
       <c r="D47">
-        <v>8.220000000000001</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="E47" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3998,10 +4149,13 @@
       <c r="S47">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:19">
+      <c r="T47" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B48">
         <v>1221</v>
@@ -4013,7 +4167,7 @@
         <v>5.13</v>
       </c>
       <c r="E48" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4057,10 +4211,13 @@
       <c r="S48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="T48" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B49">
         <v>5101</v>
@@ -4072,7 +4229,7 @@
         <v>1.81</v>
       </c>
       <c r="E49" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -4116,10 +4273,13 @@
       <c r="S49">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="T49" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B50">
         <v>5113</v>
@@ -4131,7 +4291,7 @@
         <v>7.95</v>
       </c>
       <c r="E50" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -4175,10 +4335,13 @@
       <c r="S50">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:19">
+      <c r="T50" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B51">
         <v>1221</v>
@@ -4190,7 +4353,7 @@
         <v>0.64</v>
       </c>
       <c r="E51" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -4234,10 +4397,13 @@
       <c r="S51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:19">
+      <c r="T51" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B52">
         <v>2515</v>
@@ -4249,7 +4415,7 @@
         <v>6.13</v>
       </c>
       <c r="E52" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4293,10 +4459,13 @@
       <c r="S52">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:19">
+      <c r="T52" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B53">
         <v>5458</v>
@@ -4308,7 +4477,7 @@
         <v>2.77</v>
       </c>
       <c r="E53" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4352,10 +4521,13 @@
       <c r="S53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="T53" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B54">
         <v>5408</v>
@@ -4364,10 +4536,10 @@
         <v>107</v>
       </c>
       <c r="D54">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E54" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4411,10 +4583,13 @@
       <c r="S54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:19">
+      <c r="T54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B55">
         <v>5209</v>
@@ -4426,7 +4601,7 @@
         <v>5.24</v>
       </c>
       <c r="E55" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4470,10 +4645,13 @@
       <c r="S55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:19">
+      <c r="T55" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B56">
         <v>5305</v>
@@ -4485,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4529,10 +4707,13 @@
       <c r="S56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="T56" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B57">
         <v>5305</v>
@@ -4544,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4588,10 +4769,13 @@
       <c r="S57">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="T57" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B58">
         <v>1121</v>
@@ -4603,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4647,10 +4831,13 @@
       <c r="S58">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:19">
+      <c r="T58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B59">
         <v>5205</v>
@@ -4662,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4706,10 +4893,13 @@
       <c r="S59">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="T59" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B60">
         <v>5111</v>
@@ -4721,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4765,10 +4955,13 @@
       <c r="S60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="T60" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B61">
         <v>5122</v>
@@ -4780,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4824,10 +5017,13 @@
       <c r="S61">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="1:19">
+      <c r="T61" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B62">
         <v>5111</v>
@@ -4839,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4883,10 +5079,13 @@
       <c r="S62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:19">
+      <c r="T62" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B63">
         <v>3314</v>
@@ -4898,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4942,10 +5141,13 @@
       <c r="S63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:19">
+      <c r="T63" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B64">
         <v>5305</v>
@@ -4957,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -5001,10 +5203,13 @@
       <c r="S64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:19">
+      <c r="T64" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B65">
         <v>5203</v>
@@ -5016,7 +5221,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -5060,10 +5265,13 @@
       <c r="S65">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:19">
+      <c r="T65" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B66">
         <v>5207</v>
@@ -5075,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -5119,10 +5327,13 @@
       <c r="S66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:19">
+      <c r="T66" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B67">
         <v>5207</v>
@@ -5134,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -5178,10 +5389,13 @@
       <c r="S67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:19">
+      <c r="T67" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B68">
         <v>5105</v>
@@ -5193,7 +5407,7 @@
         <v>6.54</v>
       </c>
       <c r="E68" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -5237,10 +5451,13 @@
       <c r="S68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:19">
+      <c r="T68" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B69">
         <v>5105</v>
@@ -5252,7 +5469,7 @@
         <v>6.31</v>
       </c>
       <c r="E69" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -5296,10 +5513,13 @@
       <c r="S69">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" spans="1:19">
+      <c r="T69" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B70">
         <v>5504</v>
@@ -5311,7 +5531,7 @@
         <v>3.72</v>
       </c>
       <c r="E70" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -5355,10 +5575,13 @@
       <c r="S70">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="1:19">
+      <c r="T70" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B71">
         <v>2214</v>
@@ -5370,7 +5593,7 @@
         <v>3.56</v>
       </c>
       <c r="E71" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5414,10 +5637,13 @@
       <c r="S71">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" spans="1:19">
+      <c r="T71" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B72">
         <v>2214</v>
@@ -5429,7 +5655,7 @@
         <v>19.54</v>
       </c>
       <c r="E72" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5473,10 +5699,13 @@
       <c r="S72">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="1:19">
+      <c r="T72" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B73">
         <v>5409</v>
@@ -5488,7 +5717,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5532,10 +5761,13 @@
       <c r="S73">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" spans="1:19">
+      <c r="T73" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B74">
         <v>3403</v>
@@ -5547,7 +5779,7 @@
         <v>5.41</v>
       </c>
       <c r="E74" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5591,10 +5823,13 @@
       <c r="S74">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:19">
+      <c r="T74" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B75">
         <v>4117</v>
@@ -5606,7 +5841,7 @@
         <v>5.32</v>
       </c>
       <c r="E75" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5650,10 +5885,13 @@
       <c r="S75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:19">
+      <c r="T75" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B76">
         <v>5115</v>
@@ -5665,7 +5903,7 @@
         <v>7.32</v>
       </c>
       <c r="E76" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5709,10 +5947,13 @@
       <c r="S76">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:19">
+      <c r="T76" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B77">
         <v>5202</v>
@@ -5724,7 +5965,7 @@
         <v>13.1</v>
       </c>
       <c r="E77" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5768,10 +6009,13 @@
       <c r="S77">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:19">
+      <c r="T77" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B78">
         <v>3110</v>
@@ -5780,10 +6024,10 @@
         <v>159</v>
       </c>
       <c r="D78">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E78" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5827,10 +6071,13 @@
       <c r="S78">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:19">
+      <c r="T78" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B79">
         <v>4111</v>
@@ -5842,7 +6089,7 @@
         <v>3.12</v>
       </c>
       <c r="E79" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5886,10 +6133,13 @@
       <c r="S79">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:19">
+      <c r="T79" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B80">
         <v>4410</v>
@@ -5898,10 +6148,10 @@
         <v>11</v>
       </c>
       <c r="D80">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E80" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5945,10 +6195,13 @@
       <c r="S80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:19">
+      <c r="T80" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B81">
         <v>5601</v>
@@ -5960,7 +6213,7 @@
         <v>4.68</v>
       </c>
       <c r="E81" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -6004,10 +6257,13 @@
       <c r="S81">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:19">
+      <c r="T81" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>1135</v>
@@ -6019,7 +6275,7 @@
         <v>0.85</v>
       </c>
       <c r="E82" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -6063,10 +6319,13 @@
       <c r="S82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:19">
+      <c r="T82" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B83">
         <v>5624</v>
@@ -6078,7 +6337,7 @@
         <v>5.36</v>
       </c>
       <c r="E83" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -6122,10 +6381,13 @@
       <c r="S83">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="T83" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B84">
         <v>4317</v>
@@ -6137,7 +6399,7 @@
         <v>3.64</v>
       </c>
       <c r="E84" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -6181,10 +6443,13 @@
       <c r="S84">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="1:19">
+      <c r="T84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B85">
         <v>1223</v>
@@ -6196,7 +6461,7 @@
         <v>1.22</v>
       </c>
       <c r="E85" t="s">
-        <v>269</v>
+        <v>94</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -6240,10 +6505,13 @@
       <c r="S85">
         <v>3</v>
       </c>
-    </row>
-    <row r="86" spans="1:19">
+      <c r="T85" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B86">
         <v>5621</v>
@@ -6255,7 +6523,7 @@
         <v>7.13</v>
       </c>
       <c r="E86" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -6299,10 +6567,13 @@
       <c r="S86">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:19">
+      <c r="T86" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B87">
         <v>3493</v>
@@ -6314,7 +6585,7 @@
         <v>3.81</v>
       </c>
       <c r="E87" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -6358,10 +6629,13 @@
       <c r="S87">
         <v>3</v>
       </c>
-    </row>
-    <row r="88" spans="1:19">
+      <c r="T87" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B88">
         <v>5458</v>
@@ -6370,10 +6644,10 @@
         <v>214</v>
       </c>
       <c r="D88">
-        <v>9.720000000000001</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="E88" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -6417,10 +6691,13 @@
       <c r="S88">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:19">
+      <c r="T88" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B89">
         <v>5458</v>
@@ -6432,7 +6709,7 @@
         <v>2.35</v>
       </c>
       <c r="E89" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -6476,10 +6753,13 @@
       <c r="S89">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="T89" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B90">
         <v>2220</v>
@@ -6491,7 +6771,7 @@
         <v>6.36</v>
       </c>
       <c r="E90" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6535,10 +6815,13 @@
       <c r="S90">
         <v>5</v>
       </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="T90" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B91">
         <v>2220</v>
@@ -6550,7 +6833,7 @@
         <v>7.26</v>
       </c>
       <c r="E91" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -6594,10 +6877,13 @@
       <c r="S91">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="1:19">
+      <c r="T91" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B92">
         <v>2403</v>
@@ -6609,7 +6895,7 @@
         <v>1.02</v>
       </c>
       <c r="E92" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6653,10 +6939,13 @@
       <c r="S92">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="1:19">
+      <c r="T92" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B93">
         <v>2220</v>
@@ -6665,10 +6954,10 @@
         <v>98</v>
       </c>
       <c r="D93">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="E93" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -6712,10 +7001,13 @@
       <c r="S93">
         <v>4</v>
       </c>
-    </row>
-    <row r="94" spans="1:19">
+      <c r="T93" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B94">
         <v>5662</v>
@@ -6727,7 +7019,7 @@
         <v>3.71</v>
       </c>
       <c r="E94" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6771,10 +7063,13 @@
       <c r="S94">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="1:19">
+      <c r="T94" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B95">
         <v>2512</v>
@@ -6783,10 +7078,10 @@
         <v>75</v>
       </c>
       <c r="D95">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E95" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6830,10 +7125,13 @@
       <c r="S95">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:19">
+      <c r="T95" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B96">
         <v>2514</v>
@@ -6845,7 +7143,7 @@
         <v>16.21</v>
       </c>
       <c r="E96" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -6889,10 +7187,13 @@
       <c r="S96">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="1:19">
+      <c r="T96" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B97">
         <v>3106</v>
@@ -6904,7 +7205,7 @@
         <v>3.12</v>
       </c>
       <c r="E97" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6948,10 +7249,13 @@
       <c r="S97">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:19">
+      <c r="T97" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B98">
         <v>5663</v>
@@ -6963,7 +7267,7 @@
         <v>0.03</v>
       </c>
       <c r="E98" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -7007,10 +7311,13 @@
       <c r="S98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:19">
+      <c r="T98" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B99">
         <v>5661</v>
@@ -7019,10 +7326,10 @@
         <v>87</v>
       </c>
       <c r="D99">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="E99" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -7066,10 +7373,13 @@
       <c r="S99">
         <v>3</v>
       </c>
-    </row>
-    <row r="100" spans="1:19">
+      <c r="T99" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B100">
         <v>4240</v>
@@ -7081,7 +7391,7 @@
         <v>2.72</v>
       </c>
       <c r="E100" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -7125,10 +7435,13 @@
       <c r="S100">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:19">
+      <c r="T100" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B101">
         <v>5664</v>
@@ -7140,7 +7453,7 @@
         <v>9.32</v>
       </c>
       <c r="E101" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -7184,10 +7497,13 @@
       <c r="S101">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="1:19">
+      <c r="T101" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B102">
         <v>5663</v>
@@ -7196,10 +7512,10 @@
         <v>146</v>
       </c>
       <c r="D102">
-        <v>9.109999999999999</v>
+        <v>9.11</v>
       </c>
       <c r="E102" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -7243,10 +7559,13 @@
       <c r="S102">
         <v>9</v>
       </c>
-    </row>
-    <row r="103" spans="1:19">
+      <c r="T102" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B103">
         <v>5208</v>
@@ -7258,7 +7577,7 @@
         <v>5.07</v>
       </c>
       <c r="E103" t="s">
-        <v>270</v>
+        <v>109</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -7302,10 +7621,13 @@
       <c r="S103">
         <v>7</v>
       </c>
-    </row>
-    <row r="104" spans="1:19">
+      <c r="T103" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B104">
         <v>4241</v>
@@ -7317,7 +7639,7 @@
         <v>1.27</v>
       </c>
       <c r="E104" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -7361,10 +7683,13 @@
       <c r="S104">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:19">
+      <c r="T104" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B105">
         <v>4241</v>
@@ -7376,7 +7701,7 @@
         <v>0.05</v>
       </c>
       <c r="E105" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -7420,10 +7745,13 @@
       <c r="S105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:19">
+      <c r="T105" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B106">
         <v>1107</v>
@@ -7435,7 +7763,7 @@
         <v>6.75</v>
       </c>
       <c r="E106" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -7479,10 +7807,13 @@
       <c r="S106">
         <v>9</v>
       </c>
-    </row>
-    <row r="107" spans="1:19">
+      <c r="T106" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B107">
         <v>4412</v>
@@ -7494,7 +7825,7 @@
         <v>5.39</v>
       </c>
       <c r="E107" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -7538,10 +7869,13 @@
       <c r="S107">
         <v>5</v>
       </c>
-    </row>
-    <row r="108" spans="1:19">
+      <c r="T107" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B108">
         <v>5441</v>
@@ -7553,7 +7887,7 @@
         <v>2.66</v>
       </c>
       <c r="E108" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -7597,10 +7931,13 @@
       <c r="S108">
         <v>3</v>
       </c>
-    </row>
-    <row r="109" spans="1:19">
+      <c r="T108" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B109">
         <v>5440</v>
@@ -7612,7 +7949,7 @@
         <v>22.78</v>
       </c>
       <c r="E109" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7656,10 +7993,13 @@
       <c r="S109">
         <v>5</v>
       </c>
-    </row>
-    <row r="110" spans="1:19">
+      <c r="T109" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B110">
         <v>3115</v>
@@ -7671,7 +8011,7 @@
         <v>12.71</v>
       </c>
       <c r="E110" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -7715,10 +8055,13 @@
       <c r="S110">
         <v>5</v>
       </c>
-    </row>
-    <row r="111" spans="1:19">
+      <c r="T110" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B111">
         <v>4129</v>
@@ -7730,7 +8073,7 @@
         <v>5.35</v>
       </c>
       <c r="E111" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -7774,10 +8117,13 @@
       <c r="S111">
         <v>5</v>
       </c>
-    </row>
-    <row r="112" spans="1:19">
+      <c r="T111" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B112">
         <v>3317</v>
@@ -7789,7 +8135,7 @@
         <v>16.98</v>
       </c>
       <c r="E112" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -7833,10 +8179,13 @@
       <c r="S112">
         <v>5</v>
       </c>
-    </row>
-    <row r="113" spans="1:19">
+      <c r="T112" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B113">
         <v>1215</v>
@@ -7848,7 +8197,7 @@
         <v>6.32</v>
       </c>
       <c r="E113" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -7892,10 +8241,13 @@
       <c r="S113">
         <v>4</v>
       </c>
-    </row>
-    <row r="114" spans="1:19">
+      <c r="T113" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B114">
         <v>4239</v>
@@ -7907,7 +8259,7 @@
         <v>3.35</v>
       </c>
       <c r="E114" t="s">
-        <v>271</v>
+        <v>119</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7951,10 +8303,13 @@
       <c r="S114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:19">
+      <c r="T114" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B115">
         <v>4239</v>
@@ -7966,7 +8321,7 @@
         <v>0.24</v>
       </c>
       <c r="E115" t="s">
-        <v>271</v>
+        <v>119</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -8010,10 +8365,13 @@
       <c r="S115">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:19">
+      <c r="T115" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B116">
         <v>4209</v>
@@ -8025,7 +8383,7 @@
         <v>4.32</v>
       </c>
       <c r="E116" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -8069,13 +8427,16 @@
       <c r="S116">
         <v>5</v>
       </c>
-    </row>
-    <row r="117" spans="1:19">
+      <c r="T116" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="C117">
         <v>132</v>
@@ -8084,7 +8445,7 @@
         <v>9.23</v>
       </c>
       <c r="E117" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -8128,13 +8489,16 @@
       <c r="S117">
         <v>4</v>
       </c>
-    </row>
-    <row r="118" spans="1:19">
+      <c r="T117" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="C118">
         <v>22</v>
@@ -8143,7 +8507,7 @@
         <v>2.65</v>
       </c>
       <c r="E118" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -8187,13 +8551,16 @@
       <c r="S118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:19">
+      <c r="T118" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B119" t="s">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="C119">
         <v>178</v>
@@ -8202,7 +8569,7 @@
         <v>13.54</v>
       </c>
       <c r="E119" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -8246,13 +8613,16 @@
       <c r="S119">
         <v>5</v>
       </c>
-    </row>
-    <row r="120" spans="1:19">
+      <c r="T119" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -8261,7 +8631,7 @@
         <v>0.04</v>
       </c>
       <c r="E120" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -8305,13 +8675,16 @@
       <c r="S120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:19">
+      <c r="T120" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="C121">
         <v>31</v>
@@ -8320,7 +8693,7 @@
         <v>2.5</v>
       </c>
       <c r="E121" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -8364,13 +8737,16 @@
       <c r="S121">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:19">
+      <c r="T121" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="C122">
         <v>29</v>
@@ -8379,7 +8755,7 @@
         <v>1.65</v>
       </c>
       <c r="E122" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -8423,13 +8799,16 @@
       <c r="S122">
         <v>5</v>
       </c>
-    </row>
-    <row r="123" spans="1:19">
+      <c r="T122" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B123" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="C123">
         <v>219</v>
@@ -8438,7 +8817,7 @@
         <v>11.1</v>
       </c>
       <c r="E123" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -8482,13 +8861,16 @@
       <c r="S123">
         <v>5</v>
       </c>
-    </row>
-    <row r="124" spans="1:19">
+      <c r="T123" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B124" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="C124">
         <v>254</v>
@@ -8497,7 +8879,7 @@
         <v>17.37</v>
       </c>
       <c r="E124" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -8541,13 +8923,16 @@
       <c r="S124">
         <v>5</v>
       </c>
-    </row>
-    <row r="125" spans="1:19">
+      <c r="T124" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B125" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -8556,7 +8941,7 @@
         <v>0.49</v>
       </c>
       <c r="E125" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -8600,13 +8985,16 @@
       <c r="S125">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:19">
+      <c r="T125" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="C126">
         <v>153</v>
@@ -8615,7 +9003,7 @@
         <v>13.54</v>
       </c>
       <c r="E126" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8659,13 +9047,16 @@
       <c r="S126">
         <v>4</v>
       </c>
-    </row>
-    <row r="127" spans="1:19">
+      <c r="T126" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="C127">
         <v>179</v>
@@ -8674,7 +9065,7 @@
         <v>16.21</v>
       </c>
       <c r="E127" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -8718,13 +9109,16 @@
       <c r="S127">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:19">
+      <c r="T127" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="C128">
         <v>43</v>
@@ -8733,7 +9127,7 @@
         <v>3.67</v>
       </c>
       <c r="E128" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -8777,13 +9171,16 @@
       <c r="S128">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:19">
+      <c r="T128" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="C129">
         <v>19</v>
@@ -8792,7 +9189,7 @@
         <v>0.83</v>
       </c>
       <c r="E129" t="s">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8836,13 +9233,16 @@
       <c r="S129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:19">
+      <c r="T129" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B130" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="C130">
         <v>80</v>
@@ -8851,7 +9251,7 @@
         <v>5.37</v>
       </c>
       <c r="E130" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -8895,13 +9295,16 @@
       <c r="S130">
         <v>5</v>
       </c>
-    </row>
-    <row r="131" spans="1:19">
+      <c r="T130" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="B131" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="C131">
         <v>57</v>
@@ -8910,7 +9313,7 @@
         <v>3.47</v>
       </c>
       <c r="E131" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -8954,13 +9357,16 @@
       <c r="S131">
         <v>5</v>
       </c>
-    </row>
-    <row r="132" spans="1:19">
+      <c r="T131" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B132" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="C132">
         <v>133</v>
@@ -8969,7 +9375,7 @@
         <v>8.34</v>
       </c>
       <c r="E132" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -9013,22 +9419,25 @@
       <c r="S132">
         <v>5</v>
       </c>
-    </row>
-    <row r="133" spans="1:19">
+      <c r="T132" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="C133">
         <v>213</v>
       </c>
       <c r="D133">
-        <v>19.24</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="E133" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -9072,13 +9481,16 @@
       <c r="S133">
         <v>5</v>
       </c>
-    </row>
-    <row r="134" spans="1:19">
+      <c r="T133" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="C134">
         <v>34</v>
@@ -9087,7 +9499,7 @@
         <v>2.76</v>
       </c>
       <c r="E134" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9131,13 +9543,16 @@
       <c r="S134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:19">
+      <c r="T134" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="B135" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="C135">
         <v>196</v>
@@ -9146,7 +9561,7 @@
         <v>13.27</v>
       </c>
       <c r="E135" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -9190,13 +9605,16 @@
       <c r="S135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:19">
+      <c r="T135" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="B136" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="C136">
         <v>170</v>
@@ -9205,7 +9623,7 @@
         <v>13.93</v>
       </c>
       <c r="E136" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -9249,13 +9667,16 @@
       <c r="S136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:19">
+      <c r="T136" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="C137">
         <v>153</v>
@@ -9264,7 +9685,7 @@
         <v>9.32</v>
       </c>
       <c r="E137" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -9308,13 +9729,16 @@
       <c r="S137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:19">
+      <c r="T137" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="B138" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="C138">
         <v>138</v>
@@ -9323,7 +9747,7 @@
         <v>11.68</v>
       </c>
       <c r="E138" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -9367,22 +9791,25 @@
       <c r="S138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:19">
+      <c r="T138" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="C139">
         <v>26</v>
       </c>
       <c r="D139">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E139" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9426,13 +9853,16 @@
       <c r="S139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:19">
+      <c r="T139" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B140" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>153</v>
@@ -9441,7 +9871,7 @@
         <v>13.64</v>
       </c>
       <c r="E140" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -9485,13 +9915,16 @@
       <c r="S140">
         <v>5</v>
       </c>
-    </row>
-    <row r="141" spans="1:19">
+      <c r="T140" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B141" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="C141">
         <v>106</v>
@@ -9500,7 +9933,7 @@
         <v>2.34</v>
       </c>
       <c r="E141" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -9544,13 +9977,16 @@
       <c r="S141">
         <v>5</v>
       </c>
-    </row>
-    <row r="142" spans="1:19">
+      <c r="T141" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B142" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="C142">
         <v>133</v>
@@ -9559,7 +9995,7 @@
         <v>2.95</v>
       </c>
       <c r="E142" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -9603,13 +10039,16 @@
       <c r="S142">
         <v>5</v>
       </c>
-    </row>
-    <row r="143" spans="1:19">
+      <c r="T142" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="B143" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="C143">
         <v>141</v>
@@ -9618,7 +10057,7 @@
         <v>3.21</v>
       </c>
       <c r="E143" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -9662,13 +10101,16 @@
       <c r="S143">
         <v>5</v>
       </c>
-    </row>
-    <row r="144" spans="1:19">
+      <c r="T143" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B144" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>117</v>
@@ -9677,7 +10119,7 @@
         <v>2.64</v>
       </c>
       <c r="E144" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -9721,13 +10163,16 @@
       <c r="S144">
         <v>5</v>
       </c>
-    </row>
-    <row r="145" spans="1:19">
+      <c r="T144" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B145" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>78</v>
@@ -9736,7 +10181,7 @@
         <v>4.3</v>
       </c>
       <c r="E145" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -9780,13 +10225,16 @@
       <c r="S145">
         <v>5</v>
       </c>
-    </row>
-    <row r="146" spans="1:19">
+      <c r="T145" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="B146" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>172</v>
@@ -9795,7 +10243,7 @@
         <v>11.3</v>
       </c>
       <c r="E146" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -9839,13 +10287,16 @@
       <c r="S146">
         <v>5</v>
       </c>
-    </row>
-    <row r="147" spans="1:19">
+      <c r="T146" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="B147" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>171</v>
@@ -9854,7 +10305,7 @@
         <v>11.5</v>
       </c>
       <c r="E147" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -9898,13 +10349,16 @@
       <c r="S147">
         <v>4</v>
       </c>
-    </row>
-    <row r="148" spans="1:19">
+      <c r="T147" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="B148" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -9913,7 +10367,7 @@
         <v>0.2</v>
       </c>
       <c r="E148" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9957,13 +10411,16 @@
       <c r="S148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:19">
+      <c r="T148" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="B149" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>157</v>
@@ -9972,7 +10429,7 @@
         <v>13.21</v>
       </c>
       <c r="E149" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -10016,13 +10473,16 @@
       <c r="S149">
         <v>5</v>
       </c>
-    </row>
-    <row r="150" spans="1:19">
+      <c r="T149" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="B150" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>72</v>
@@ -10031,7 +10491,7 @@
         <v>5.32</v>
       </c>
       <c r="E150" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -10075,22 +10535,25 @@
       <c r="S150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:19">
+      <c r="T150" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="B151" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>96</v>
       </c>
       <c r="D151">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="E151" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -10134,13 +10597,16 @@
       <c r="S151">
         <v>3</v>
       </c>
-    </row>
-    <row r="152" spans="1:19">
+      <c r="T151" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="B152" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>153</v>
@@ -10149,7 +10615,7 @@
         <v>13.41</v>
       </c>
       <c r="E152" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -10193,13 +10659,16 @@
       <c r="S152">
         <v>5</v>
       </c>
-    </row>
-    <row r="153" spans="1:19">
+      <c r="T152" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="B153" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C153">
         <v>111</v>
@@ -10208,7 +10677,7 @@
         <v>12.74</v>
       </c>
       <c r="E153" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -10252,13 +10721,16 @@
       <c r="S153">
         <v>5</v>
       </c>
-    </row>
-    <row r="154" spans="1:19">
+      <c r="T153" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="B154" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="C154">
         <v>199</v>
@@ -10267,7 +10739,7 @@
         <v>17.62</v>
       </c>
       <c r="E154" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -10311,13 +10783,16 @@
       <c r="S154">
         <v>5</v>
       </c>
-    </row>
-    <row r="155" spans="1:19">
+      <c r="T154" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="B155" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="C155">
         <v>206</v>
@@ -10326,7 +10801,7 @@
         <v>18.89</v>
       </c>
       <c r="E155" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -10370,22 +10845,25 @@
       <c r="S155">
         <v>5</v>
       </c>
-    </row>
-    <row r="156" spans="1:19">
+      <c r="T155" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="B156" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="C156">
         <v>181</v>
       </c>
       <c r="D156">
-        <v>16.74</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="E156" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -10429,13 +10907,16 @@
       <c r="S156">
         <v>5</v>
       </c>
-    </row>
-    <row r="157" spans="1:19">
+      <c r="T156" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="B157" t="s">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="C157">
         <v>5</v>
@@ -10444,7 +10925,7 @@
         <v>0.1</v>
       </c>
       <c r="E157" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -10488,13 +10969,16 @@
       <c r="S157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:19">
+      <c r="T157" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="B158" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="C158">
         <v>57</v>
@@ -10503,7 +10987,7 @@
         <v>3.42</v>
       </c>
       <c r="E158" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -10547,13 +11031,16 @@
       <c r="S158">
         <v>5</v>
       </c>
-    </row>
-    <row r="159" spans="1:19">
+      <c r="T158" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="B159" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="C159">
         <v>116</v>
@@ -10562,7 +11049,7 @@
         <v>11.36</v>
       </c>
       <c r="E159" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -10606,13 +11093,16 @@
       <c r="S159">
         <v>2</v>
       </c>
-    </row>
-    <row r="160" spans="1:19">
+      <c r="T159" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="B160" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="C160">
         <v>59</v>
@@ -10621,7 +11111,7 @@
         <v>4.3</v>
       </c>
       <c r="E160" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -10665,13 +11155,16 @@
       <c r="S160">
         <v>2</v>
       </c>
-    </row>
-    <row r="161" spans="1:19">
+      <c r="T160" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="B161" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="C161">
         <v>118</v>
@@ -10680,7 +11173,7 @@
         <v>9.32</v>
       </c>
       <c r="E161" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -10724,13 +11217,16 @@
       <c r="S161">
         <v>5</v>
       </c>
-    </row>
-    <row r="162" spans="1:19">
+      <c r="T161" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="B162" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="C162">
         <v>58</v>
@@ -10739,7 +11235,7 @@
         <v>4.12</v>
       </c>
       <c r="E162" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -10783,22 +11279,25 @@
       <c r="S162">
         <v>5</v>
       </c>
-    </row>
-    <row r="163" spans="1:19">
+      <c r="T162" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="C163">
         <v>105</v>
       </c>
       <c r="D163">
-        <v>10.21</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="E163" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -10842,13 +11341,16 @@
       <c r="S163">
         <v>2</v>
       </c>
-    </row>
-    <row r="164" spans="1:19">
+      <c r="T163" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="B164" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="C164">
         <v>49</v>
@@ -10857,7 +11359,7 @@
         <v>3.65</v>
       </c>
       <c r="E164" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -10901,13 +11403,16 @@
       <c r="S164">
         <v>3</v>
       </c>
-    </row>
-    <row r="165" spans="1:19">
+      <c r="T164" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="B165" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C165">
         <v>141</v>
@@ -10916,7 +11421,7 @@
         <v>9.65</v>
       </c>
       <c r="E165" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -10960,13 +11465,16 @@
       <c r="S165">
         <v>5</v>
       </c>
-    </row>
-    <row r="166" spans="1:19">
+      <c r="T165" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B166" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C166">
         <v>180</v>
@@ -10975,7 +11483,7 @@
         <v>14.98</v>
       </c>
       <c r="E166" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -11019,13 +11527,16 @@
       <c r="S166">
         <v>5</v>
       </c>
-    </row>
-    <row r="167" spans="1:19">
+      <c r="T166" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="B167" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C167">
         <v>193</v>
@@ -11034,7 +11545,7 @@
         <v>14.38</v>
       </c>
       <c r="E167" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -11078,13 +11589,16 @@
       <c r="S167">
         <v>5</v>
       </c>
-    </row>
-    <row r="168" spans="1:19">
+      <c r="T167" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="B168" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C168">
         <v>116</v>
@@ -11093,7 +11607,7 @@
         <v>11.32</v>
       </c>
       <c r="E168" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -11137,13 +11651,16 @@
       <c r="S168">
         <v>5</v>
       </c>
-    </row>
-    <row r="169" spans="1:19">
+      <c r="T168" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="B169" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C169">
         <v>159</v>
@@ -11152,7 +11669,7 @@
         <v>15.32</v>
       </c>
       <c r="E169" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -11196,13 +11713,16 @@
       <c r="S169">
         <v>4</v>
       </c>
-    </row>
-    <row r="170" spans="1:19">
+      <c r="T169" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="B170" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C170">
         <v>26</v>
@@ -11211,7 +11731,7 @@
         <v>0.9</v>
       </c>
       <c r="E170" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -11255,13 +11775,16 @@
       <c r="S170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:19">
+      <c r="T170" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="B171" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -11270,7 +11793,7 @@
         <v>0.12</v>
       </c>
       <c r="E171" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -11314,13 +11837,16 @@
       <c r="S171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:19">
+      <c r="T171" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="B172" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="C172">
         <v>171</v>
@@ -11329,7 +11855,7 @@
         <v>17.32</v>
       </c>
       <c r="E172" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -11373,13 +11899,16 @@
       <c r="S172">
         <v>5</v>
       </c>
-    </row>
-    <row r="173" spans="1:19">
+      <c r="T172" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="B173" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="C173">
         <v>142</v>
@@ -11388,7 +11917,7 @@
         <v>11.98</v>
       </c>
       <c r="E173" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -11432,22 +11961,25 @@
       <c r="S173">
         <v>5</v>
       </c>
-    </row>
-    <row r="174" spans="1:19">
+      <c r="T173" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="B174" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C174">
         <v>103</v>
       </c>
       <c r="D174">
-        <v>8.789999999999999</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="E174" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -11491,13 +12023,16 @@
       <c r="S174">
         <v>5</v>
       </c>
-    </row>
-    <row r="175" spans="1:19">
+      <c r="T174" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="B175" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C175">
         <v>11</v>
@@ -11506,7 +12041,7 @@
         <v>0.32</v>
       </c>
       <c r="E175" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -11550,13 +12085,16 @@
       <c r="S175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:19">
+      <c r="T175" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="B176" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C176">
         <v>204</v>
@@ -11565,7 +12103,7 @@
         <v>20.89</v>
       </c>
       <c r="E176" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -11609,13 +12147,16 @@
       <c r="S176">
         <v>5</v>
       </c>
-    </row>
-    <row r="177" spans="1:19">
+      <c r="T176" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="B177" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C177">
         <v>186</v>
@@ -11624,7 +12165,7 @@
         <v>13.65</v>
       </c>
       <c r="E177" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -11668,13 +12209,16 @@
       <c r="S177">
         <v>5</v>
       </c>
-    </row>
-    <row r="178" spans="1:19">
+      <c r="T177" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="B178" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -11683,7 +12227,7 @@
         <v>0.32</v>
       </c>
       <c r="E178" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -11727,13 +12271,16 @@
       <c r="S178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:19">
+      <c r="T178" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="B179" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C179">
         <v>190</v>
@@ -11742,7 +12289,7 @@
         <v>16.27</v>
       </c>
       <c r="E179" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -11786,13 +12333,16 @@
       <c r="S179">
         <v>5</v>
       </c>
-    </row>
-    <row r="180" spans="1:19">
+      <c r="T179" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>156</v>
+        <v>220</v>
       </c>
       <c r="B180" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C180">
         <v>125</v>
@@ -11801,7 +12351,7 @@
         <v>15.32</v>
       </c>
       <c r="E180" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -11845,13 +12395,16 @@
       <c r="S180">
         <v>8</v>
       </c>
-    </row>
-    <row r="181" spans="1:19">
+      <c r="T180" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="B181" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C181">
         <v>59</v>
@@ -11860,7 +12413,7 @@
         <v>3.54</v>
       </c>
       <c r="E181" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -11904,13 +12457,16 @@
       <c r="S181">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:19">
+      <c r="T181" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="B182" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C182">
         <v>27</v>
@@ -11919,7 +12475,7 @@
         <v>1.21</v>
       </c>
       <c r="E182" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -11963,13 +12519,16 @@
       <c r="S182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:19">
+      <c r="T182" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="B183" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C183">
         <v>54</v>
@@ -11978,7 +12537,7 @@
         <v>3.17</v>
       </c>
       <c r="E183" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -12022,13 +12581,16 @@
       <c r="S183">
         <v>5</v>
       </c>
-    </row>
-    <row r="184" spans="1:19">
+      <c r="T183" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="B184" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C184">
         <v>192</v>
@@ -12037,7 +12599,7 @@
         <v>17.98</v>
       </c>
       <c r="E184" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -12081,22 +12643,25 @@
       <c r="S184">
         <v>5</v>
       </c>
-    </row>
-    <row r="185" spans="1:19">
+      <c r="T184" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="B185" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C185">
         <v>67</v>
       </c>
       <c r="D185">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E185" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -12140,13 +12705,16 @@
       <c r="S185">
         <v>5</v>
       </c>
-    </row>
-    <row r="186" spans="1:19">
+      <c r="T185" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="B186" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C186">
         <v>8</v>
@@ -12155,7 +12723,7 @@
         <v>0.54</v>
       </c>
       <c r="E186" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -12199,13 +12767,16 @@
       <c r="S186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:19">
+      <c r="T186" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="B187" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C187">
         <v>185</v>
@@ -12214,7 +12785,7 @@
         <v>16.87</v>
       </c>
       <c r="E187" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -12258,13 +12829,16 @@
       <c r="S187">
         <v>5</v>
       </c>
-    </row>
-    <row r="188" spans="1:19">
+      <c r="T187" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="B188" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C188">
         <v>181</v>
@@ -12273,7 +12847,7 @@
         <v>21.5</v>
       </c>
       <c r="E188" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -12317,13 +12891,16 @@
       <c r="S188">
         <v>5</v>
       </c>
-    </row>
-    <row r="189" spans="1:19">
+      <c r="T188" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="B189" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C189">
         <v>178</v>
@@ -12332,7 +12909,7 @@
         <v>20.21</v>
       </c>
       <c r="E189" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -12376,13 +12953,16 @@
       <c r="S189">
         <v>10</v>
       </c>
-    </row>
-    <row r="190" spans="1:19">
+      <c r="T189" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="B190" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C190">
         <v>165</v>
@@ -12391,7 +12971,7 @@
         <v>17.54</v>
       </c>
       <c r="E190" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -12435,13 +13015,16 @@
       <c r="S190">
         <v>5</v>
       </c>
-    </row>
-    <row r="191" spans="1:19">
+      <c r="T190" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="B191" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C191">
         <v>138</v>
@@ -12450,7 +13033,7 @@
         <v>15.32</v>
       </c>
       <c r="E191" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -12494,13 +13077,16 @@
       <c r="S191">
         <v>4</v>
       </c>
-    </row>
-    <row r="192" spans="1:19">
+      <c r="T191" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="B192" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C192">
         <v>36</v>
@@ -12509,7 +13095,7 @@
         <v>3.21</v>
       </c>
       <c r="E192" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -12553,13 +13139,16 @@
       <c r="S192">
         <v>4</v>
       </c>
-    </row>
-    <row r="193" spans="1:19">
+      <c r="T192" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="B193" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C193">
         <v>119</v>
@@ -12568,7 +13157,7 @@
         <v>18.32</v>
       </c>
       <c r="E193" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -12612,13 +13201,16 @@
       <c r="S193">
         <v>5</v>
       </c>
-    </row>
-    <row r="194" spans="1:19">
+      <c r="T193" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="B194" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -12627,7 +13219,7 @@
         <v>0.04</v>
       </c>
       <c r="E194" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -12671,13 +13263,16 @@
       <c r="S194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:19">
+      <c r="T194" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="B195" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C195">
         <v>177</v>
@@ -12686,7 +13281,7 @@
         <v>17.98</v>
       </c>
       <c r="E195" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -12730,13 +13325,16 @@
       <c r="S195">
         <v>5</v>
       </c>
-    </row>
-    <row r="196" spans="1:19">
+      <c r="T195" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="B196" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C196">
         <v>118</v>
@@ -12745,7 +13343,7 @@
         <v>17.34</v>
       </c>
       <c r="E196" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -12789,13 +13387,16 @@
       <c r="S196">
         <v>3</v>
       </c>
-    </row>
-    <row r="197" spans="1:19">
+      <c r="T196" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="B197" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C197">
         <v>69</v>
@@ -12804,7 +13405,7 @@
         <v>5.21</v>
       </c>
       <c r="E197" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -12848,13 +13449,16 @@
       <c r="S197">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:19">
+      <c r="T197" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="B198" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C198">
         <v>11</v>
@@ -12863,7 +13467,7 @@
         <v>0.79</v>
       </c>
       <c r="E198" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -12907,13 +13511,16 @@
       <c r="S198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:19">
+      <c r="T198" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="B199" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C199">
         <v>44</v>
@@ -12922,7 +13529,7 @@
         <v>3.24</v>
       </c>
       <c r="E199" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -12966,13 +13573,16 @@
       <c r="S199">
         <v>2</v>
       </c>
-    </row>
-    <row r="200" spans="1:19">
+      <c r="T199" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="B200" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C200">
         <v>21</v>
@@ -12981,7 +13591,7 @@
         <v>1.17</v>
       </c>
       <c r="E200" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -13025,13 +13635,16 @@
       <c r="S200">
         <v>2</v>
       </c>
-    </row>
-    <row r="201" spans="1:19">
+      <c r="T200" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="B201" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C201">
         <v>85</v>
@@ -13040,7 +13653,7 @@
         <v>7.32</v>
       </c>
       <c r="E201" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -13084,13 +13697,16 @@
       <c r="S201">
         <v>7</v>
       </c>
-    </row>
-    <row r="202" spans="1:19">
+      <c r="T201" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="B202" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C202">
         <v>91</v>
@@ -13099,7 +13715,7 @@
         <v>9.32</v>
       </c>
       <c r="E202" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -13143,13 +13759,16 @@
       <c r="S202">
         <v>5</v>
       </c>
-    </row>
-    <row r="203" spans="1:19">
+      <c r="T202" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="B203" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C203">
         <v>69</v>
@@ -13158,7 +13777,7 @@
         <v>4.32</v>
       </c>
       <c r="E203" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -13202,22 +13821,25 @@
       <c r="S203">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:19">
+      <c r="T203" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="B204" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C204">
         <v>24</v>
       </c>
       <c r="D204">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E204" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -13261,13 +13883,16 @@
       <c r="S204">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:19">
+      <c r="T204" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="B205" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C205">
         <v>80</v>
@@ -13276,7 +13901,7 @@
         <v>5.32</v>
       </c>
       <c r="E205" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -13320,13 +13945,16 @@
       <c r="S205">
         <v>5</v>
       </c>
-    </row>
-    <row r="206" spans="1:19">
+      <c r="T205" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="B206" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C206">
         <v>105</v>
@@ -13335,7 +13963,7 @@
         <v>11.32</v>
       </c>
       <c r="E206" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -13379,13 +14007,16 @@
       <c r="S206">
         <v>4</v>
       </c>
-    </row>
-    <row r="207" spans="1:19">
+      <c r="T206" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="B207" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C207">
         <v>17</v>
@@ -13394,7 +14025,7 @@
         <v>0.18</v>
       </c>
       <c r="E207" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -13438,13 +14069,16 @@
       <c r="S207">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:19">
+      <c r="T207" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="B208" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -13453,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -13497,13 +14131,16 @@
       <c r="S208">
         <v>3</v>
       </c>
-    </row>
-    <row r="209" spans="1:19">
+      <c r="T208" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="B209" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C209">
         <v>40</v>
@@ -13512,7 +14149,7 @@
         <v>3.21</v>
       </c>
       <c r="E209" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -13556,13 +14193,16 @@
       <c r="S209">
         <v>2</v>
       </c>
-    </row>
-    <row r="210" spans="1:19">
+      <c r="T209" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="B210" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C210">
         <v>2</v>
@@ -13571,7 +14211,7 @@
         <v>0.01</v>
       </c>
       <c r="E210" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -13615,13 +14255,16 @@
       <c r="S210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:19">
+      <c r="T210" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="B211" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C211">
         <v>125</v>
@@ -13630,7 +14273,7 @@
         <v>19.32</v>
       </c>
       <c r="E211" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -13674,13 +14317,16 @@
       <c r="S211">
         <v>3</v>
       </c>
-    </row>
-    <row r="212" spans="1:19">
+      <c r="T211" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="B212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C212">
         <v>12</v>
@@ -13689,7 +14335,7 @@
         <v>0.02</v>
       </c>
       <c r="E212" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -13733,22 +14379,25 @@
       <c r="S212">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:19">
+      <c r="T212" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="B213" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C213">
         <v>124</v>
       </c>
       <c r="D213">
-        <v>19.35</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="E213" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -13792,13 +14441,16 @@
       <c r="S213">
         <v>4</v>
       </c>
-    </row>
-    <row r="214" spans="1:19">
+      <c r="T213" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="B214" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C214">
         <v>8</v>
@@ -13807,7 +14459,7 @@
         <v>0.03</v>
       </c>
       <c r="E214" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -13851,13 +14503,16 @@
       <c r="S214">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:19">
+      <c r="T214" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>181</v>
+        <v>267</v>
       </c>
       <c r="B215" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C215">
         <v>36</v>
@@ -13866,7 +14521,7 @@
         <v>3.21</v>
       </c>
       <c r="E215" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -13910,22 +14565,25 @@
       <c r="S215">
         <v>2</v>
       </c>
-    </row>
-    <row r="216" spans="1:19">
+      <c r="T215" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="B216" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C216">
         <v>89</v>
       </c>
       <c r="D216">
-        <v>9.369999999999999</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="E216" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -13969,13 +14627,16 @@
       <c r="S216">
         <v>3</v>
       </c>
-    </row>
-    <row r="217" spans="1:19">
+      <c r="T216" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="B217" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C217">
         <v>105</v>
@@ -13984,7 +14645,7 @@
         <v>16.12</v>
       </c>
       <c r="E217" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -14028,67 +14689,135 @@
       <c r="S217">
         <v>3</v>
       </c>
-    </row>
-    <row r="218" spans="1:19">
+      <c r="T217" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>184</v>
+        <v>271</v>
       </c>
       <c r="B218" t="s">
-        <v>255</v>
-      </c>
-      <c r="C218" t="s">
-        <v>256</v>
-      </c>
-      <c r="D218" t="s">
-        <v>257</v>
+        <v>272</v>
+      </c>
+      <c r="C218">
+        <v>136</v>
+      </c>
+      <c r="D218">
+        <v>17.920000000000002</v>
       </c>
       <c r="E218" t="s">
-        <v>259</v>
-      </c>
-      <c r="F218" t="s">
+        <v>24</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>9</v>
+      </c>
+      <c r="H218">
+        <v>17</v>
+      </c>
+      <c r="I218">
+        <v>17</v>
+      </c>
+      <c r="J218">
+        <v>17</v>
+      </c>
+      <c r="K218">
+        <v>10</v>
+      </c>
+      <c r="L218">
+        <v>6</v>
+      </c>
+      <c r="M218">
         <v>274</v>
       </c>
-      <c r="G218" t="s">
+      <c r="N218">
+        <v>4</v>
+      </c>
+      <c r="O218">
+        <v>4</v>
+      </c>
+      <c r="P218">
+        <v>3</v>
+      </c>
+      <c r="Q218">
+        <v>21</v>
+      </c>
+      <c r="R218">
+        <v>1</v>
+      </c>
+      <c r="S218">
+        <v>5</v>
+      </c>
+      <c r="T218" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>273</v>
+      </c>
+      <c r="B219" t="s">
+        <v>245</v>
+      </c>
+      <c r="C219" t="s">
+        <v>274</v>
+      </c>
+      <c r="D219" t="s">
         <v>275</v>
       </c>
-      <c r="H218" t="s">
+      <c r="E219" t="s">
+        <v>24</v>
+      </c>
+      <c r="F219" t="s">
         <v>276</v>
       </c>
-      <c r="I218" t="s">
+      <c r="G219" t="s">
+        <v>277</v>
+      </c>
+      <c r="H219" t="s">
+        <v>278</v>
+      </c>
+      <c r="I219" t="s">
+        <v>278</v>
+      </c>
+      <c r="J219" t="s">
+        <v>278</v>
+      </c>
+      <c r="K219" t="s">
+        <v>275</v>
+      </c>
+      <c r="L219" t="s">
+        <v>279</v>
+      </c>
+      <c r="M219" t="s">
+        <v>280</v>
+      </c>
+      <c r="N219" t="s">
+        <v>281</v>
+      </c>
+      <c r="O219" t="s">
+        <v>281</v>
+      </c>
+      <c r="P219" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>275</v>
+      </c>
+      <c r="R219" t="s">
         <v>276</v>
       </c>
-      <c r="J218" t="s">
-        <v>276</v>
-      </c>
-      <c r="K218" t="s">
-        <v>277</v>
-      </c>
-      <c r="L218" t="s">
-        <v>278</v>
-      </c>
-      <c r="M218" t="s">
-        <v>279</v>
-      </c>
-      <c r="N218" t="s">
-        <v>280</v>
-      </c>
-      <c r="O218" t="s">
-        <v>280</v>
-      </c>
-      <c r="P218" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q218" t="s">
+      <c r="S219" t="s">
         <v>282</v>
       </c>
-      <c r="R218" t="s">
-        <v>274</v>
-      </c>
-      <c r="S218" t="s">
-        <v>283</v>
+      <c r="T219" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>